--- a/ReporteChoferes.xlsx
+++ b/ReporteChoferes.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12300"/>
+    <workbookView windowWidth="28800" windowHeight="11580"/>
   </bookViews>
   <sheets>
     <sheet name="Worksheet" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>REPORTE DE CHOFERES</t>
   </si>
@@ -74,7 +74,10 @@
     <t xml:space="preserve">Ganancia </t>
   </si>
   <si>
-    <t>Empresa</t>
+    <t>Tickets</t>
+  </si>
+  <si>
+    <t>Dias trabajados</t>
   </si>
 </sst>
 </file>
@@ -87,7 +90,7 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -115,6 +118,11 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Calibri"/>
       <charset val="134"/>
     </font>
@@ -579,29 +587,26 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -610,119 +615,122 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -735,6 +743,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1098,6 +1109,7 @@
     <col min="12" max="12" width="15" customWidth="1"/>
     <col min="13" max="13" width="18.7142857142857" customWidth="1"/>
     <col min="14" max="14" width="13.2857142857143" customWidth="1"/>
+    <col min="15" max="15" width="20.5714285714286" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" customHeight="1" spans="1:18">
@@ -1118,7 +1130,7 @@
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
-      <c r="O1" s="5"/>
+      <c r="O1" s="1"/>
       <c r="P1" s="5"/>
       <c r="Q1" s="5"/>
       <c r="R1" s="5"/>
@@ -1137,7 +1149,7 @@
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
       <c r="N2" s="1"/>
-      <c r="O2" s="5"/>
+      <c r="O2" s="1"/>
       <c r="P2" s="5"/>
       <c r="Q2" s="5"/>
       <c r="R2" s="5"/>
@@ -1156,7 +1168,7 @@
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
       <c r="N3" s="1"/>
-      <c r="O3" s="5"/>
+      <c r="O3" s="1"/>
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
@@ -1175,7 +1187,7 @@
       <c r="L4" s="1"/>
       <c r="M4" s="1"/>
       <c r="N4" s="1"/>
-      <c r="O4" s="5"/>
+      <c r="O4" s="1"/>
       <c r="P4" s="5"/>
       <c r="Q4" s="5"/>
       <c r="R4" s="5"/>
@@ -1194,7 +1206,7 @@
       <c r="L5" s="1"/>
       <c r="M5" s="1"/>
       <c r="N5" s="1"/>
-      <c r="O5" s="5"/>
+      <c r="O5" s="1"/>
       <c r="P5" s="5"/>
       <c r="Q5" s="5"/>
       <c r="R5" s="5"/>
@@ -1215,12 +1227,12 @@
       <c r="L6" s="1"/>
       <c r="M6" s="1"/>
       <c r="N6" s="1"/>
-      <c r="O6" s="6"/>
+      <c r="O6" s="1"/>
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
     </row>
-    <row r="7" ht="18.75" customHeight="1" spans="1:14">
+    <row r="7" ht="18.75" customHeight="1" spans="1:15">
       <c r="A7" s="3" t="s">
         <v>3</v>
       </c>
@@ -1259,6 +1271,9 @@
       </c>
       <c r="N7" s="3" t="s">
         <v>15</v>
+      </c>
+      <c r="O7" s="3" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="7:18">
@@ -1269,7 +1284,7 @@
         <v/>
       </c>
       <c r="N8" s="7"/>
-      <c r="O8" s="5"/>
+      <c r="O8" s="8"/>
       <c r="P8" s="5"/>
       <c r="Q8" s="5"/>
       <c r="R8" s="5"/>
@@ -1282,7 +1297,7 @@
         <v/>
       </c>
       <c r="N9" s="7"/>
-      <c r="O9" s="5"/>
+      <c r="O9" s="8"/>
       <c r="P9" s="5"/>
       <c r="Q9" s="5"/>
       <c r="R9" s="5"/>
@@ -1295,7 +1310,7 @@
         <v/>
       </c>
       <c r="N10" s="7"/>
-      <c r="O10" s="5"/>
+      <c r="O10" s="8"/>
       <c r="P10" s="5"/>
       <c r="Q10" s="5"/>
       <c r="R10" s="5"/>
@@ -1308,7 +1323,7 @@
         <v/>
       </c>
       <c r="N11" s="7"/>
-      <c r="O11" s="5"/>
+      <c r="O11" s="8"/>
       <c r="P11" s="5"/>
       <c r="Q11" s="5"/>
       <c r="R11" s="5"/>
@@ -1321,7 +1336,7 @@
         <v/>
       </c>
       <c r="N12" s="7"/>
-      <c r="O12" s="5"/>
+      <c r="O12" s="8"/>
       <c r="P12" s="5"/>
       <c r="Q12" s="5"/>
       <c r="R12" s="5"/>
@@ -1334,7 +1349,7 @@
         <v/>
       </c>
       <c r="N13" s="7"/>
-      <c r="O13" s="5"/>
+      <c r="O13" s="8"/>
       <c r="P13" s="5"/>
       <c r="Q13" s="5"/>
       <c r="R13" s="5"/>
@@ -1347,12 +1362,12 @@
         <v/>
       </c>
       <c r="N14" s="7"/>
-      <c r="O14" s="6"/>
+      <c r="O14" s="8"/>
       <c r="P14" s="6"/>
       <c r="Q14" s="6"/>
       <c r="R14" s="6"/>
     </row>
-    <row r="15" spans="7:14">
+    <row r="15" spans="7:15">
       <c r="G15" s="4"/>
       <c r="K15" s="4"/>
       <c r="M15" s="4" t="str">
@@ -1360,6 +1375,7 @@
         <v/>
       </c>
       <c r="N15" s="7"/>
+      <c r="O15" s="9"/>
     </row>
     <row r="16" customHeight="1" spans="7:18">
       <c r="G16" s="4"/>
@@ -1369,7 +1385,7 @@
         <v/>
       </c>
       <c r="N16" s="7"/>
-      <c r="O16" s="5"/>
+      <c r="O16" s="8"/>
       <c r="P16" s="5"/>
       <c r="Q16" s="5"/>
       <c r="R16" s="5"/>
@@ -1382,7 +1398,7 @@
         <v/>
       </c>
       <c r="N17" s="7"/>
-      <c r="O17" s="5"/>
+      <c r="O17" s="8"/>
       <c r="P17" s="5"/>
       <c r="Q17" s="5"/>
       <c r="R17" s="5"/>
@@ -1395,7 +1411,7 @@
         <v/>
       </c>
       <c r="N18" s="7"/>
-      <c r="O18" s="5"/>
+      <c r="O18" s="8"/>
       <c r="P18" s="5"/>
       <c r="Q18" s="5"/>
       <c r="R18" s="5"/>
@@ -1408,7 +1424,7 @@
         <v/>
       </c>
       <c r="N19" s="7"/>
-      <c r="O19" s="5"/>
+      <c r="O19" s="8"/>
       <c r="P19" s="5"/>
       <c r="Q19" s="5"/>
       <c r="R19" s="5"/>
@@ -1421,7 +1437,7 @@
         <v/>
       </c>
       <c r="N20" s="7"/>
-      <c r="O20" s="5"/>
+      <c r="O20" s="8"/>
       <c r="P20" s="5"/>
       <c r="Q20" s="5"/>
       <c r="R20" s="5"/>
@@ -1434,7 +1450,7 @@
         <v/>
       </c>
       <c r="N21" s="7"/>
-      <c r="O21" s="5"/>
+      <c r="O21" s="8"/>
       <c r="P21" s="5"/>
       <c r="Q21" s="5"/>
       <c r="R21" s="5"/>
@@ -1447,12 +1463,12 @@
         <v/>
       </c>
       <c r="N22" s="7"/>
-      <c r="O22" s="6"/>
+      <c r="O22" s="8"/>
       <c r="P22" s="6"/>
       <c r="Q22" s="6"/>
       <c r="R22" s="6"/>
     </row>
-    <row r="23" spans="7:14">
+    <row r="23" spans="7:15">
       <c r="G23" s="4"/>
       <c r="K23" s="4"/>
       <c r="M23" s="4" t="str">
@@ -1460,8 +1476,9 @@
         <v/>
       </c>
       <c r="N23" s="7"/>
-    </row>
-    <row r="24" spans="7:14">
+      <c r="O23" s="9"/>
+    </row>
+    <row r="24" spans="7:15">
       <c r="G24" s="4"/>
       <c r="K24" s="4"/>
       <c r="M24" s="4" t="str">
@@ -1469,8 +1486,9 @@
         <v/>
       </c>
       <c r="N24" s="7"/>
-    </row>
-    <row r="25" spans="7:14">
+      <c r="O24" s="9"/>
+    </row>
+    <row r="25" spans="7:15">
       <c r="G25" s="4"/>
       <c r="K25" s="4"/>
       <c r="M25" s="4" t="str">
@@ -1478,8 +1496,9 @@
         <v/>
       </c>
       <c r="N25" s="7"/>
-    </row>
-    <row r="26" spans="7:14">
+      <c r="O25" s="9"/>
+    </row>
+    <row r="26" spans="7:15">
       <c r="G26" s="4"/>
       <c r="K26" s="4"/>
       <c r="M26" s="4" t="str">
@@ -1487,8 +1506,9 @@
         <v/>
       </c>
       <c r="N26" s="7"/>
-    </row>
-    <row r="27" spans="7:14">
+      <c r="O26" s="9"/>
+    </row>
+    <row r="27" spans="7:15">
       <c r="G27" s="4"/>
       <c r="K27" s="4"/>
       <c r="M27" s="4" t="str">
@@ -1496,8 +1516,9 @@
         <v/>
       </c>
       <c r="N27" s="7"/>
-    </row>
-    <row r="28" spans="7:14">
+      <c r="O27" s="9"/>
+    </row>
+    <row r="28" spans="7:15">
       <c r="G28" s="4"/>
       <c r="K28" s="4"/>
       <c r="M28" s="4" t="str">
@@ -1505,8 +1526,9 @@
         <v/>
       </c>
       <c r="N28" s="7"/>
-    </row>
-    <row r="29" spans="7:14">
+      <c r="O28" s="9"/>
+    </row>
+    <row r="29" spans="7:15">
       <c r="G29" s="4"/>
       <c r="K29" s="4"/>
       <c r="M29" s="4" t="str">
@@ -1514,8 +1536,9 @@
         <v/>
       </c>
       <c r="N29" s="7"/>
-    </row>
-    <row r="30" spans="7:14">
+      <c r="O29" s="9"/>
+    </row>
+    <row r="30" spans="7:15">
       <c r="G30" s="4"/>
       <c r="K30" s="4"/>
       <c r="M30" s="4" t="str">
@@ -1523,8 +1546,9 @@
         <v/>
       </c>
       <c r="N30" s="7"/>
-    </row>
-    <row r="31" spans="7:14">
+      <c r="O30" s="9"/>
+    </row>
+    <row r="31" spans="7:15">
       <c r="G31" s="4"/>
       <c r="K31" s="4"/>
       <c r="M31" s="4" t="str">
@@ -1532,8 +1556,9 @@
         <v/>
       </c>
       <c r="N31" s="7"/>
-    </row>
-    <row r="32" spans="7:14">
+      <c r="O31" s="9"/>
+    </row>
+    <row r="32" spans="7:15">
       <c r="G32" s="4"/>
       <c r="K32" s="4"/>
       <c r="M32" s="4" t="str">
@@ -1541,8 +1566,9 @@
         <v/>
       </c>
       <c r="N32" s="7"/>
-    </row>
-    <row r="33" spans="7:14">
+      <c r="O32" s="9"/>
+    </row>
+    <row r="33" spans="7:15">
       <c r="G33" s="4"/>
       <c r="K33" s="4"/>
       <c r="M33" s="4" t="str">
@@ -1550,8 +1576,9 @@
         <v/>
       </c>
       <c r="N33" s="7"/>
-    </row>
-    <row r="34" spans="7:14">
+      <c r="O33" s="9"/>
+    </row>
+    <row r="34" spans="7:15">
       <c r="G34" s="4"/>
       <c r="K34" s="4"/>
       <c r="M34" s="4" t="str">
@@ -1559,8 +1586,9 @@
         <v/>
       </c>
       <c r="N34" s="7"/>
-    </row>
-    <row r="35" spans="7:14">
+      <c r="O34" s="9"/>
+    </row>
+    <row r="35" spans="7:15">
       <c r="G35" s="4"/>
       <c r="K35" s="4"/>
       <c r="M35" s="4" t="str">
@@ -1568,8 +1596,9 @@
         <v/>
       </c>
       <c r="N35" s="7"/>
-    </row>
-    <row r="36" spans="7:14">
+      <c r="O35" s="9"/>
+    </row>
+    <row r="36" spans="7:15">
       <c r="G36" s="4"/>
       <c r="K36" s="4"/>
       <c r="M36" s="4" t="str">
@@ -1577,8 +1606,9 @@
         <v/>
       </c>
       <c r="N36" s="7"/>
-    </row>
-    <row r="37" spans="7:14">
+      <c r="O36" s="9"/>
+    </row>
+    <row r="37" spans="7:15">
       <c r="G37" s="4"/>
       <c r="K37" s="4"/>
       <c r="M37" s="4" t="str">
@@ -1586,8 +1616,9 @@
         <v/>
       </c>
       <c r="N37" s="7"/>
-    </row>
-    <row r="38" spans="7:14">
+      <c r="O37" s="9"/>
+    </row>
+    <row r="38" spans="7:15">
       <c r="G38" s="4"/>
       <c r="K38" s="4"/>
       <c r="M38" s="4" t="str">
@@ -1595,8 +1626,9 @@
         <v/>
       </c>
       <c r="N38" s="7"/>
-    </row>
-    <row r="39" spans="7:14">
+      <c r="O38" s="9"/>
+    </row>
+    <row r="39" spans="7:15">
       <c r="G39" s="4"/>
       <c r="K39" s="4"/>
       <c r="M39" s="4" t="str">
@@ -1604,8 +1636,9 @@
         <v/>
       </c>
       <c r="N39" s="7"/>
-    </row>
-    <row r="40" spans="7:14">
+      <c r="O39" s="9"/>
+    </row>
+    <row r="40" spans="7:15">
       <c r="G40" s="4"/>
       <c r="K40" s="4"/>
       <c r="M40" s="4" t="str">
@@ -1613,8 +1646,9 @@
         <v/>
       </c>
       <c r="N40" s="7"/>
-    </row>
-    <row r="41" spans="7:14">
+      <c r="O40" s="9"/>
+    </row>
+    <row r="41" spans="7:15">
       <c r="G41" s="4"/>
       <c r="K41" s="4"/>
       <c r="M41" s="4" t="str">
@@ -1622,8 +1656,9 @@
         <v/>
       </c>
       <c r="N41" s="7"/>
-    </row>
-    <row r="42" spans="7:14">
+      <c r="O41" s="9"/>
+    </row>
+    <row r="42" spans="7:15">
       <c r="G42" s="4"/>
       <c r="K42" s="4"/>
       <c r="M42" s="4" t="str">
@@ -1631,8 +1666,9 @@
         <v/>
       </c>
       <c r="N42" s="7"/>
-    </row>
-    <row r="43" spans="7:14">
+      <c r="O42" s="9"/>
+    </row>
+    <row r="43" spans="7:15">
       <c r="G43" s="4"/>
       <c r="K43" s="4"/>
       <c r="M43" s="4" t="str">
@@ -1640,8 +1676,9 @@
         <v/>
       </c>
       <c r="N43" s="7"/>
-    </row>
-    <row r="44" spans="7:14">
+      <c r="O43" s="9"/>
+    </row>
+    <row r="44" spans="7:15">
       <c r="G44" s="4"/>
       <c r="K44" s="4"/>
       <c r="M44" s="4" t="str">
@@ -1649,8 +1686,9 @@
         <v/>
       </c>
       <c r="N44" s="7"/>
-    </row>
-    <row r="45" spans="7:14">
+      <c r="O44" s="9"/>
+    </row>
+    <row r="45" spans="7:15">
       <c r="G45" s="4"/>
       <c r="K45" s="4"/>
       <c r="M45" s="4" t="str">
@@ -1658,8 +1696,9 @@
         <v/>
       </c>
       <c r="N45" s="7"/>
-    </row>
-    <row r="46" spans="7:14">
+      <c r="O45" s="9"/>
+    </row>
+    <row r="46" spans="7:15">
       <c r="G46" s="4"/>
       <c r="K46" s="4"/>
       <c r="M46" s="4" t="str">
@@ -1667,8 +1706,9 @@
         <v/>
       </c>
       <c r="N46" s="7"/>
-    </row>
-    <row r="47" spans="7:14">
+      <c r="O46" s="9"/>
+    </row>
+    <row r="47" spans="7:15">
       <c r="G47" s="4"/>
       <c r="K47" s="4"/>
       <c r="M47" s="4" t="str">
@@ -1676,8 +1716,9 @@
         <v/>
       </c>
       <c r="N47" s="7"/>
-    </row>
-    <row r="48" spans="7:14">
+      <c r="O47" s="9"/>
+    </row>
+    <row r="48" spans="7:15">
       <c r="G48" s="4"/>
       <c r="K48" s="4"/>
       <c r="M48" s="4" t="str">
@@ -1685,8 +1726,9 @@
         <v/>
       </c>
       <c r="N48" s="7"/>
-    </row>
-    <row r="49" spans="7:14">
+      <c r="O48" s="9"/>
+    </row>
+    <row r="49" spans="7:15">
       <c r="G49" s="4"/>
       <c r="K49" s="4"/>
       <c r="M49" s="4" t="str">
@@ -1694,8 +1736,9 @@
         <v/>
       </c>
       <c r="N49" s="7"/>
-    </row>
-    <row r="50" spans="7:14">
+      <c r="O49" s="9"/>
+    </row>
+    <row r="50" spans="7:15">
       <c r="G50" s="4"/>
       <c r="K50" s="4"/>
       <c r="M50" s="4" t="str">
@@ -1703,8 +1746,9 @@
         <v/>
       </c>
       <c r="N50" s="7"/>
-    </row>
-    <row r="51" spans="7:14">
+      <c r="O50" s="9"/>
+    </row>
+    <row r="51" spans="7:15">
       <c r="G51" s="4"/>
       <c r="K51" s="4"/>
       <c r="M51" s="4" t="str">
@@ -1712,8 +1756,9 @@
         <v/>
       </c>
       <c r="N51" s="7"/>
-    </row>
-    <row r="52" spans="7:14">
+      <c r="O51" s="9"/>
+    </row>
+    <row r="52" spans="7:15">
       <c r="G52" s="4"/>
       <c r="K52" s="4"/>
       <c r="M52" s="4" t="str">
@@ -1721,8 +1766,9 @@
         <v/>
       </c>
       <c r="N52" s="7"/>
-    </row>
-    <row r="53" spans="7:14">
+      <c r="O52" s="9"/>
+    </row>
+    <row r="53" spans="7:15">
       <c r="G53" s="4"/>
       <c r="K53" s="4"/>
       <c r="M53" s="4" t="str">
@@ -1730,8 +1776,9 @@
         <v/>
       </c>
       <c r="N53" s="7"/>
-    </row>
-    <row r="54" spans="7:14">
+      <c r="O53" s="9"/>
+    </row>
+    <row r="54" spans="7:15">
       <c r="G54" s="4"/>
       <c r="K54" s="4"/>
       <c r="M54" s="4" t="str">
@@ -1739,8 +1786,9 @@
         <v/>
       </c>
       <c r="N54" s="7"/>
-    </row>
-    <row r="55" spans="7:14">
+      <c r="O54" s="9"/>
+    </row>
+    <row r="55" spans="7:15">
       <c r="G55" s="4"/>
       <c r="K55" s="4"/>
       <c r="M55" s="4" t="str">
@@ -1748,8 +1796,9 @@
         <v/>
       </c>
       <c r="N55" s="7"/>
-    </row>
-    <row r="56" spans="7:14">
+      <c r="O55" s="9"/>
+    </row>
+    <row r="56" spans="7:15">
       <c r="G56" s="4"/>
       <c r="K56" s="4"/>
       <c r="M56" s="4" t="str">
@@ -1757,8 +1806,9 @@
         <v/>
       </c>
       <c r="N56" s="7"/>
-    </row>
-    <row r="57" spans="7:14">
+      <c r="O56" s="9"/>
+    </row>
+    <row r="57" spans="7:15">
       <c r="G57" s="4"/>
       <c r="K57" s="4"/>
       <c r="M57" s="4" t="str">
@@ -1766,8 +1816,9 @@
         <v/>
       </c>
       <c r="N57" s="7"/>
-    </row>
-    <row r="58" spans="7:14">
+      <c r="O57" s="9"/>
+    </row>
+    <row r="58" spans="7:15">
       <c r="G58" s="4"/>
       <c r="K58" s="4"/>
       <c r="M58" s="4" t="str">
@@ -1775,8 +1826,9 @@
         <v/>
       </c>
       <c r="N58" s="7"/>
-    </row>
-    <row r="59" spans="7:14">
+      <c r="O58" s="9"/>
+    </row>
+    <row r="59" spans="7:15">
       <c r="G59" s="4"/>
       <c r="K59" s="4"/>
       <c r="M59" s="4" t="str">
@@ -1784,8 +1836,9 @@
         <v/>
       </c>
       <c r="N59" s="7"/>
-    </row>
-    <row r="60" spans="7:14">
+      <c r="O59" s="9"/>
+    </row>
+    <row r="60" spans="7:15">
       <c r="G60" s="4"/>
       <c r="K60" s="4"/>
       <c r="M60" s="4" t="str">
@@ -1793,8 +1846,9 @@
         <v/>
       </c>
       <c r="N60" s="7"/>
-    </row>
-    <row r="61" spans="7:14">
+      <c r="O60" s="9"/>
+    </row>
+    <row r="61" spans="7:15">
       <c r="G61" s="4"/>
       <c r="K61" s="4"/>
       <c r="M61" s="4" t="str">
@@ -1802,8 +1856,9 @@
         <v/>
       </c>
       <c r="N61" s="7"/>
-    </row>
-    <row r="62" spans="7:14">
+      <c r="O61" s="9"/>
+    </row>
+    <row r="62" spans="7:15">
       <c r="G62" s="4"/>
       <c r="K62" s="4"/>
       <c r="M62" s="4" t="str">
@@ -1811,8 +1866,9 @@
         <v/>
       </c>
       <c r="N62" s="7"/>
-    </row>
-    <row r="63" spans="7:14">
+      <c r="O62" s="9"/>
+    </row>
+    <row r="63" spans="7:15">
       <c r="G63" s="4"/>
       <c r="K63" s="4"/>
       <c r="M63" s="4" t="str">
@@ -1820,8 +1876,9 @@
         <v/>
       </c>
       <c r="N63" s="7"/>
-    </row>
-    <row r="64" spans="7:14">
+      <c r="O63" s="9"/>
+    </row>
+    <row r="64" spans="7:15">
       <c r="G64" s="4"/>
       <c r="K64" s="4"/>
       <c r="M64" s="4" t="str">
@@ -1829,8 +1886,9 @@
         <v/>
       </c>
       <c r="N64" s="7"/>
-    </row>
-    <row r="65" spans="7:14">
+      <c r="O64" s="9"/>
+    </row>
+    <row r="65" spans="7:15">
       <c r="G65" s="4"/>
       <c r="K65" s="4"/>
       <c r="M65" s="4" t="str">
@@ -1838,8 +1896,9 @@
         <v/>
       </c>
       <c r="N65" s="7"/>
-    </row>
-    <row r="66" spans="7:14">
+      <c r="O65" s="9"/>
+    </row>
+    <row r="66" spans="7:15">
       <c r="G66" s="4"/>
       <c r="K66" s="4"/>
       <c r="M66" s="4" t="str">
@@ -1847,8 +1906,9 @@
         <v/>
       </c>
       <c r="N66" s="7"/>
-    </row>
-    <row r="67" spans="7:14">
+      <c r="O66" s="9"/>
+    </row>
+    <row r="67" spans="7:15">
       <c r="G67" s="4"/>
       <c r="K67" s="4"/>
       <c r="M67" s="4" t="str">
@@ -1856,8 +1916,9 @@
         <v/>
       </c>
       <c r="N67" s="7"/>
-    </row>
-    <row r="68" spans="7:14">
+      <c r="O67" s="9"/>
+    </row>
+    <row r="68" spans="7:15">
       <c r="G68" s="4"/>
       <c r="K68" s="4"/>
       <c r="M68" s="4" t="str">
@@ -1865,8 +1926,9 @@
         <v/>
       </c>
       <c r="N68" s="7"/>
-    </row>
-    <row r="69" spans="7:14">
+      <c r="O68" s="9"/>
+    </row>
+    <row r="69" spans="7:15">
       <c r="G69" s="4"/>
       <c r="K69" s="4"/>
       <c r="M69" s="4" t="str">
@@ -1874,8 +1936,9 @@
         <v/>
       </c>
       <c r="N69" s="7"/>
-    </row>
-    <row r="70" spans="7:14">
+      <c r="O69" s="9"/>
+    </row>
+    <row r="70" spans="7:15">
       <c r="G70" s="4"/>
       <c r="K70" s="4"/>
       <c r="M70" s="4" t="str">
@@ -1883,8 +1946,9 @@
         <v/>
       </c>
       <c r="N70" s="7"/>
-    </row>
-    <row r="71" spans="7:14">
+      <c r="O70" s="9"/>
+    </row>
+    <row r="71" spans="7:15">
       <c r="G71" s="4"/>
       <c r="K71" s="4"/>
       <c r="M71" s="4" t="str">
@@ -1892,8 +1956,9 @@
         <v/>
       </c>
       <c r="N71" s="7"/>
-    </row>
-    <row r="72" spans="7:14">
+      <c r="O71" s="9"/>
+    </row>
+    <row r="72" spans="7:15">
       <c r="G72" s="4"/>
       <c r="K72" s="4"/>
       <c r="M72" s="4" t="str">
@@ -1901,8 +1966,9 @@
         <v/>
       </c>
       <c r="N72" s="7"/>
-    </row>
-    <row r="73" spans="7:14">
+      <c r="O72" s="9"/>
+    </row>
+    <row r="73" spans="7:15">
       <c r="G73" s="4"/>
       <c r="K73" s="4"/>
       <c r="M73" s="4" t="str">
@@ -1910,8 +1976,9 @@
         <v/>
       </c>
       <c r="N73" s="7"/>
-    </row>
-    <row r="74" spans="7:14">
+      <c r="O73" s="9"/>
+    </row>
+    <row r="74" spans="7:15">
       <c r="G74" s="4"/>
       <c r="K74" s="4"/>
       <c r="M74" s="4" t="str">
@@ -1919,8 +1986,9 @@
         <v/>
       </c>
       <c r="N74" s="7"/>
-    </row>
-    <row r="75" spans="7:14">
+      <c r="O74" s="9"/>
+    </row>
+    <row r="75" spans="7:15">
       <c r="G75" s="4"/>
       <c r="K75" s="4"/>
       <c r="M75" s="4" t="str">
@@ -1928,8 +1996,9 @@
         <v/>
       </c>
       <c r="N75" s="7"/>
-    </row>
-    <row r="76" spans="7:14">
+      <c r="O75" s="9"/>
+    </row>
+    <row r="76" spans="7:15">
       <c r="G76" s="4"/>
       <c r="K76" s="4"/>
       <c r="M76" s="4" t="str">
@@ -1937,8 +2006,9 @@
         <v/>
       </c>
       <c r="N76" s="7"/>
-    </row>
-    <row r="77" spans="7:14">
+      <c r="O76" s="9"/>
+    </row>
+    <row r="77" spans="7:15">
       <c r="G77" s="4"/>
       <c r="K77" s="4"/>
       <c r="M77" s="4" t="str">
@@ -1946,8 +2016,9 @@
         <v/>
       </c>
       <c r="N77" s="7"/>
-    </row>
-    <row r="78" spans="7:14">
+      <c r="O77" s="9"/>
+    </row>
+    <row r="78" spans="7:15">
       <c r="G78" s="4"/>
       <c r="K78" s="4"/>
       <c r="M78" s="4" t="str">
@@ -1955,8 +2026,9 @@
         <v/>
       </c>
       <c r="N78" s="7"/>
-    </row>
-    <row r="79" spans="7:14">
+      <c r="O78" s="9"/>
+    </row>
+    <row r="79" spans="7:15">
       <c r="G79" s="4"/>
       <c r="K79" s="4"/>
       <c r="M79" s="4" t="str">
@@ -1964,8 +2036,9 @@
         <v/>
       </c>
       <c r="N79" s="7"/>
-    </row>
-    <row r="80" spans="7:14">
+      <c r="O79" s="9"/>
+    </row>
+    <row r="80" spans="7:15">
       <c r="G80" s="4"/>
       <c r="K80" s="4"/>
       <c r="M80" s="4" t="str">
@@ -1973,8 +2046,9 @@
         <v/>
       </c>
       <c r="N80" s="7"/>
-    </row>
-    <row r="81" spans="7:14">
+      <c r="O80" s="9"/>
+    </row>
+    <row r="81" spans="7:15">
       <c r="G81" s="4"/>
       <c r="K81" s="4"/>
       <c r="M81" s="4" t="str">
@@ -1982,8 +2056,9 @@
         <v/>
       </c>
       <c r="N81" s="7"/>
-    </row>
-    <row r="82" spans="7:14">
+      <c r="O81" s="9"/>
+    </row>
+    <row r="82" spans="7:15">
       <c r="G82" s="4"/>
       <c r="K82" s="4"/>
       <c r="M82" s="4" t="str">
@@ -1991,8 +2066,9 @@
         <v/>
       </c>
       <c r="N82" s="7"/>
-    </row>
-    <row r="83" spans="7:14">
+      <c r="O82" s="9"/>
+    </row>
+    <row r="83" spans="7:15">
       <c r="G83" s="4"/>
       <c r="K83" s="4"/>
       <c r="M83" s="4" t="str">
@@ -2000,8 +2076,9 @@
         <v/>
       </c>
       <c r="N83" s="7"/>
-    </row>
-    <row r="84" spans="7:14">
+      <c r="O83" s="9"/>
+    </row>
+    <row r="84" spans="7:15">
       <c r="G84" s="4"/>
       <c r="K84" s="4"/>
       <c r="M84" s="4" t="str">
@@ -2009,8 +2086,9 @@
         <v/>
       </c>
       <c r="N84" s="7"/>
-    </row>
-    <row r="85" spans="7:14">
+      <c r="O84" s="9"/>
+    </row>
+    <row r="85" spans="7:15">
       <c r="G85" s="4"/>
       <c r="K85" s="4"/>
       <c r="M85" s="4" t="str">
@@ -2018,8 +2096,9 @@
         <v/>
       </c>
       <c r="N85" s="7"/>
-    </row>
-    <row r="86" spans="7:14">
+      <c r="O85" s="9"/>
+    </row>
+    <row r="86" spans="7:15">
       <c r="G86" s="4"/>
       <c r="K86" s="4"/>
       <c r="M86" s="4" t="str">
@@ -2027,8 +2106,9 @@
         <v/>
       </c>
       <c r="N86" s="7"/>
-    </row>
-    <row r="87" spans="7:14">
+      <c r="O86" s="9"/>
+    </row>
+    <row r="87" spans="7:15">
       <c r="G87" s="4"/>
       <c r="K87" s="4"/>
       <c r="M87" s="4" t="str">
@@ -2036,8 +2116,9 @@
         <v/>
       </c>
       <c r="N87" s="7"/>
-    </row>
-    <row r="88" spans="7:14">
+      <c r="O87" s="9"/>
+    </row>
+    <row r="88" spans="7:15">
       <c r="G88" s="4"/>
       <c r="K88" s="4"/>
       <c r="M88" s="4" t="str">
@@ -2045,8 +2126,9 @@
         <v/>
       </c>
       <c r="N88" s="7"/>
-    </row>
-    <row r="89" spans="7:14">
+      <c r="O88" s="9"/>
+    </row>
+    <row r="89" spans="7:15">
       <c r="G89" s="4"/>
       <c r="K89" s="4"/>
       <c r="M89" s="4" t="str">
@@ -2054,8 +2136,9 @@
         <v/>
       </c>
       <c r="N89" s="7"/>
-    </row>
-    <row r="90" spans="7:14">
+      <c r="O89" s="9"/>
+    </row>
+    <row r="90" spans="7:15">
       <c r="G90" s="4"/>
       <c r="K90" s="4"/>
       <c r="M90" s="4" t="str">
@@ -2063,8 +2146,9 @@
         <v/>
       </c>
       <c r="N90" s="7"/>
-    </row>
-    <row r="91" spans="7:14">
+      <c r="O90" s="9"/>
+    </row>
+    <row r="91" spans="7:15">
       <c r="G91" s="4"/>
       <c r="K91" s="4"/>
       <c r="M91" s="4" t="str">
@@ -2072,8 +2156,9 @@
         <v/>
       </c>
       <c r="N91" s="7"/>
-    </row>
-    <row r="92" spans="7:14">
+      <c r="O91" s="9"/>
+    </row>
+    <row r="92" spans="7:15">
       <c r="G92" s="4"/>
       <c r="K92" s="4"/>
       <c r="M92" s="4" t="str">
@@ -2081,8 +2166,9 @@
         <v/>
       </c>
       <c r="N92" s="7"/>
-    </row>
-    <row r="93" spans="7:14">
+      <c r="O92" s="9"/>
+    </row>
+    <row r="93" spans="7:15">
       <c r="G93" s="4"/>
       <c r="K93" s="4"/>
       <c r="M93" s="4" t="str">
@@ -2090,8 +2176,9 @@
         <v/>
       </c>
       <c r="N93" s="7"/>
-    </row>
-    <row r="94" spans="7:14">
+      <c r="O93" s="9"/>
+    </row>
+    <row r="94" spans="7:15">
       <c r="G94" s="4"/>
       <c r="K94" s="4"/>
       <c r="M94" s="4" t="str">
@@ -2099,8 +2186,9 @@
         <v/>
       </c>
       <c r="N94" s="7"/>
-    </row>
-    <row r="95" spans="7:14">
+      <c r="O94" s="9"/>
+    </row>
+    <row r="95" spans="7:15">
       <c r="G95" s="4"/>
       <c r="K95" s="4"/>
       <c r="M95" s="4" t="str">
@@ -2108,8 +2196,9 @@
         <v/>
       </c>
       <c r="N95" s="7"/>
-    </row>
-    <row r="96" spans="7:14">
+      <c r="O95" s="9"/>
+    </row>
+    <row r="96" spans="7:15">
       <c r="G96" s="4"/>
       <c r="K96" s="4"/>
       <c r="M96" s="4" t="str">
@@ -2117,8 +2206,9 @@
         <v/>
       </c>
       <c r="N96" s="7"/>
-    </row>
-    <row r="97" spans="7:14">
+      <c r="O96" s="9"/>
+    </row>
+    <row r="97" spans="7:15">
       <c r="G97" s="4"/>
       <c r="K97" s="4"/>
       <c r="M97" s="4" t="str">
@@ -2126,8 +2216,9 @@
         <v/>
       </c>
       <c r="N97" s="7"/>
-    </row>
-    <row r="98" spans="7:14">
+      <c r="O97" s="9"/>
+    </row>
+    <row r="98" spans="7:15">
       <c r="G98" s="4"/>
       <c r="K98" s="4"/>
       <c r="M98" s="4" t="str">
@@ -2135,8 +2226,9 @@
         <v/>
       </c>
       <c r="N98" s="7"/>
-    </row>
-    <row r="99" spans="7:14">
+      <c r="O98" s="9"/>
+    </row>
+    <row r="99" spans="7:15">
       <c r="G99" s="4"/>
       <c r="K99" s="4"/>
       <c r="M99" s="4" t="str">
@@ -2144,8 +2236,9 @@
         <v/>
       </c>
       <c r="N99" s="7"/>
-    </row>
-    <row r="100" spans="7:14">
+      <c r="O99" s="9"/>
+    </row>
+    <row r="100" spans="7:15">
       <c r="G100" s="4"/>
       <c r="K100" s="4"/>
       <c r="M100" s="4" t="str">
@@ -2153,8 +2246,9 @@
         <v/>
       </c>
       <c r="N100" s="7"/>
-    </row>
-    <row r="101" spans="7:14">
+      <c r="O100" s="9"/>
+    </row>
+    <row r="101" spans="7:15">
       <c r="G101" s="4"/>
       <c r="K101" s="4"/>
       <c r="M101" s="4" t="str">
@@ -2162,8 +2256,9 @@
         <v/>
       </c>
       <c r="N101" s="7"/>
-    </row>
-    <row r="102" spans="7:14">
+      <c r="O101" s="9"/>
+    </row>
+    <row r="102" spans="7:15">
       <c r="G102" s="4"/>
       <c r="K102" s="4"/>
       <c r="M102" s="4" t="str">
@@ -2171,8 +2266,9 @@
         <v/>
       </c>
       <c r="N102" s="7"/>
-    </row>
-    <row r="103" spans="7:14">
+      <c r="O102" s="9"/>
+    </row>
+    <row r="103" spans="7:15">
       <c r="G103" s="4"/>
       <c r="K103" s="4"/>
       <c r="M103" s="4" t="str">
@@ -2180,8 +2276,9 @@
         <v/>
       </c>
       <c r="N103" s="7"/>
-    </row>
-    <row r="104" spans="7:14">
+      <c r="O103" s="9"/>
+    </row>
+    <row r="104" spans="7:15">
       <c r="G104" s="4"/>
       <c r="K104" s="4"/>
       <c r="M104" s="4" t="str">
@@ -2189,8 +2286,9 @@
         <v/>
       </c>
       <c r="N104" s="7"/>
-    </row>
-    <row r="105" spans="7:14">
+      <c r="O104" s="9"/>
+    </row>
+    <row r="105" spans="7:15">
       <c r="G105" s="4"/>
       <c r="K105" s="4"/>
       <c r="M105" s="4" t="str">
@@ -2198,8 +2296,9 @@
         <v/>
       </c>
       <c r="N105" s="7"/>
-    </row>
-    <row r="106" spans="7:14">
+      <c r="O105" s="9"/>
+    </row>
+    <row r="106" spans="7:15">
       <c r="G106" s="4"/>
       <c r="K106" s="4"/>
       <c r="M106" s="4" t="str">
@@ -2207,8 +2306,9 @@
         <v/>
       </c>
       <c r="N106" s="7"/>
-    </row>
-    <row r="107" spans="7:14">
+      <c r="O106" s="9"/>
+    </row>
+    <row r="107" spans="7:15">
       <c r="G107" s="4"/>
       <c r="K107" s="4"/>
       <c r="M107" s="4" t="str">
@@ -2216,8 +2316,9 @@
         <v/>
       </c>
       <c r="N107" s="7"/>
-    </row>
-    <row r="108" spans="7:14">
+      <c r="O107" s="9"/>
+    </row>
+    <row r="108" spans="7:15">
       <c r="G108" s="4"/>
       <c r="K108" s="4"/>
       <c r="M108" s="4" t="str">
@@ -2225,8 +2326,9 @@
         <v/>
       </c>
       <c r="N108" s="7"/>
-    </row>
-    <row r="109" spans="7:14">
+      <c r="O108" s="9"/>
+    </row>
+    <row r="109" spans="7:15">
       <c r="G109" s="4"/>
       <c r="K109" s="4"/>
       <c r="M109" s="4" t="str">
@@ -2234,8 +2336,9 @@
         <v/>
       </c>
       <c r="N109" s="7"/>
-    </row>
-    <row r="110" spans="7:14">
+      <c r="O109" s="9"/>
+    </row>
+    <row r="110" spans="7:15">
       <c r="G110" s="4"/>
       <c r="K110" s="4"/>
       <c r="M110" s="4" t="str">
@@ -2243,8 +2346,9 @@
         <v/>
       </c>
       <c r="N110" s="7"/>
-    </row>
-    <row r="111" spans="7:14">
+      <c r="O110" s="9"/>
+    </row>
+    <row r="111" spans="7:15">
       <c r="G111" s="4"/>
       <c r="K111" s="4"/>
       <c r="M111" s="4" t="str">
@@ -2252,8 +2356,9 @@
         <v/>
       </c>
       <c r="N111" s="7"/>
-    </row>
-    <row r="112" spans="7:14">
+      <c r="O111" s="9"/>
+    </row>
+    <row r="112" spans="7:15">
       <c r="G112" s="4"/>
       <c r="K112" s="4"/>
       <c r="M112" s="4" t="str">
@@ -2261,8 +2366,9 @@
         <v/>
       </c>
       <c r="N112" s="7"/>
-    </row>
-    <row r="113" spans="7:14">
+      <c r="O112" s="9"/>
+    </row>
+    <row r="113" spans="7:15">
       <c r="G113" s="4"/>
       <c r="K113" s="4"/>
       <c r="M113" s="4" t="str">
@@ -2270,8 +2376,9 @@
         <v/>
       </c>
       <c r="N113" s="7"/>
-    </row>
-    <row r="114" spans="7:14">
+      <c r="O113" s="9"/>
+    </row>
+    <row r="114" spans="7:15">
       <c r="G114" s="4"/>
       <c r="K114" s="4"/>
       <c r="M114" s="4" t="str">
@@ -2279,8 +2386,9 @@
         <v/>
       </c>
       <c r="N114" s="7"/>
-    </row>
-    <row r="115" spans="7:14">
+      <c r="O114" s="9"/>
+    </row>
+    <row r="115" spans="7:15">
       <c r="G115" s="4"/>
       <c r="K115" s="4"/>
       <c r="M115" s="4" t="str">
@@ -2288,8 +2396,9 @@
         <v/>
       </c>
       <c r="N115" s="7"/>
-    </row>
-    <row r="116" spans="7:14">
+      <c r="O115" s="9"/>
+    </row>
+    <row r="116" spans="7:15">
       <c r="G116" s="4"/>
       <c r="K116" s="4"/>
       <c r="M116" s="4" t="str">
@@ -2297,8 +2406,9 @@
         <v/>
       </c>
       <c r="N116" s="7"/>
-    </row>
-    <row r="117" spans="7:14">
+      <c r="O116" s="9"/>
+    </row>
+    <row r="117" spans="7:15">
       <c r="G117" s="4"/>
       <c r="K117" s="4"/>
       <c r="M117" s="4" t="str">
@@ -2306,8 +2416,9 @@
         <v/>
       </c>
       <c r="N117" s="7"/>
-    </row>
-    <row r="118" spans="7:14">
+      <c r="O117" s="9"/>
+    </row>
+    <row r="118" spans="7:15">
       <c r="G118" s="4"/>
       <c r="K118" s="4"/>
       <c r="M118" s="4" t="str">
@@ -2315,8 +2426,9 @@
         <v/>
       </c>
       <c r="N118" s="7"/>
-    </row>
-    <row r="119" spans="7:14">
+      <c r="O118" s="9"/>
+    </row>
+    <row r="119" spans="7:15">
       <c r="G119" s="4"/>
       <c r="K119" s="4"/>
       <c r="M119" s="4" t="str">
@@ -2324,8 +2436,9 @@
         <v/>
       </c>
       <c r="N119" s="7"/>
-    </row>
-    <row r="120" spans="7:14">
+      <c r="O119" s="9"/>
+    </row>
+    <row r="120" spans="7:15">
       <c r="G120" s="4"/>
       <c r="K120" s="4"/>
       <c r="M120" s="4" t="str">
@@ -2333,8 +2446,9 @@
         <v/>
       </c>
       <c r="N120" s="7"/>
-    </row>
-    <row r="121" spans="7:14">
+      <c r="O120" s="9"/>
+    </row>
+    <row r="121" spans="7:15">
       <c r="G121" s="4"/>
       <c r="K121" s="4"/>
       <c r="M121" s="4" t="str">
@@ -2342,8 +2456,9 @@
         <v/>
       </c>
       <c r="N121" s="7"/>
-    </row>
-    <row r="122" spans="7:14">
+      <c r="O121" s="9"/>
+    </row>
+    <row r="122" spans="7:15">
       <c r="G122" s="4"/>
       <c r="K122" s="4"/>
       <c r="M122" s="4" t="str">
@@ -2351,8 +2466,9 @@
         <v/>
       </c>
       <c r="N122" s="7"/>
-    </row>
-    <row r="123" spans="7:14">
+      <c r="O122" s="9"/>
+    </row>
+    <row r="123" spans="7:15">
       <c r="G123" s="4"/>
       <c r="K123" s="4"/>
       <c r="M123" s="4" t="str">
@@ -2360,8 +2476,9 @@
         <v/>
       </c>
       <c r="N123" s="7"/>
-    </row>
-    <row r="124" spans="7:14">
+      <c r="O123" s="9"/>
+    </row>
+    <row r="124" spans="7:15">
       <c r="G124" s="4"/>
       <c r="K124" s="4"/>
       <c r="M124" s="4" t="str">
@@ -2369,8 +2486,9 @@
         <v/>
       </c>
       <c r="N124" s="7"/>
-    </row>
-    <row r="125" spans="7:14">
+      <c r="O124" s="9"/>
+    </row>
+    <row r="125" spans="7:15">
       <c r="G125" s="4"/>
       <c r="K125" s="4"/>
       <c r="M125" s="4" t="str">
@@ -2378,8 +2496,9 @@
         <v/>
       </c>
       <c r="N125" s="7"/>
-    </row>
-    <row r="126" spans="7:14">
+      <c r="O125" s="9"/>
+    </row>
+    <row r="126" spans="7:15">
       <c r="G126" s="4"/>
       <c r="K126" s="4"/>
       <c r="M126" s="4" t="str">
@@ -2387,8 +2506,9 @@
         <v/>
       </c>
       <c r="N126" s="7"/>
-    </row>
-    <row r="127" spans="7:14">
+      <c r="O126" s="9"/>
+    </row>
+    <row r="127" spans="7:15">
       <c r="G127" s="4"/>
       <c r="K127" s="4"/>
       <c r="M127" s="4" t="str">
@@ -2396,8 +2516,9 @@
         <v/>
       </c>
       <c r="N127" s="7"/>
-    </row>
-    <row r="128" spans="7:14">
+      <c r="O127" s="9"/>
+    </row>
+    <row r="128" spans="7:15">
       <c r="G128" s="4"/>
       <c r="K128" s="4"/>
       <c r="M128" s="4" t="str">
@@ -2405,8 +2526,9 @@
         <v/>
       </c>
       <c r="N128" s="7"/>
-    </row>
-    <row r="129" spans="7:14">
+      <c r="O128" s="9"/>
+    </row>
+    <row r="129" spans="7:15">
       <c r="G129" s="4"/>
       <c r="K129" s="4"/>
       <c r="M129" s="4" t="str">
@@ -2414,8 +2536,9 @@
         <v/>
       </c>
       <c r="N129" s="7"/>
-    </row>
-    <row r="130" spans="7:14">
+      <c r="O129" s="9"/>
+    </row>
+    <row r="130" spans="7:15">
       <c r="G130" s="4"/>
       <c r="K130" s="4"/>
       <c r="M130" s="4" t="str">
@@ -2423,8 +2546,9 @@
         <v/>
       </c>
       <c r="N130" s="7"/>
-    </row>
-    <row r="131" spans="7:14">
+      <c r="O130" s="9"/>
+    </row>
+    <row r="131" spans="7:15">
       <c r="G131" s="4"/>
       <c r="K131" s="4"/>
       <c r="M131" s="4" t="str">
@@ -2432,8 +2556,9 @@
         <v/>
       </c>
       <c r="N131" s="7"/>
-    </row>
-    <row r="132" spans="7:14">
+      <c r="O131" s="9"/>
+    </row>
+    <row r="132" spans="7:15">
       <c r="G132" s="4"/>
       <c r="K132" s="4"/>
       <c r="M132" s="4" t="str">
@@ -2441,8 +2566,9 @@
         <v/>
       </c>
       <c r="N132" s="7"/>
-    </row>
-    <row r="133" spans="7:14">
+      <c r="O132" s="9"/>
+    </row>
+    <row r="133" spans="7:15">
       <c r="G133" s="4"/>
       <c r="K133" s="4"/>
       <c r="M133" s="4" t="str">
@@ -2450,8 +2576,9 @@
         <v/>
       </c>
       <c r="N133" s="7"/>
-    </row>
-    <row r="134" spans="7:14">
+      <c r="O133" s="9"/>
+    </row>
+    <row r="134" spans="7:15">
       <c r="G134" s="4"/>
       <c r="K134" s="4"/>
       <c r="M134" s="4" t="str">
@@ -2459,8 +2586,9 @@
         <v/>
       </c>
       <c r="N134" s="7"/>
-    </row>
-    <row r="135" spans="7:14">
+      <c r="O134" s="9"/>
+    </row>
+    <row r="135" spans="7:15">
       <c r="G135" s="4"/>
       <c r="K135" s="4"/>
       <c r="M135" s="4" t="str">
@@ -2468,8 +2596,9 @@
         <v/>
       </c>
       <c r="N135" s="7"/>
-    </row>
-    <row r="136" spans="7:14">
+      <c r="O135" s="9"/>
+    </row>
+    <row r="136" spans="7:15">
       <c r="G136" s="4"/>
       <c r="K136" s="4"/>
       <c r="M136" s="4" t="str">
@@ -2477,8 +2606,9 @@
         <v/>
       </c>
       <c r="N136" s="7"/>
-    </row>
-    <row r="137" spans="7:14">
+      <c r="O136" s="9"/>
+    </row>
+    <row r="137" spans="7:15">
       <c r="G137" s="4"/>
       <c r="K137" s="4"/>
       <c r="M137" s="4" t="str">
@@ -2486,8 +2616,9 @@
         <v/>
       </c>
       <c r="N137" s="7"/>
-    </row>
-    <row r="138" spans="7:14">
+      <c r="O137" s="9"/>
+    </row>
+    <row r="138" spans="7:15">
       <c r="G138" s="4"/>
       <c r="K138" s="4"/>
       <c r="M138" s="4" t="str">
@@ -2495,8 +2626,9 @@
         <v/>
       </c>
       <c r="N138" s="7"/>
-    </row>
-    <row r="139" spans="7:14">
+      <c r="O138" s="9"/>
+    </row>
+    <row r="139" spans="7:15">
       <c r="G139" s="4"/>
       <c r="K139" s="4"/>
       <c r="M139" s="4" t="str">
@@ -2504,8 +2636,9 @@
         <v/>
       </c>
       <c r="N139" s="7"/>
-    </row>
-    <row r="140" spans="7:14">
+      <c r="O139" s="9"/>
+    </row>
+    <row r="140" spans="7:15">
       <c r="G140" s="4"/>
       <c r="K140" s="4"/>
       <c r="M140" s="4" t="str">
@@ -2513,8 +2646,9 @@
         <v/>
       </c>
       <c r="N140" s="7"/>
-    </row>
-    <row r="141" spans="7:14">
+      <c r="O140" s="9"/>
+    </row>
+    <row r="141" spans="7:15">
       <c r="G141" s="4"/>
       <c r="K141" s="4"/>
       <c r="M141" s="4" t="str">
@@ -2522,8 +2656,9 @@
         <v/>
       </c>
       <c r="N141" s="7"/>
-    </row>
-    <row r="142" spans="7:14">
+      <c r="O141" s="9"/>
+    </row>
+    <row r="142" spans="7:15">
       <c r="G142" s="4"/>
       <c r="K142" s="4"/>
       <c r="M142" s="4" t="str">
@@ -2531,8 +2666,9 @@
         <v/>
       </c>
       <c r="N142" s="7"/>
-    </row>
-    <row r="143" spans="7:14">
+      <c r="O142" s="9"/>
+    </row>
+    <row r="143" spans="7:15">
       <c r="G143" s="4"/>
       <c r="K143" s="4"/>
       <c r="M143" s="4" t="str">
@@ -2540,8 +2676,9 @@
         <v/>
       </c>
       <c r="N143" s="7"/>
-    </row>
-    <row r="144" spans="7:14">
+      <c r="O143" s="9"/>
+    </row>
+    <row r="144" spans="7:15">
       <c r="G144" s="4"/>
       <c r="K144" s="4"/>
       <c r="M144" s="4" t="str">
@@ -2549,8 +2686,9 @@
         <v/>
       </c>
       <c r="N144" s="7"/>
-    </row>
-    <row r="145" spans="7:14">
+      <c r="O144" s="9"/>
+    </row>
+    <row r="145" spans="7:15">
       <c r="G145" s="4"/>
       <c r="K145" s="4"/>
       <c r="M145" s="4" t="str">
@@ -2558,8 +2696,9 @@
         <v/>
       </c>
       <c r="N145" s="7"/>
-    </row>
-    <row r="146" spans="7:14">
+      <c r="O145" s="9"/>
+    </row>
+    <row r="146" spans="7:15">
       <c r="G146" s="4"/>
       <c r="K146" s="4"/>
       <c r="M146" s="4" t="str">
@@ -2567,8 +2706,9 @@
         <v/>
       </c>
       <c r="N146" s="7"/>
-    </row>
-    <row r="147" spans="7:14">
+      <c r="O146" s="9"/>
+    </row>
+    <row r="147" spans="7:15">
       <c r="G147" s="4"/>
       <c r="K147" s="4"/>
       <c r="M147" s="4" t="str">
@@ -2576,8 +2716,9 @@
         <v/>
       </c>
       <c r="N147" s="7"/>
-    </row>
-    <row r="148" spans="7:14">
+      <c r="O147" s="9"/>
+    </row>
+    <row r="148" spans="7:15">
       <c r="G148" s="4"/>
       <c r="K148" s="4"/>
       <c r="M148" s="4" t="str">
@@ -2585,8 +2726,9 @@
         <v/>
       </c>
       <c r="N148" s="7"/>
-    </row>
-    <row r="149" spans="7:14">
+      <c r="O148" s="9"/>
+    </row>
+    <row r="149" spans="7:15">
       <c r="G149" s="4"/>
       <c r="K149" s="4"/>
       <c r="M149" s="4" t="str">
@@ -2594,8 +2736,9 @@
         <v/>
       </c>
       <c r="N149" s="7"/>
-    </row>
-    <row r="150" spans="7:14">
+      <c r="O149" s="9"/>
+    </row>
+    <row r="150" spans="7:15">
       <c r="G150" s="4"/>
       <c r="K150" s="4"/>
       <c r="M150" s="4" t="str">
@@ -2603,8 +2746,9 @@
         <v/>
       </c>
       <c r="N150" s="7"/>
-    </row>
-    <row r="151" spans="7:14">
+      <c r="O150" s="9"/>
+    </row>
+    <row r="151" spans="7:15">
       <c r="G151" s="4"/>
       <c r="K151" s="4"/>
       <c r="M151" s="4" t="str">
@@ -2612,8 +2756,9 @@
         <v/>
       </c>
       <c r="N151" s="7"/>
-    </row>
-    <row r="152" spans="7:14">
+      <c r="O151" s="9"/>
+    </row>
+    <row r="152" spans="7:15">
       <c r="G152" s="4"/>
       <c r="K152" s="4"/>
       <c r="M152" s="4" t="str">
@@ -2621,8 +2766,9 @@
         <v/>
       </c>
       <c r="N152" s="7"/>
-    </row>
-    <row r="153" spans="7:14">
+      <c r="O152" s="9"/>
+    </row>
+    <row r="153" spans="7:15">
       <c r="G153" s="4"/>
       <c r="K153" s="4"/>
       <c r="M153" s="4" t="str">
@@ -2630,8 +2776,9 @@
         <v/>
       </c>
       <c r="N153" s="7"/>
-    </row>
-    <row r="154" spans="7:14">
+      <c r="O153" s="9"/>
+    </row>
+    <row r="154" spans="7:15">
       <c r="G154" s="4"/>
       <c r="K154" s="4"/>
       <c r="M154" s="4" t="str">
@@ -2639,8 +2786,9 @@
         <v/>
       </c>
       <c r="N154" s="7"/>
-    </row>
-    <row r="155" spans="7:14">
+      <c r="O154" s="9"/>
+    </row>
+    <row r="155" spans="7:15">
       <c r="G155" s="4"/>
       <c r="K155" s="4"/>
       <c r="M155" s="4" t="str">
@@ -2648,8 +2796,9 @@
         <v/>
       </c>
       <c r="N155" s="7"/>
-    </row>
-    <row r="156" spans="7:14">
+      <c r="O155" s="9"/>
+    </row>
+    <row r="156" spans="7:15">
       <c r="G156" s="4"/>
       <c r="K156" s="4"/>
       <c r="M156" s="4" t="str">
@@ -2657,8 +2806,9 @@
         <v/>
       </c>
       <c r="N156" s="7"/>
-    </row>
-    <row r="157" spans="7:14">
+      <c r="O156" s="9"/>
+    </row>
+    <row r="157" spans="7:15">
       <c r="G157" s="4"/>
       <c r="K157" s="4"/>
       <c r="M157" s="4" t="str">
@@ -2666,8 +2816,9 @@
         <v/>
       </c>
       <c r="N157" s="7"/>
-    </row>
-    <row r="158" spans="7:14">
+      <c r="O157" s="9"/>
+    </row>
+    <row r="158" spans="7:15">
       <c r="G158" s="4"/>
       <c r="K158" s="4"/>
       <c r="M158" s="4" t="str">
@@ -2675,8 +2826,9 @@
         <v/>
       </c>
       <c r="N158" s="7"/>
-    </row>
-    <row r="159" spans="7:14">
+      <c r="O158" s="9"/>
+    </row>
+    <row r="159" spans="7:15">
       <c r="G159" s="4"/>
       <c r="K159" s="4"/>
       <c r="M159" s="4" t="str">
@@ -2684,8 +2836,9 @@
         <v/>
       </c>
       <c r="N159" s="7"/>
-    </row>
-    <row r="160" spans="7:14">
+      <c r="O159" s="9"/>
+    </row>
+    <row r="160" spans="7:15">
       <c r="G160" s="4"/>
       <c r="K160" s="4"/>
       <c r="M160" s="4" t="str">
@@ -2693,8 +2846,9 @@
         <v/>
       </c>
       <c r="N160" s="7"/>
-    </row>
-    <row r="161" spans="7:14">
+      <c r="O160" s="9"/>
+    </row>
+    <row r="161" spans="7:15">
       <c r="G161" s="4"/>
       <c r="K161" s="4"/>
       <c r="M161" s="4" t="str">
@@ -2702,8 +2856,9 @@
         <v/>
       </c>
       <c r="N161" s="7"/>
-    </row>
-    <row r="162" spans="7:14">
+      <c r="O161" s="9"/>
+    </row>
+    <row r="162" spans="7:15">
       <c r="G162" s="4"/>
       <c r="K162" s="4"/>
       <c r="M162" s="4" t="str">
@@ -2711,8 +2866,9 @@
         <v/>
       </c>
       <c r="N162" s="7"/>
-    </row>
-    <row r="163" spans="7:14">
+      <c r="O162" s="9"/>
+    </row>
+    <row r="163" spans="7:15">
       <c r="G163" s="4"/>
       <c r="K163" s="4"/>
       <c r="M163" s="4" t="str">
@@ -2720,8 +2876,9 @@
         <v/>
       </c>
       <c r="N163" s="7"/>
-    </row>
-    <row r="164" spans="7:14">
+      <c r="O163" s="9"/>
+    </row>
+    <row r="164" spans="7:15">
       <c r="G164" s="4"/>
       <c r="K164" s="4"/>
       <c r="M164" s="4" t="str">
@@ -2729,8 +2886,9 @@
         <v/>
       </c>
       <c r="N164" s="7"/>
-    </row>
-    <row r="165" spans="7:14">
+      <c r="O164" s="9"/>
+    </row>
+    <row r="165" spans="7:15">
       <c r="G165" s="4"/>
       <c r="K165" s="4"/>
       <c r="M165" s="4" t="str">
@@ -2738,8 +2896,9 @@
         <v/>
       </c>
       <c r="N165" s="7"/>
-    </row>
-    <row r="166" spans="7:14">
+      <c r="O165" s="9"/>
+    </row>
+    <row r="166" spans="7:15">
       <c r="G166" s="4"/>
       <c r="K166" s="4"/>
       <c r="M166" s="4" t="str">
@@ -2747,8 +2906,9 @@
         <v/>
       </c>
       <c r="N166" s="7"/>
-    </row>
-    <row r="167" spans="7:14">
+      <c r="O166" s="9"/>
+    </row>
+    <row r="167" spans="7:15">
       <c r="G167" s="4"/>
       <c r="K167" s="4"/>
       <c r="M167" s="4" t="str">
@@ -2756,8 +2916,9 @@
         <v/>
       </c>
       <c r="N167" s="7"/>
-    </row>
-    <row r="168" spans="7:14">
+      <c r="O167" s="9"/>
+    </row>
+    <row r="168" spans="7:15">
       <c r="G168" s="4"/>
       <c r="K168" s="4"/>
       <c r="M168" s="4" t="str">
@@ -2765,8 +2926,9 @@
         <v/>
       </c>
       <c r="N168" s="7"/>
-    </row>
-    <row r="169" spans="7:14">
+      <c r="O168" s="9"/>
+    </row>
+    <row r="169" spans="7:15">
       <c r="G169" s="4"/>
       <c r="K169" s="4"/>
       <c r="M169" s="4" t="str">
@@ -2774,8 +2936,9 @@
         <v/>
       </c>
       <c r="N169" s="7"/>
-    </row>
-    <row r="170" spans="7:14">
+      <c r="O169" s="9"/>
+    </row>
+    <row r="170" spans="7:15">
       <c r="G170" s="4"/>
       <c r="K170" s="4"/>
       <c r="M170" s="4" t="str">
@@ -2783,8 +2946,9 @@
         <v/>
       </c>
       <c r="N170" s="7"/>
-    </row>
-    <row r="171" spans="7:14">
+      <c r="O170" s="9"/>
+    </row>
+    <row r="171" spans="7:15">
       <c r="G171" s="4"/>
       <c r="K171" s="4"/>
       <c r="M171" s="4" t="str">
@@ -2792,8 +2956,9 @@
         <v/>
       </c>
       <c r="N171" s="7"/>
-    </row>
-    <row r="172" spans="7:14">
+      <c r="O171" s="9"/>
+    </row>
+    <row r="172" spans="7:15">
       <c r="G172" s="4"/>
       <c r="K172" s="4"/>
       <c r="M172" s="4" t="str">
@@ -2801,8 +2966,9 @@
         <v/>
       </c>
       <c r="N172" s="7"/>
-    </row>
-    <row r="173" spans="7:14">
+      <c r="O172" s="9"/>
+    </row>
+    <row r="173" spans="7:15">
       <c r="G173" s="4"/>
       <c r="K173" s="4"/>
       <c r="M173" s="4" t="str">
@@ -2810,8 +2976,9 @@
         <v/>
       </c>
       <c r="N173" s="7"/>
-    </row>
-    <row r="174" spans="7:14">
+      <c r="O173" s="9"/>
+    </row>
+    <row r="174" spans="7:15">
       <c r="G174" s="4"/>
       <c r="K174" s="4"/>
       <c r="M174" s="4" t="str">
@@ -2819,8 +2986,9 @@
         <v/>
       </c>
       <c r="N174" s="7"/>
-    </row>
-    <row r="175" spans="7:14">
+      <c r="O174" s="9"/>
+    </row>
+    <row r="175" spans="7:15">
       <c r="G175" s="4"/>
       <c r="K175" s="4"/>
       <c r="M175" s="4" t="str">
@@ -2828,8 +2996,9 @@
         <v/>
       </c>
       <c r="N175" s="7"/>
-    </row>
-    <row r="176" spans="7:14">
+      <c r="O175" s="9"/>
+    </row>
+    <row r="176" spans="7:15">
       <c r="G176" s="4"/>
       <c r="K176" s="4"/>
       <c r="M176" s="4" t="str">
@@ -2837,8 +3006,9 @@
         <v/>
       </c>
       <c r="N176" s="7"/>
-    </row>
-    <row r="177" spans="7:14">
+      <c r="O176" s="9"/>
+    </row>
+    <row r="177" spans="7:15">
       <c r="G177" s="4"/>
       <c r="K177" s="4"/>
       <c r="M177" s="4" t="str">
@@ -2846,8 +3016,9 @@
         <v/>
       </c>
       <c r="N177" s="7"/>
-    </row>
-    <row r="178" spans="7:14">
+      <c r="O177" s="9"/>
+    </row>
+    <row r="178" spans="7:15">
       <c r="G178" s="4"/>
       <c r="K178" s="4"/>
       <c r="M178" s="4" t="str">
@@ -2855,8 +3026,9 @@
         <v/>
       </c>
       <c r="N178" s="7"/>
-    </row>
-    <row r="179" spans="7:14">
+      <c r="O178" s="9"/>
+    </row>
+    <row r="179" spans="7:15">
       <c r="G179" s="4"/>
       <c r="K179" s="4"/>
       <c r="M179" s="4" t="str">
@@ -2864,8 +3036,9 @@
         <v/>
       </c>
       <c r="N179" s="7"/>
-    </row>
-    <row r="180" spans="7:14">
+      <c r="O179" s="9"/>
+    </row>
+    <row r="180" spans="7:15">
       <c r="G180" s="4"/>
       <c r="K180" s="4"/>
       <c r="M180" s="4" t="str">
@@ -2873,8 +3046,9 @@
         <v/>
       </c>
       <c r="N180" s="7"/>
-    </row>
-    <row r="181" spans="7:14">
+      <c r="O180" s="9"/>
+    </row>
+    <row r="181" spans="7:15">
       <c r="G181" s="4"/>
       <c r="K181" s="4"/>
       <c r="M181" s="4" t="str">
@@ -2882,8 +3056,9 @@
         <v/>
       </c>
       <c r="N181" s="7"/>
-    </row>
-    <row r="182" spans="7:14">
+      <c r="O181" s="9"/>
+    </row>
+    <row r="182" spans="7:15">
       <c r="G182" s="4"/>
       <c r="K182" s="4"/>
       <c r="M182" s="4" t="str">
@@ -2891,8 +3066,9 @@
         <v/>
       </c>
       <c r="N182" s="7"/>
-    </row>
-    <row r="183" spans="7:14">
+      <c r="O182" s="9"/>
+    </row>
+    <row r="183" spans="7:15">
       <c r="G183" s="4"/>
       <c r="K183" s="4"/>
       <c r="M183" s="4" t="str">
@@ -2900,8 +3076,9 @@
         <v/>
       </c>
       <c r="N183" s="7"/>
-    </row>
-    <row r="184" spans="7:14">
+      <c r="O183" s="9"/>
+    </row>
+    <row r="184" spans="7:15">
       <c r="G184" s="4"/>
       <c r="K184" s="4"/>
       <c r="M184" s="4" t="str">
@@ -2909,8 +3086,9 @@
         <v/>
       </c>
       <c r="N184" s="7"/>
-    </row>
-    <row r="185" spans="7:14">
+      <c r="O184" s="9"/>
+    </row>
+    <row r="185" spans="7:15">
       <c r="G185" s="4"/>
       <c r="K185" s="4"/>
       <c r="M185" s="4" t="str">
@@ -2918,8 +3096,9 @@
         <v/>
       </c>
       <c r="N185" s="7"/>
-    </row>
-    <row r="186" spans="7:14">
+      <c r="O185" s="9"/>
+    </row>
+    <row r="186" spans="7:15">
       <c r="G186" s="4"/>
       <c r="K186" s="4"/>
       <c r="M186" s="4" t="str">
@@ -2927,8 +3106,9 @@
         <v/>
       </c>
       <c r="N186" s="7"/>
-    </row>
-    <row r="187" spans="7:14">
+      <c r="O186" s="9"/>
+    </row>
+    <row r="187" spans="7:15">
       <c r="G187" s="4"/>
       <c r="K187" s="4"/>
       <c r="M187" s="4" t="str">
@@ -2936,8 +3116,9 @@
         <v/>
       </c>
       <c r="N187" s="7"/>
-    </row>
-    <row r="188" spans="7:14">
+      <c r="O187" s="9"/>
+    </row>
+    <row r="188" spans="7:15">
       <c r="G188" s="4"/>
       <c r="K188" s="4"/>
       <c r="M188" s="4" t="str">
@@ -2945,8 +3126,9 @@
         <v/>
       </c>
       <c r="N188" s="7"/>
-    </row>
-    <row r="189" spans="7:14">
+      <c r="O188" s="9"/>
+    </row>
+    <row r="189" spans="7:15">
       <c r="G189" s="4"/>
       <c r="K189" s="4"/>
       <c r="M189" s="4" t="str">
@@ -2954,8 +3136,9 @@
         <v/>
       </c>
       <c r="N189" s="7"/>
-    </row>
-    <row r="190" spans="7:14">
+      <c r="O189" s="9"/>
+    </row>
+    <row r="190" spans="7:15">
       <c r="G190" s="4"/>
       <c r="K190" s="4"/>
       <c r="M190" s="4" t="str">
@@ -2963,8 +3146,9 @@
         <v/>
       </c>
       <c r="N190" s="7"/>
-    </row>
-    <row r="191" spans="7:14">
+      <c r="O190" s="9"/>
+    </row>
+    <row r="191" spans="7:15">
       <c r="G191" s="4"/>
       <c r="K191" s="4"/>
       <c r="M191" s="4" t="str">
@@ -2972,8 +3156,9 @@
         <v/>
       </c>
       <c r="N191" s="7"/>
-    </row>
-    <row r="192" spans="7:14">
+      <c r="O191" s="9"/>
+    </row>
+    <row r="192" spans="7:15">
       <c r="G192" s="4"/>
       <c r="K192" s="4"/>
       <c r="M192" s="4" t="str">
@@ -2981,8 +3166,9 @@
         <v/>
       </c>
       <c r="N192" s="7"/>
-    </row>
-    <row r="193" spans="7:14">
+      <c r="O192" s="9"/>
+    </row>
+    <row r="193" spans="7:15">
       <c r="G193" s="4"/>
       <c r="K193" s="4"/>
       <c r="M193" s="4" t="str">
@@ -2990,8 +3176,9 @@
         <v/>
       </c>
       <c r="N193" s="7"/>
-    </row>
-    <row r="194" spans="7:14">
+      <c r="O193" s="9"/>
+    </row>
+    <row r="194" spans="7:15">
       <c r="G194" s="4"/>
       <c r="K194" s="4"/>
       <c r="M194" s="4" t="str">
@@ -2999,8 +3186,9 @@
         <v/>
       </c>
       <c r="N194" s="7"/>
-    </row>
-    <row r="195" spans="7:14">
+      <c r="O194" s="9"/>
+    </row>
+    <row r="195" spans="7:15">
       <c r="G195" s="4"/>
       <c r="K195" s="4"/>
       <c r="M195" s="4" t="str">
@@ -3008,8 +3196,9 @@
         <v/>
       </c>
       <c r="N195" s="7"/>
-    </row>
-    <row r="196" spans="7:14">
+      <c r="O195" s="9"/>
+    </row>
+    <row r="196" spans="7:15">
       <c r="G196" s="4"/>
       <c r="K196" s="4"/>
       <c r="M196" s="4" t="str">
@@ -3017,8 +3206,9 @@
         <v/>
       </c>
       <c r="N196" s="7"/>
-    </row>
-    <row r="197" spans="7:14">
+      <c r="O196" s="9"/>
+    </row>
+    <row r="197" spans="7:15">
       <c r="G197" s="4"/>
       <c r="K197" s="4"/>
       <c r="M197" s="4" t="str">
@@ -3026,8 +3216,9 @@
         <v/>
       </c>
       <c r="N197" s="7"/>
-    </row>
-    <row r="198" spans="7:14">
+      <c r="O197" s="9"/>
+    </row>
+    <row r="198" spans="7:15">
       <c r="G198" s="4"/>
       <c r="K198" s="4"/>
       <c r="M198" s="4" t="str">
@@ -3035,8 +3226,9 @@
         <v/>
       </c>
       <c r="N198" s="7"/>
-    </row>
-    <row r="199" spans="7:14">
+      <c r="O198" s="9"/>
+    </row>
+    <row r="199" spans="7:15">
       <c r="G199" s="4"/>
       <c r="K199" s="4"/>
       <c r="M199" s="4" t="str">
@@ -3044,8 +3236,9 @@
         <v/>
       </c>
       <c r="N199" s="7"/>
-    </row>
-    <row r="200" spans="7:14">
+      <c r="O199" s="9"/>
+    </row>
+    <row r="200" spans="7:15">
       <c r="G200" s="4"/>
       <c r="K200" s="4"/>
       <c r="M200" s="4" t="str">
@@ -3053,8 +3246,9 @@
         <v/>
       </c>
       <c r="N200" s="7"/>
-    </row>
-    <row r="201" spans="7:14">
+      <c r="O200" s="9"/>
+    </row>
+    <row r="201" spans="7:15">
       <c r="G201" s="4"/>
       <c r="K201" s="4"/>
       <c r="M201" s="4" t="str">
@@ -3062,8 +3256,9 @@
         <v/>
       </c>
       <c r="N201" s="7"/>
-    </row>
-    <row r="202" spans="7:14">
+      <c r="O201" s="9"/>
+    </row>
+    <row r="202" spans="7:15">
       <c r="G202" s="4"/>
       <c r="K202" s="4"/>
       <c r="M202" s="4" t="str">
@@ -3071,8 +3266,9 @@
         <v/>
       </c>
       <c r="N202" s="7"/>
-    </row>
-    <row r="203" spans="7:14">
+      <c r="O202" s="9"/>
+    </row>
+    <row r="203" spans="7:15">
       <c r="G203" s="4"/>
       <c r="K203" s="4"/>
       <c r="M203" s="4" t="str">
@@ -3080,8 +3276,9 @@
         <v/>
       </c>
       <c r="N203" s="7"/>
-    </row>
-    <row r="204" spans="7:14">
+      <c r="O203" s="9"/>
+    </row>
+    <row r="204" spans="7:15">
       <c r="G204" s="4"/>
       <c r="K204" s="4"/>
       <c r="M204" s="4" t="str">
@@ -3089,8 +3286,9 @@
         <v/>
       </c>
       <c r="N204" s="7"/>
-    </row>
-    <row r="205" spans="7:14">
+      <c r="O204" s="9"/>
+    </row>
+    <row r="205" spans="7:15">
       <c r="G205" s="4"/>
       <c r="K205" s="4"/>
       <c r="M205" s="4" t="str">
@@ -3098,8 +3296,9 @@
         <v/>
       </c>
       <c r="N205" s="7"/>
-    </row>
-    <row r="206" spans="7:14">
+      <c r="O205" s="9"/>
+    </row>
+    <row r="206" spans="7:15">
       <c r="G206" s="4"/>
       <c r="K206" s="4"/>
       <c r="M206" s="4" t="str">
@@ -3107,8 +3306,9 @@
         <v/>
       </c>
       <c r="N206" s="7"/>
-    </row>
-    <row r="207" spans="7:14">
+      <c r="O206" s="9"/>
+    </row>
+    <row r="207" spans="7:15">
       <c r="G207" s="4"/>
       <c r="K207" s="4"/>
       <c r="M207" s="4" t="str">
@@ -3116,8 +3316,9 @@
         <v/>
       </c>
       <c r="N207" s="7"/>
-    </row>
-    <row r="208" spans="7:14">
+      <c r="O207" s="9"/>
+    </row>
+    <row r="208" spans="7:15">
       <c r="G208" s="4"/>
       <c r="K208" s="4"/>
       <c r="M208" s="4" t="str">
@@ -3125,8 +3326,9 @@
         <v/>
       </c>
       <c r="N208" s="7"/>
-    </row>
-    <row r="209" spans="7:14">
+      <c r="O208" s="9"/>
+    </row>
+    <row r="209" spans="7:15">
       <c r="G209" s="4"/>
       <c r="K209" s="4"/>
       <c r="M209" s="4" t="str">
@@ -3134,8 +3336,9 @@
         <v/>
       </c>
       <c r="N209" s="7"/>
-    </row>
-    <row r="210" spans="7:14">
+      <c r="O209" s="9"/>
+    </row>
+    <row r="210" spans="7:15">
       <c r="G210" s="4"/>
       <c r="K210" s="4"/>
       <c r="M210" s="4" t="str">
@@ -3143,8 +3346,9 @@
         <v/>
       </c>
       <c r="N210" s="7"/>
-    </row>
-    <row r="211" spans="7:14">
+      <c r="O210" s="9"/>
+    </row>
+    <row r="211" spans="7:15">
       <c r="G211" s="4"/>
       <c r="K211" s="4"/>
       <c r="M211" s="4" t="str">
@@ -3152,8 +3356,9 @@
         <v/>
       </c>
       <c r="N211" s="7"/>
-    </row>
-    <row r="212" spans="7:14">
+      <c r="O211" s="9"/>
+    </row>
+    <row r="212" spans="7:15">
       <c r="G212" s="4"/>
       <c r="K212" s="4"/>
       <c r="M212" s="4" t="str">
@@ -3161,8 +3366,9 @@
         <v/>
       </c>
       <c r="N212" s="7"/>
-    </row>
-    <row r="213" spans="7:14">
+      <c r="O212" s="9"/>
+    </row>
+    <row r="213" spans="7:15">
       <c r="G213" s="4"/>
       <c r="K213" s="4"/>
       <c r="M213" s="4" t="str">
@@ -3170,8 +3376,9 @@
         <v/>
       </c>
       <c r="N213" s="7"/>
-    </row>
-    <row r="214" spans="7:14">
+      <c r="O213" s="9"/>
+    </row>
+    <row r="214" spans="7:15">
       <c r="G214" s="4"/>
       <c r="K214" s="4"/>
       <c r="M214" s="4" t="str">
@@ -3179,8 +3386,9 @@
         <v/>
       </c>
       <c r="N214" s="7"/>
-    </row>
-    <row r="215" spans="7:14">
+      <c r="O214" s="9"/>
+    </row>
+    <row r="215" spans="7:15">
       <c r="G215" s="4"/>
       <c r="K215" s="4"/>
       <c r="M215" s="4" t="str">
@@ -3188,8 +3396,9 @@
         <v/>
       </c>
       <c r="N215" s="7"/>
-    </row>
-    <row r="216" spans="7:14">
+      <c r="O215" s="9"/>
+    </row>
+    <row r="216" spans="7:15">
       <c r="G216" s="4"/>
       <c r="K216" s="4"/>
       <c r="M216" s="4" t="str">
@@ -3197,8 +3406,9 @@
         <v/>
       </c>
       <c r="N216" s="7"/>
-    </row>
-    <row r="217" spans="7:14">
+      <c r="O216" s="9"/>
+    </row>
+    <row r="217" spans="7:15">
       <c r="G217" s="4"/>
       <c r="K217" s="4"/>
       <c r="M217" s="4" t="str">
@@ -3206,8 +3416,9 @@
         <v/>
       </c>
       <c r="N217" s="7"/>
-    </row>
-    <row r="218" spans="7:14">
+      <c r="O217" s="9"/>
+    </row>
+    <row r="218" spans="7:15">
       <c r="G218" s="4"/>
       <c r="K218" s="4"/>
       <c r="M218" s="4" t="str">
@@ -3215,8 +3426,9 @@
         <v/>
       </c>
       <c r="N218" s="7"/>
-    </row>
-    <row r="219" spans="7:14">
+      <c r="O218" s="9"/>
+    </row>
+    <row r="219" spans="7:15">
       <c r="G219" s="4"/>
       <c r="K219" s="4"/>
       <c r="M219" s="4" t="str">
@@ -3224,8 +3436,9 @@
         <v/>
       </c>
       <c r="N219" s="7"/>
-    </row>
-    <row r="220" spans="7:14">
+      <c r="O219" s="9"/>
+    </row>
+    <row r="220" spans="7:15">
       <c r="G220" s="4"/>
       <c r="K220" s="4"/>
       <c r="M220" s="4" t="str">
@@ -3233,8 +3446,9 @@
         <v/>
       </c>
       <c r="N220" s="7"/>
-    </row>
-    <row r="221" spans="7:14">
+      <c r="O220" s="9"/>
+    </row>
+    <row r="221" spans="7:15">
       <c r="G221" s="4"/>
       <c r="K221" s="4"/>
       <c r="M221" s="4" t="str">
@@ -3242,8 +3456,9 @@
         <v/>
       </c>
       <c r="N221" s="7"/>
-    </row>
-    <row r="222" spans="7:14">
+      <c r="O221" s="9"/>
+    </row>
+    <row r="222" spans="7:15">
       <c r="G222" s="4"/>
       <c r="K222" s="4"/>
       <c r="M222" s="4" t="str">
@@ -3251,8 +3466,9 @@
         <v/>
       </c>
       <c r="N222" s="7"/>
-    </row>
-    <row r="223" spans="7:14">
+      <c r="O222" s="9"/>
+    </row>
+    <row r="223" spans="7:15">
       <c r="G223" s="4"/>
       <c r="K223" s="4"/>
       <c r="M223" s="4" t="str">
@@ -3260,8 +3476,9 @@
         <v/>
       </c>
       <c r="N223" s="7"/>
-    </row>
-    <row r="224" spans="7:14">
+      <c r="O223" s="9"/>
+    </row>
+    <row r="224" spans="7:15">
       <c r="G224" s="4"/>
       <c r="K224" s="4"/>
       <c r="M224" s="4" t="str">
@@ -3269,8 +3486,9 @@
         <v/>
       </c>
       <c r="N224" s="7"/>
-    </row>
-    <row r="225" spans="7:14">
+      <c r="O224" s="9"/>
+    </row>
+    <row r="225" spans="7:15">
       <c r="G225" s="4"/>
       <c r="K225" s="4"/>
       <c r="M225" s="4" t="str">
@@ -3278,8 +3496,9 @@
         <v/>
       </c>
       <c r="N225" s="7"/>
-    </row>
-    <row r="226" spans="7:14">
+      <c r="O225" s="9"/>
+    </row>
+    <row r="226" spans="7:15">
       <c r="G226" s="4"/>
       <c r="K226" s="4"/>
       <c r="M226" s="4" t="str">
@@ -3287,8 +3506,9 @@
         <v/>
       </c>
       <c r="N226" s="7"/>
-    </row>
-    <row r="227" spans="7:14">
+      <c r="O226" s="9"/>
+    </row>
+    <row r="227" spans="7:15">
       <c r="G227" s="4"/>
       <c r="K227" s="4"/>
       <c r="M227" s="4" t="str">
@@ -3296,8 +3516,9 @@
         <v/>
       </c>
       <c r="N227" s="7"/>
-    </row>
-    <row r="228" spans="7:14">
+      <c r="O227" s="9"/>
+    </row>
+    <row r="228" spans="7:15">
       <c r="G228" s="4"/>
       <c r="K228" s="4"/>
       <c r="M228" s="4" t="str">
@@ -3305,8 +3526,9 @@
         <v/>
       </c>
       <c r="N228" s="7"/>
-    </row>
-    <row r="229" spans="7:14">
+      <c r="O228" s="9"/>
+    </row>
+    <row r="229" spans="7:15">
       <c r="G229" s="4"/>
       <c r="K229" s="4"/>
       <c r="M229" s="4" t="str">
@@ -3314,8 +3536,9 @@
         <v/>
       </c>
       <c r="N229" s="7"/>
-    </row>
-    <row r="230" spans="7:14">
+      <c r="O229" s="9"/>
+    </row>
+    <row r="230" spans="7:15">
       <c r="G230" s="4"/>
       <c r="K230" s="4"/>
       <c r="M230" s="4" t="str">
@@ -3323,8 +3546,9 @@
         <v/>
       </c>
       <c r="N230" s="7"/>
-    </row>
-    <row r="231" spans="7:14">
+      <c r="O230" s="9"/>
+    </row>
+    <row r="231" spans="7:15">
       <c r="G231" s="4"/>
       <c r="K231" s="4"/>
       <c r="M231" s="4" t="str">
@@ -3332,8 +3556,9 @@
         <v/>
       </c>
       <c r="N231" s="7"/>
-    </row>
-    <row r="232" spans="7:14">
+      <c r="O231" s="9"/>
+    </row>
+    <row r="232" spans="7:15">
       <c r="G232" s="4"/>
       <c r="K232" s="4"/>
       <c r="M232" s="4" t="str">
@@ -3341,8 +3566,9 @@
         <v/>
       </c>
       <c r="N232" s="7"/>
-    </row>
-    <row r="233" spans="7:14">
+      <c r="O232" s="9"/>
+    </row>
+    <row r="233" spans="7:15">
       <c r="G233" s="4"/>
       <c r="K233" s="4"/>
       <c r="M233" s="4" t="str">
@@ -3350,8 +3576,9 @@
         <v/>
       </c>
       <c r="N233" s="7"/>
-    </row>
-    <row r="234" spans="7:14">
+      <c r="O233" s="9"/>
+    </row>
+    <row r="234" spans="7:15">
       <c r="G234" s="4"/>
       <c r="K234" s="4"/>
       <c r="M234" s="4" t="str">
@@ -3359,8 +3586,9 @@
         <v/>
       </c>
       <c r="N234" s="7"/>
-    </row>
-    <row r="235" spans="7:14">
+      <c r="O234" s="9"/>
+    </row>
+    <row r="235" spans="7:15">
       <c r="G235" s="4"/>
       <c r="K235" s="4"/>
       <c r="M235" s="4" t="str">
@@ -3368,8 +3596,9 @@
         <v/>
       </c>
       <c r="N235" s="7"/>
-    </row>
-    <row r="236" spans="7:14">
+      <c r="O235" s="9"/>
+    </row>
+    <row r="236" spans="7:15">
       <c r="G236" s="4"/>
       <c r="K236" s="4"/>
       <c r="M236" s="4" t="str">
@@ -3377,8 +3606,9 @@
         <v/>
       </c>
       <c r="N236" s="7"/>
-    </row>
-    <row r="237" spans="7:14">
+      <c r="O236" s="9"/>
+    </row>
+    <row r="237" spans="7:15">
       <c r="G237" s="4"/>
       <c r="K237" s="4"/>
       <c r="M237" s="4" t="str">
@@ -3386,8 +3616,9 @@
         <v/>
       </c>
       <c r="N237" s="7"/>
-    </row>
-    <row r="238" spans="7:14">
+      <c r="O237" s="9"/>
+    </row>
+    <row r="238" spans="7:15">
       <c r="G238" s="4"/>
       <c r="K238" s="4"/>
       <c r="M238" s="4" t="str">
@@ -3395,8 +3626,9 @@
         <v/>
       </c>
       <c r="N238" s="7"/>
-    </row>
-    <row r="239" spans="7:14">
+      <c r="O238" s="9"/>
+    </row>
+    <row r="239" spans="7:15">
       <c r="G239" s="4"/>
       <c r="K239" s="4"/>
       <c r="M239" s="4" t="str">
@@ -3404,8 +3636,9 @@
         <v/>
       </c>
       <c r="N239" s="7"/>
-    </row>
-    <row r="240" spans="7:14">
+      <c r="O239" s="9"/>
+    </row>
+    <row r="240" spans="7:15">
       <c r="G240" s="4"/>
       <c r="K240" s="4"/>
       <c r="M240" s="4" t="str">
@@ -3413,8 +3646,9 @@
         <v/>
       </c>
       <c r="N240" s="7"/>
-    </row>
-    <row r="241" spans="7:14">
+      <c r="O240" s="9"/>
+    </row>
+    <row r="241" spans="7:15">
       <c r="G241" s="4"/>
       <c r="K241" s="4"/>
       <c r="M241" s="4" t="str">
@@ -3422,8 +3656,9 @@
         <v/>
       </c>
       <c r="N241" s="7"/>
-    </row>
-    <row r="242" spans="7:14">
+      <c r="O241" s="9"/>
+    </row>
+    <row r="242" spans="7:15">
       <c r="G242" s="4"/>
       <c r="K242" s="4"/>
       <c r="M242" s="4" t="str">
@@ -3431,8 +3666,9 @@
         <v/>
       </c>
       <c r="N242" s="7"/>
-    </row>
-    <row r="243" spans="7:14">
+      <c r="O242" s="9"/>
+    </row>
+    <row r="243" spans="7:15">
       <c r="G243" s="4"/>
       <c r="K243" s="4"/>
       <c r="M243" s="4" t="str">
@@ -3440,8 +3676,9 @@
         <v/>
       </c>
       <c r="N243" s="7"/>
-    </row>
-    <row r="244" spans="7:14">
+      <c r="O243" s="9"/>
+    </row>
+    <row r="244" spans="7:15">
       <c r="G244" s="4"/>
       <c r="K244" s="4"/>
       <c r="M244" s="4" t="str">
@@ -3449,8 +3686,9 @@
         <v/>
       </c>
       <c r="N244" s="7"/>
-    </row>
-    <row r="245" spans="7:14">
+      <c r="O244" s="9"/>
+    </row>
+    <row r="245" spans="7:15">
       <c r="G245" s="4"/>
       <c r="K245" s="4"/>
       <c r="M245" s="4" t="str">
@@ -3458,8 +3696,9 @@
         <v/>
       </c>
       <c r="N245" s="7"/>
-    </row>
-    <row r="246" spans="7:14">
+      <c r="O245" s="9"/>
+    </row>
+    <row r="246" spans="7:15">
       <c r="G246" s="4"/>
       <c r="K246" s="4"/>
       <c r="M246" s="4" t="str">
@@ -3467,8 +3706,9 @@
         <v/>
       </c>
       <c r="N246" s="7"/>
-    </row>
-    <row r="247" spans="7:14">
+      <c r="O246" s="9"/>
+    </row>
+    <row r="247" spans="7:15">
       <c r="G247" s="4"/>
       <c r="K247" s="4"/>
       <c r="M247" s="4" t="str">
@@ -3476,8 +3716,9 @@
         <v/>
       </c>
       <c r="N247" s="7"/>
-    </row>
-    <row r="248" spans="7:14">
+      <c r="O247" s="9"/>
+    </row>
+    <row r="248" spans="7:15">
       <c r="G248" s="4"/>
       <c r="K248" s="4"/>
       <c r="M248" s="4" t="str">
@@ -3485,8 +3726,9 @@
         <v/>
       </c>
       <c r="N248" s="7"/>
-    </row>
-    <row r="249" spans="7:14">
+      <c r="O248" s="9"/>
+    </row>
+    <row r="249" spans="7:15">
       <c r="G249" s="4"/>
       <c r="K249" s="4"/>
       <c r="M249" s="4" t="str">
@@ -3494,8 +3736,9 @@
         <v/>
       </c>
       <c r="N249" s="7"/>
-    </row>
-    <row r="250" spans="7:14">
+      <c r="O249" s="9"/>
+    </row>
+    <row r="250" spans="7:15">
       <c r="G250" s="4"/>
       <c r="K250" s="4"/>
       <c r="M250" s="4" t="str">
@@ -3503,8 +3746,9 @@
         <v/>
       </c>
       <c r="N250" s="7"/>
-    </row>
-    <row r="251" spans="7:14">
+      <c r="O250" s="9"/>
+    </row>
+    <row r="251" spans="7:15">
       <c r="G251" s="4"/>
       <c r="K251" s="4"/>
       <c r="M251" s="4" t="str">
@@ -3512,8 +3756,9 @@
         <v/>
       </c>
       <c r="N251" s="7"/>
-    </row>
-    <row r="252" spans="7:14">
+      <c r="O251" s="9"/>
+    </row>
+    <row r="252" spans="7:15">
       <c r="G252" s="4"/>
       <c r="K252" s="4"/>
       <c r="M252" s="4" t="str">
@@ -3521,8 +3766,9 @@
         <v/>
       </c>
       <c r="N252" s="7"/>
-    </row>
-    <row r="253" spans="7:14">
+      <c r="O252" s="9"/>
+    </row>
+    <row r="253" spans="7:15">
       <c r="G253" s="4"/>
       <c r="K253" s="4"/>
       <c r="M253" s="4" t="str">
@@ -3530,8 +3776,9 @@
         <v/>
       </c>
       <c r="N253" s="7"/>
-    </row>
-    <row r="254" spans="7:14">
+      <c r="O253" s="9"/>
+    </row>
+    <row r="254" spans="7:15">
       <c r="G254" s="4"/>
       <c r="K254" s="4"/>
       <c r="M254" s="4" t="str">
@@ -3539,8 +3786,9 @@
         <v/>
       </c>
       <c r="N254" s="7"/>
-    </row>
-    <row r="255" spans="7:14">
+      <c r="O254" s="9"/>
+    </row>
+    <row r="255" spans="7:15">
       <c r="G255" s="4"/>
       <c r="K255" s="4"/>
       <c r="M255" s="4" t="str">
@@ -3548,8 +3796,9 @@
         <v/>
       </c>
       <c r="N255" s="7"/>
-    </row>
-    <row r="256" spans="7:14">
+      <c r="O255" s="9"/>
+    </row>
+    <row r="256" spans="7:15">
       <c r="G256" s="4"/>
       <c r="K256" s="4"/>
       <c r="M256" s="4" t="str">
@@ -3557,8 +3806,9 @@
         <v/>
       </c>
       <c r="N256" s="7"/>
-    </row>
-    <row r="257" spans="7:14">
+      <c r="O256" s="9"/>
+    </row>
+    <row r="257" spans="7:15">
       <c r="G257" s="4"/>
       <c r="K257" s="4"/>
       <c r="M257" s="4" t="str">
@@ -3566,8 +3816,9 @@
         <v/>
       </c>
       <c r="N257" s="7"/>
-    </row>
-    <row r="258" spans="7:14">
+      <c r="O257" s="9"/>
+    </row>
+    <row r="258" spans="7:15">
       <c r="G258" s="4"/>
       <c r="K258" s="4"/>
       <c r="M258" s="4" t="str">
@@ -3575,8 +3826,9 @@
         <v/>
       </c>
       <c r="N258" s="7"/>
-    </row>
-    <row r="259" spans="7:14">
+      <c r="O258" s="9"/>
+    </row>
+    <row r="259" spans="7:15">
       <c r="G259" s="4"/>
       <c r="K259" s="4"/>
       <c r="M259" s="4" t="str">
@@ -3584,8 +3836,9 @@
         <v/>
       </c>
       <c r="N259" s="7"/>
-    </row>
-    <row r="260" spans="7:14">
+      <c r="O259" s="9"/>
+    </row>
+    <row r="260" spans="7:15">
       <c r="G260" s="4"/>
       <c r="K260" s="4"/>
       <c r="M260" s="4" t="str">
@@ -3593,8 +3846,9 @@
         <v/>
       </c>
       <c r="N260" s="7"/>
-    </row>
-    <row r="261" spans="7:14">
+      <c r="O260" s="9"/>
+    </row>
+    <row r="261" spans="7:15">
       <c r="G261" s="4"/>
       <c r="K261" s="4"/>
       <c r="M261" s="4" t="str">
@@ -3602,8 +3856,9 @@
         <v/>
       </c>
       <c r="N261" s="7"/>
-    </row>
-    <row r="262" spans="7:14">
+      <c r="O261" s="9"/>
+    </row>
+    <row r="262" spans="7:15">
       <c r="G262" s="4"/>
       <c r="K262" s="4"/>
       <c r="M262" s="4" t="str">
@@ -3611,8 +3866,9 @@
         <v/>
       </c>
       <c r="N262" s="7"/>
-    </row>
-    <row r="263" spans="7:14">
+      <c r="O262" s="9"/>
+    </row>
+    <row r="263" spans="7:15">
       <c r="G263" s="4"/>
       <c r="K263" s="4"/>
       <c r="M263" s="4" t="str">
@@ -3620,8 +3876,9 @@
         <v/>
       </c>
       <c r="N263" s="7"/>
-    </row>
-    <row r="264" spans="7:14">
+      <c r="O263" s="9"/>
+    </row>
+    <row r="264" spans="7:15">
       <c r="G264" s="4"/>
       <c r="K264" s="4"/>
       <c r="M264" s="4" t="str">
@@ -3629,8 +3886,9 @@
         <v/>
       </c>
       <c r="N264" s="7"/>
-    </row>
-    <row r="265" spans="7:14">
+      <c r="O264" s="9"/>
+    </row>
+    <row r="265" spans="7:15">
       <c r="G265" s="4"/>
       <c r="K265" s="4"/>
       <c r="M265" s="4" t="str">
@@ -3638,8 +3896,9 @@
         <v/>
       </c>
       <c r="N265" s="7"/>
-    </row>
-    <row r="266" spans="7:14">
+      <c r="O265" s="9"/>
+    </row>
+    <row r="266" spans="7:15">
       <c r="G266" s="4"/>
       <c r="K266" s="4"/>
       <c r="M266" s="4" t="str">
@@ -3647,8 +3906,9 @@
         <v/>
       </c>
       <c r="N266" s="7"/>
-    </row>
-    <row r="267" spans="7:14">
+      <c r="O266" s="9"/>
+    </row>
+    <row r="267" spans="7:15">
       <c r="G267" s="4"/>
       <c r="K267" s="4"/>
       <c r="M267" s="4" t="str">
@@ -3656,8 +3916,9 @@
         <v/>
       </c>
       <c r="N267" s="7"/>
-    </row>
-    <row r="268" spans="7:14">
+      <c r="O267" s="9"/>
+    </row>
+    <row r="268" spans="7:15">
       <c r="G268" s="4"/>
       <c r="K268" s="4"/>
       <c r="M268" s="4" t="str">
@@ -3665,8 +3926,9 @@
         <v/>
       </c>
       <c r="N268" s="7"/>
-    </row>
-    <row r="269" spans="7:14">
+      <c r="O268" s="9"/>
+    </row>
+    <row r="269" spans="7:15">
       <c r="G269" s="4"/>
       <c r="K269" s="4"/>
       <c r="M269" s="4" t="str">
@@ -3674,8 +3936,9 @@
         <v/>
       </c>
       <c r="N269" s="7"/>
-    </row>
-    <row r="270" spans="7:14">
+      <c r="O269" s="9"/>
+    </row>
+    <row r="270" spans="7:15">
       <c r="G270" s="4"/>
       <c r="K270" s="4"/>
       <c r="M270" s="4" t="str">
@@ -3683,8 +3946,9 @@
         <v/>
       </c>
       <c r="N270" s="7"/>
-    </row>
-    <row r="271" spans="7:14">
+      <c r="O270" s="9"/>
+    </row>
+    <row r="271" spans="7:15">
       <c r="G271" s="4"/>
       <c r="K271" s="4"/>
       <c r="M271" s="4" t="str">
@@ -3692,8 +3956,9 @@
         <v/>
       </c>
       <c r="N271" s="7"/>
-    </row>
-    <row r="272" spans="7:14">
+      <c r="O271" s="9"/>
+    </row>
+    <row r="272" spans="7:15">
       <c r="G272" s="4"/>
       <c r="K272" s="4"/>
       <c r="M272" s="4" t="str">
@@ -3701,8 +3966,9 @@
         <v/>
       </c>
       <c r="N272" s="7"/>
-    </row>
-    <row r="273" spans="7:14">
+      <c r="O272" s="9"/>
+    </row>
+    <row r="273" spans="7:15">
       <c r="G273" s="4"/>
       <c r="K273" s="4"/>
       <c r="M273" s="4" t="str">
@@ -3710,8 +3976,9 @@
         <v/>
       </c>
       <c r="N273" s="7"/>
-    </row>
-    <row r="274" spans="7:14">
+      <c r="O273" s="9"/>
+    </row>
+    <row r="274" spans="7:15">
       <c r="G274" s="4"/>
       <c r="K274" s="4"/>
       <c r="M274" s="4" t="str">
@@ -3719,8 +3986,9 @@
         <v/>
       </c>
       <c r="N274" s="7"/>
-    </row>
-    <row r="275" spans="7:14">
+      <c r="O274" s="9"/>
+    </row>
+    <row r="275" spans="7:15">
       <c r="G275" s="4"/>
       <c r="K275" s="4"/>
       <c r="M275" s="4" t="str">
@@ -3728,8 +3996,9 @@
         <v/>
       </c>
       <c r="N275" s="7"/>
-    </row>
-    <row r="276" spans="7:14">
+      <c r="O275" s="9"/>
+    </row>
+    <row r="276" spans="7:15">
       <c r="G276" s="4"/>
       <c r="K276" s="4"/>
       <c r="M276" s="4" t="str">
@@ -3737,8 +4006,9 @@
         <v/>
       </c>
       <c r="N276" s="7"/>
-    </row>
-    <row r="277" spans="7:14">
+      <c r="O276" s="9"/>
+    </row>
+    <row r="277" spans="7:15">
       <c r="G277" s="4"/>
       <c r="K277" s="4"/>
       <c r="M277" s="4" t="str">
@@ -3746,8 +4016,9 @@
         <v/>
       </c>
       <c r="N277" s="7"/>
-    </row>
-    <row r="278" spans="7:14">
+      <c r="O277" s="9"/>
+    </row>
+    <row r="278" spans="7:15">
       <c r="G278" s="4"/>
       <c r="K278" s="4"/>
       <c r="M278" s="4" t="str">
@@ -3755,8 +4026,9 @@
         <v/>
       </c>
       <c r="N278" s="7"/>
-    </row>
-    <row r="279" spans="7:14">
+      <c r="O278" s="9"/>
+    </row>
+    <row r="279" spans="7:15">
       <c r="G279" s="4"/>
       <c r="K279" s="4"/>
       <c r="M279" s="4" t="str">
@@ -3764,8 +4036,9 @@
         <v/>
       </c>
       <c r="N279" s="7"/>
-    </row>
-    <row r="280" spans="7:14">
+      <c r="O279" s="9"/>
+    </row>
+    <row r="280" spans="7:15">
       <c r="G280" s="4"/>
       <c r="K280" s="4"/>
       <c r="M280" s="4" t="str">
@@ -3773,8 +4046,9 @@
         <v/>
       </c>
       <c r="N280" s="7"/>
-    </row>
-    <row r="281" spans="7:14">
+      <c r="O280" s="9"/>
+    </row>
+    <row r="281" spans="7:15">
       <c r="G281" s="4"/>
       <c r="K281" s="4"/>
       <c r="M281" s="4" t="str">
@@ -3782,8 +4056,9 @@
         <v/>
       </c>
       <c r="N281" s="7"/>
-    </row>
-    <row r="282" spans="7:14">
+      <c r="O281" s="9"/>
+    </row>
+    <row r="282" spans="7:15">
       <c r="G282" s="4"/>
       <c r="K282" s="4"/>
       <c r="M282" s="4" t="str">
@@ -3791,8 +4066,9 @@
         <v/>
       </c>
       <c r="N282" s="7"/>
-    </row>
-    <row r="283" spans="7:14">
+      <c r="O282" s="9"/>
+    </row>
+    <row r="283" spans="7:15">
       <c r="G283" s="4"/>
       <c r="K283" s="4"/>
       <c r="M283" s="4" t="str">
@@ -3800,8 +4076,9 @@
         <v/>
       </c>
       <c r="N283" s="7"/>
-    </row>
-    <row r="284" spans="7:14">
+      <c r="O283" s="9"/>
+    </row>
+    <row r="284" spans="7:15">
       <c r="G284" s="4"/>
       <c r="K284" s="4"/>
       <c r="M284" s="4" t="str">
@@ -3809,8 +4086,9 @@
         <v/>
       </c>
       <c r="N284" s="7"/>
-    </row>
-    <row r="285" spans="7:14">
+      <c r="O284" s="9"/>
+    </row>
+    <row r="285" spans="7:15">
       <c r="G285" s="4"/>
       <c r="K285" s="4"/>
       <c r="M285" s="4" t="str">
@@ -3818,8 +4096,9 @@
         <v/>
       </c>
       <c r="N285" s="7"/>
-    </row>
-    <row r="286" spans="7:14">
+      <c r="O285" s="9"/>
+    </row>
+    <row r="286" spans="7:15">
       <c r="G286" s="4"/>
       <c r="K286" s="4"/>
       <c r="M286" s="4" t="str">
@@ -3827,8 +4106,9 @@
         <v/>
       </c>
       <c r="N286" s="7"/>
-    </row>
-    <row r="287" spans="7:14">
+      <c r="O286" s="9"/>
+    </row>
+    <row r="287" spans="7:15">
       <c r="G287" s="4"/>
       <c r="K287" s="4"/>
       <c r="M287" s="4" t="str">
@@ -3836,8 +4116,9 @@
         <v/>
       </c>
       <c r="N287" s="7"/>
-    </row>
-    <row r="288" spans="7:14">
+      <c r="O287" s="9"/>
+    </row>
+    <row r="288" spans="7:15">
       <c r="G288" s="4"/>
       <c r="K288" s="4"/>
       <c r="M288" s="4" t="str">
@@ -3845,8 +4126,9 @@
         <v/>
       </c>
       <c r="N288" s="7"/>
-    </row>
-    <row r="289" spans="7:14">
+      <c r="O288" s="9"/>
+    </row>
+    <row r="289" spans="7:15">
       <c r="G289" s="4"/>
       <c r="K289" s="4"/>
       <c r="M289" s="4" t="str">
@@ -3854,8 +4136,9 @@
         <v/>
       </c>
       <c r="N289" s="7"/>
-    </row>
-    <row r="290" spans="7:14">
+      <c r="O289" s="9"/>
+    </row>
+    <row r="290" spans="7:15">
       <c r="G290" s="4"/>
       <c r="K290" s="4"/>
       <c r="M290" s="4" t="str">
@@ -3863,8 +4146,9 @@
         <v/>
       </c>
       <c r="N290" s="7"/>
-    </row>
-    <row r="291" spans="7:14">
+      <c r="O290" s="9"/>
+    </row>
+    <row r="291" spans="7:15">
       <c r="G291" s="4"/>
       <c r="K291" s="4"/>
       <c r="M291" s="4" t="str">
@@ -3872,8 +4156,9 @@
         <v/>
       </c>
       <c r="N291" s="7"/>
-    </row>
-    <row r="292" spans="7:14">
+      <c r="O291" s="9"/>
+    </row>
+    <row r="292" spans="7:15">
       <c r="G292" s="4"/>
       <c r="K292" s="4"/>
       <c r="M292" s="4" t="str">
@@ -3881,8 +4166,9 @@
         <v/>
       </c>
       <c r="N292" s="7"/>
-    </row>
-    <row r="293" spans="7:14">
+      <c r="O292" s="9"/>
+    </row>
+    <row r="293" spans="7:15">
       <c r="G293" s="4"/>
       <c r="K293" s="4"/>
       <c r="M293" s="4" t="str">
@@ -3890,8 +4176,9 @@
         <v/>
       </c>
       <c r="N293" s="7"/>
-    </row>
-    <row r="294" spans="7:14">
+      <c r="O293" s="9"/>
+    </row>
+    <row r="294" spans="7:15">
       <c r="G294" s="4"/>
       <c r="K294" s="4"/>
       <c r="M294" s="4" t="str">
@@ -3899,8 +4186,9 @@
         <v/>
       </c>
       <c r="N294" s="7"/>
-    </row>
-    <row r="295" spans="7:14">
+      <c r="O294" s="9"/>
+    </row>
+    <row r="295" spans="7:15">
       <c r="G295" s="4"/>
       <c r="K295" s="4"/>
       <c r="M295" s="4" t="str">
@@ -3908,8 +4196,9 @@
         <v/>
       </c>
       <c r="N295" s="7"/>
-    </row>
-    <row r="296" spans="7:14">
+      <c r="O295" s="9"/>
+    </row>
+    <row r="296" spans="7:15">
       <c r="G296" s="4"/>
       <c r="K296" s="4"/>
       <c r="M296" s="4" t="str">
@@ -3917,8 +4206,9 @@
         <v/>
       </c>
       <c r="N296" s="7"/>
-    </row>
-    <row r="297" spans="7:14">
+      <c r="O296" s="9"/>
+    </row>
+    <row r="297" spans="7:15">
       <c r="G297" s="4"/>
       <c r="K297" s="4"/>
       <c r="M297" s="4" t="str">
@@ -3926,8 +4216,9 @@
         <v/>
       </c>
       <c r="N297" s="7"/>
-    </row>
-    <row r="298" spans="7:14">
+      <c r="O297" s="9"/>
+    </row>
+    <row r="298" spans="7:15">
       <c r="G298" s="4"/>
       <c r="K298" s="4"/>
       <c r="M298" s="4" t="str">
@@ -3935,8 +4226,9 @@
         <v/>
       </c>
       <c r="N298" s="7"/>
-    </row>
-    <row r="299" spans="7:14">
+      <c r="O298" s="9"/>
+    </row>
+    <row r="299" spans="7:15">
       <c r="G299" s="4"/>
       <c r="K299" s="4"/>
       <c r="M299" s="4" t="str">
@@ -3944,8 +4236,9 @@
         <v/>
       </c>
       <c r="N299" s="7"/>
-    </row>
-    <row r="300" spans="7:14">
+      <c r="O299" s="9"/>
+    </row>
+    <row r="300" spans="7:15">
       <c r="G300" s="4"/>
       <c r="K300" s="4"/>
       <c r="M300" s="4" t="str">
@@ -3953,8 +4246,9 @@
         <v/>
       </c>
       <c r="N300" s="7"/>
-    </row>
-    <row r="301" spans="7:14">
+      <c r="O300" s="9"/>
+    </row>
+    <row r="301" spans="7:15">
       <c r="G301" s="4"/>
       <c r="K301" s="4"/>
       <c r="M301" s="4" t="str">
@@ -3962,8 +4256,9 @@
         <v/>
       </c>
       <c r="N301" s="7"/>
-    </row>
-    <row r="302" spans="7:14">
+      <c r="O301" s="9"/>
+    </row>
+    <row r="302" spans="7:15">
       <c r="G302" s="4"/>
       <c r="K302" s="4"/>
       <c r="M302" s="4" t="str">
@@ -3971,8 +4266,9 @@
         <v/>
       </c>
       <c r="N302" s="7"/>
-    </row>
-    <row r="303" spans="7:14">
+      <c r="O302" s="9"/>
+    </row>
+    <row r="303" spans="7:15">
       <c r="G303" s="4"/>
       <c r="K303" s="4"/>
       <c r="M303" s="4" t="str">
@@ -3980,8 +4276,9 @@
         <v/>
       </c>
       <c r="N303" s="7"/>
-    </row>
-    <row r="304" spans="7:14">
+      <c r="O303" s="9"/>
+    </row>
+    <row r="304" spans="7:15">
       <c r="G304" s="4"/>
       <c r="K304" s="4"/>
       <c r="M304" s="4" t="str">
@@ -3989,8 +4286,9 @@
         <v/>
       </c>
       <c r="N304" s="7"/>
-    </row>
-    <row r="305" spans="7:14">
+      <c r="O304" s="9"/>
+    </row>
+    <row r="305" spans="7:15">
       <c r="G305" s="4"/>
       <c r="K305" s="4"/>
       <c r="M305" s="4" t="str">
@@ -3998,8 +4296,9 @@
         <v/>
       </c>
       <c r="N305" s="7"/>
-    </row>
-    <row r="306" spans="7:14">
+      <c r="O305" s="9"/>
+    </row>
+    <row r="306" spans="7:15">
       <c r="G306" s="4"/>
       <c r="K306" s="4"/>
       <c r="M306" s="4" t="str">
@@ -4007,8 +4306,9 @@
         <v/>
       </c>
       <c r="N306" s="7"/>
-    </row>
-    <row r="307" spans="7:14">
+      <c r="O306" s="9"/>
+    </row>
+    <row r="307" spans="7:15">
       <c r="G307" s="4"/>
       <c r="K307" s="4"/>
       <c r="M307" s="4" t="str">
@@ -4016,8 +4316,9 @@
         <v/>
       </c>
       <c r="N307" s="7"/>
-    </row>
-    <row r="308" spans="7:14">
+      <c r="O307" s="9"/>
+    </row>
+    <row r="308" spans="7:15">
       <c r="G308" s="4"/>
       <c r="K308" s="4"/>
       <c r="M308" s="4" t="str">
@@ -4025,8 +4326,9 @@
         <v/>
       </c>
       <c r="N308" s="7"/>
-    </row>
-    <row r="309" spans="7:14">
+      <c r="O308" s="9"/>
+    </row>
+    <row r="309" spans="7:15">
       <c r="G309" s="4"/>
       <c r="K309" s="4"/>
       <c r="M309" s="4" t="str">
@@ -4034,8 +4336,9 @@
         <v/>
       </c>
       <c r="N309" s="7"/>
-    </row>
-    <row r="310" spans="7:14">
+      <c r="O309" s="9"/>
+    </row>
+    <row r="310" spans="7:15">
       <c r="G310" s="4"/>
       <c r="K310" s="4"/>
       <c r="M310" s="4" t="str">
@@ -4043,8 +4346,9 @@
         <v/>
       </c>
       <c r="N310" s="7"/>
-    </row>
-    <row r="311" spans="7:14">
+      <c r="O310" s="9"/>
+    </row>
+    <row r="311" spans="7:15">
       <c r="G311" s="4"/>
       <c r="K311" s="4"/>
       <c r="M311" s="4" t="str">
@@ -4052,8 +4356,9 @@
         <v/>
       </c>
       <c r="N311" s="7"/>
-    </row>
-    <row r="312" spans="7:14">
+      <c r="O311" s="9"/>
+    </row>
+    <row r="312" spans="7:15">
       <c r="G312" s="4"/>
       <c r="K312" s="4"/>
       <c r="M312" s="4" t="str">
@@ -4061,8 +4366,9 @@
         <v/>
       </c>
       <c r="N312" s="7"/>
-    </row>
-    <row r="313" spans="7:14">
+      <c r="O312" s="9"/>
+    </row>
+    <row r="313" spans="7:15">
       <c r="G313" s="4"/>
       <c r="K313" s="4"/>
       <c r="M313" s="4" t="str">
@@ -4070,8 +4376,9 @@
         <v/>
       </c>
       <c r="N313" s="7"/>
-    </row>
-    <row r="314" spans="7:14">
+      <c r="O313" s="9"/>
+    </row>
+    <row r="314" spans="7:15">
       <c r="G314" s="4"/>
       <c r="K314" s="4"/>
       <c r="M314" s="4" t="str">
@@ -4079,8 +4386,9 @@
         <v/>
       </c>
       <c r="N314" s="7"/>
-    </row>
-    <row r="315" spans="7:14">
+      <c r="O314" s="9"/>
+    </row>
+    <row r="315" spans="7:15">
       <c r="G315" s="4"/>
       <c r="K315" s="4"/>
       <c r="M315" s="4" t="str">
@@ -4088,8 +4396,9 @@
         <v/>
       </c>
       <c r="N315" s="7"/>
-    </row>
-    <row r="316" spans="7:14">
+      <c r="O315" s="9"/>
+    </row>
+    <row r="316" spans="7:15">
       <c r="G316" s="4"/>
       <c r="K316" s="4"/>
       <c r="M316" s="4" t="str">
@@ -4097,8 +4406,9 @@
         <v/>
       </c>
       <c r="N316" s="7"/>
-    </row>
-    <row r="317" spans="7:14">
+      <c r="O316" s="9"/>
+    </row>
+    <row r="317" spans="7:15">
       <c r="G317" s="4"/>
       <c r="K317" s="4"/>
       <c r="M317" s="4" t="str">
@@ -4106,8 +4416,9 @@
         <v/>
       </c>
       <c r="N317" s="7"/>
-    </row>
-    <row r="318" spans="7:14">
+      <c r="O317" s="9"/>
+    </row>
+    <row r="318" spans="7:15">
       <c r="G318" s="4"/>
       <c r="K318" s="4"/>
       <c r="M318" s="4" t="str">
@@ -4115,8 +4426,9 @@
         <v/>
       </c>
       <c r="N318" s="7"/>
-    </row>
-    <row r="319" spans="7:14">
+      <c r="O318" s="9"/>
+    </row>
+    <row r="319" spans="7:15">
       <c r="G319" s="4"/>
       <c r="K319" s="4"/>
       <c r="M319" s="4" t="str">
@@ -4124,8 +4436,9 @@
         <v/>
       </c>
       <c r="N319" s="7"/>
-    </row>
-    <row r="320" spans="7:14">
+      <c r="O319" s="9"/>
+    </row>
+    <row r="320" spans="7:15">
       <c r="G320" s="4"/>
       <c r="K320" s="4"/>
       <c r="M320" s="4" t="str">
@@ -4133,8 +4446,9 @@
         <v/>
       </c>
       <c r="N320" s="7"/>
-    </row>
-    <row r="321" spans="7:14">
+      <c r="O320" s="9"/>
+    </row>
+    <row r="321" spans="7:15">
       <c r="G321" s="4"/>
       <c r="K321" s="4"/>
       <c r="M321" s="4" t="str">
@@ -4142,8 +4456,9 @@
         <v/>
       </c>
       <c r="N321" s="7"/>
-    </row>
-    <row r="322" spans="7:14">
+      <c r="O321" s="9"/>
+    </row>
+    <row r="322" spans="7:15">
       <c r="G322" s="4"/>
       <c r="K322" s="4"/>
       <c r="M322" s="4" t="str">
@@ -4151,8 +4466,9 @@
         <v/>
       </c>
       <c r="N322" s="7"/>
-    </row>
-    <row r="323" spans="7:14">
+      <c r="O322" s="9"/>
+    </row>
+    <row r="323" spans="7:15">
       <c r="G323" s="4"/>
       <c r="K323" s="4"/>
       <c r="M323" s="4" t="str">
@@ -4160,8 +4476,9 @@
         <v/>
       </c>
       <c r="N323" s="7"/>
-    </row>
-    <row r="324" spans="7:14">
+      <c r="O323" s="9"/>
+    </row>
+    <row r="324" spans="7:15">
       <c r="G324" s="4"/>
       <c r="K324" s="4"/>
       <c r="M324" s="4" t="str">
@@ -4169,8 +4486,9 @@
         <v/>
       </c>
       <c r="N324" s="7"/>
-    </row>
-    <row r="325" spans="7:14">
+      <c r="O324" s="9"/>
+    </row>
+    <row r="325" spans="7:15">
       <c r="G325" s="4"/>
       <c r="K325" s="4"/>
       <c r="M325" s="4" t="str">
@@ -4178,8 +4496,9 @@
         <v/>
       </c>
       <c r="N325" s="7"/>
-    </row>
-    <row r="326" spans="7:14">
+      <c r="O325" s="9"/>
+    </row>
+    <row r="326" spans="7:15">
       <c r="G326" s="4"/>
       <c r="K326" s="4"/>
       <c r="M326" s="4" t="str">
@@ -4187,8 +4506,9 @@
         <v/>
       </c>
       <c r="N326" s="7"/>
-    </row>
-    <row r="327" spans="7:14">
+      <c r="O326" s="9"/>
+    </row>
+    <row r="327" spans="7:15">
       <c r="G327" s="4"/>
       <c r="K327" s="4"/>
       <c r="M327" s="4" t="str">
@@ -4196,8 +4516,9 @@
         <v/>
       </c>
       <c r="N327" s="7"/>
-    </row>
-    <row r="328" spans="7:14">
+      <c r="O327" s="9"/>
+    </row>
+    <row r="328" spans="7:15">
       <c r="G328" s="4"/>
       <c r="K328" s="4"/>
       <c r="M328" s="4" t="str">
@@ -4205,8 +4526,9 @@
         <v/>
       </c>
       <c r="N328" s="7"/>
-    </row>
-    <row r="329" spans="7:14">
+      <c r="O328" s="9"/>
+    </row>
+    <row r="329" spans="7:15">
       <c r="G329" s="4"/>
       <c r="K329" s="4"/>
       <c r="M329" s="4" t="str">
@@ -4214,8 +4536,9 @@
         <v/>
       </c>
       <c r="N329" s="7"/>
-    </row>
-    <row r="330" spans="7:14">
+      <c r="O329" s="9"/>
+    </row>
+    <row r="330" spans="7:15">
       <c r="G330" s="4"/>
       <c r="K330" s="4"/>
       <c r="M330" s="4" t="str">
@@ -4223,8 +4546,9 @@
         <v/>
       </c>
       <c r="N330" s="7"/>
-    </row>
-    <row r="331" spans="7:14">
+      <c r="O330" s="9"/>
+    </row>
+    <row r="331" spans="7:15">
       <c r="G331" s="4"/>
       <c r="K331" s="4"/>
       <c r="M331" s="4" t="str">
@@ -4232,8 +4556,9 @@
         <v/>
       </c>
       <c r="N331" s="7"/>
-    </row>
-    <row r="332" spans="7:14">
+      <c r="O331" s="9"/>
+    </row>
+    <row r="332" spans="7:15">
       <c r="G332" s="4"/>
       <c r="K332" s="4"/>
       <c r="M332" s="4" t="str">
@@ -4241,8 +4566,9 @@
         <v/>
       </c>
       <c r="N332" s="7"/>
-    </row>
-    <row r="333" spans="7:14">
+      <c r="O332" s="9"/>
+    </row>
+    <row r="333" spans="7:15">
       <c r="G333" s="4"/>
       <c r="K333" s="4"/>
       <c r="M333" s="4" t="str">
@@ -4250,8 +4576,9 @@
         <v/>
       </c>
       <c r="N333" s="7"/>
-    </row>
-    <row r="334" spans="7:14">
+      <c r="O333" s="9"/>
+    </row>
+    <row r="334" spans="7:15">
       <c r="G334" s="4"/>
       <c r="K334" s="4"/>
       <c r="M334" s="4" t="str">
@@ -4259,8 +4586,9 @@
         <v/>
       </c>
       <c r="N334" s="7"/>
-    </row>
-    <row r="335" spans="7:14">
+      <c r="O334" s="9"/>
+    </row>
+    <row r="335" spans="7:15">
       <c r="G335" s="4"/>
       <c r="K335" s="4"/>
       <c r="M335" s="4" t="str">
@@ -4268,8 +4596,9 @@
         <v/>
       </c>
       <c r="N335" s="7"/>
-    </row>
-    <row r="336" spans="7:14">
+      <c r="O335" s="9"/>
+    </row>
+    <row r="336" spans="7:15">
       <c r="G336" s="4"/>
       <c r="K336" s="4"/>
       <c r="M336" s="4" t="str">
@@ -4277,8 +4606,9 @@
         <v/>
       </c>
       <c r="N336" s="7"/>
-    </row>
-    <row r="337" spans="7:14">
+      <c r="O336" s="9"/>
+    </row>
+    <row r="337" spans="7:15">
       <c r="G337" s="4"/>
       <c r="K337" s="4"/>
       <c r="M337" s="4" t="str">
@@ -4286,8 +4616,9 @@
         <v/>
       </c>
       <c r="N337" s="7"/>
-    </row>
-    <row r="338" spans="7:14">
+      <c r="O337" s="9"/>
+    </row>
+    <row r="338" spans="7:15">
       <c r="G338" s="4"/>
       <c r="K338" s="4"/>
       <c r="M338" s="4" t="str">
@@ -4295,8 +4626,9 @@
         <v/>
       </c>
       <c r="N338" s="7"/>
-    </row>
-    <row r="339" spans="7:14">
+      <c r="O338" s="9"/>
+    </row>
+    <row r="339" spans="7:15">
       <c r="G339" s="4"/>
       <c r="K339" s="4"/>
       <c r="M339" s="4" t="str">
@@ -4304,8 +4636,9 @@
         <v/>
       </c>
       <c r="N339" s="7"/>
-    </row>
-    <row r="340" spans="7:14">
+      <c r="O339" s="9"/>
+    </row>
+    <row r="340" spans="7:15">
       <c r="G340" s="4"/>
       <c r="K340" s="4"/>
       <c r="M340" s="4" t="str">
@@ -4313,8 +4646,9 @@
         <v/>
       </c>
       <c r="N340" s="7"/>
-    </row>
-    <row r="341" spans="7:14">
+      <c r="O340" s="9"/>
+    </row>
+    <row r="341" spans="7:15">
       <c r="G341" s="4"/>
       <c r="K341" s="4"/>
       <c r="M341" s="4" t="str">
@@ -4322,8 +4656,9 @@
         <v/>
       </c>
       <c r="N341" s="7"/>
-    </row>
-    <row r="342" spans="7:14">
+      <c r="O341" s="9"/>
+    </row>
+    <row r="342" spans="7:15">
       <c r="G342" s="4"/>
       <c r="K342" s="4"/>
       <c r="M342" s="4" t="str">
@@ -4331,8 +4666,9 @@
         <v/>
       </c>
       <c r="N342" s="7"/>
-    </row>
-    <row r="343" spans="7:14">
+      <c r="O342" s="9"/>
+    </row>
+    <row r="343" spans="7:15">
       <c r="G343" s="4"/>
       <c r="K343" s="4"/>
       <c r="M343" s="4" t="str">
@@ -4340,8 +4676,9 @@
         <v/>
       </c>
       <c r="N343" s="7"/>
-    </row>
-    <row r="344" spans="7:14">
+      <c r="O343" s="9"/>
+    </row>
+    <row r="344" spans="7:15">
       <c r="G344" s="4"/>
       <c r="K344" s="4"/>
       <c r="M344" s="4" t="str">
@@ -4349,8 +4686,9 @@
         <v/>
       </c>
       <c r="N344" s="7"/>
-    </row>
-    <row r="345" spans="7:14">
+      <c r="O344" s="9"/>
+    </row>
+    <row r="345" spans="7:15">
       <c r="G345" s="4"/>
       <c r="K345" s="4"/>
       <c r="M345" s="4" t="str">
@@ -4358,8 +4696,9 @@
         <v/>
       </c>
       <c r="N345" s="7"/>
-    </row>
-    <row r="346" spans="7:14">
+      <c r="O345" s="9"/>
+    </row>
+    <row r="346" spans="7:15">
       <c r="G346" s="4"/>
       <c r="K346" s="4"/>
       <c r="M346" s="4" t="str">
@@ -4367,8 +4706,9 @@
         <v/>
       </c>
       <c r="N346" s="7"/>
-    </row>
-    <row r="347" spans="7:14">
+      <c r="O346" s="9"/>
+    </row>
+    <row r="347" spans="7:15">
       <c r="G347" s="4"/>
       <c r="K347" s="4"/>
       <c r="M347" s="4" t="str">
@@ -4376,8 +4716,9 @@
         <v/>
       </c>
       <c r="N347" s="7"/>
-    </row>
-    <row r="348" spans="7:14">
+      <c r="O347" s="9"/>
+    </row>
+    <row r="348" spans="7:15">
       <c r="G348" s="4"/>
       <c r="K348" s="4"/>
       <c r="M348" s="4" t="str">
@@ -4385,8 +4726,9 @@
         <v/>
       </c>
       <c r="N348" s="7"/>
-    </row>
-    <row r="349" spans="7:14">
+      <c r="O348" s="9"/>
+    </row>
+    <row r="349" spans="7:15">
       <c r="G349" s="4"/>
       <c r="K349" s="4"/>
       <c r="M349" s="4" t="str">
@@ -4394,8 +4736,9 @@
         <v/>
       </c>
       <c r="N349" s="7"/>
-    </row>
-    <row r="350" spans="7:14">
+      <c r="O349" s="9"/>
+    </row>
+    <row r="350" spans="7:15">
       <c r="G350" s="4"/>
       <c r="K350" s="4"/>
       <c r="M350" s="4" t="str">
@@ -4403,8 +4746,9 @@
         <v/>
       </c>
       <c r="N350" s="7"/>
-    </row>
-    <row r="351" spans="7:14">
+      <c r="O350" s="10"/>
+    </row>
+    <row r="351" spans="7:15">
       <c r="G351" s="4"/>
       <c r="K351" s="4"/>
       <c r="M351" s="4" t="str">
@@ -4412,8 +4756,9 @@
         <v/>
       </c>
       <c r="N351" s="7"/>
-    </row>
-    <row r="352" spans="7:14">
+      <c r="O351" s="10"/>
+    </row>
+    <row r="352" spans="7:15">
       <c r="G352" s="4"/>
       <c r="K352" s="4"/>
       <c r="M352" s="4" t="str">
@@ -4421,8 +4766,9 @@
         <v/>
       </c>
       <c r="N352" s="7"/>
-    </row>
-    <row r="353" spans="7:14">
+      <c r="O352" s="10"/>
+    </row>
+    <row r="353" spans="7:15">
       <c r="G353" s="4"/>
       <c r="K353" s="4"/>
       <c r="M353" s="4" t="str">
@@ -4430,8 +4776,9 @@
         <v/>
       </c>
       <c r="N353" s="7"/>
-    </row>
-    <row r="354" spans="7:14">
+      <c r="O353" s="10"/>
+    </row>
+    <row r="354" spans="7:15">
       <c r="G354" s="4"/>
       <c r="K354" s="4"/>
       <c r="M354" s="4" t="str">
@@ -4439,8 +4786,9 @@
         <v/>
       </c>
       <c r="N354" s="7"/>
-    </row>
-    <row r="355" spans="7:14">
+      <c r="O354" s="10"/>
+    </row>
+    <row r="355" spans="7:15">
       <c r="G355" s="4"/>
       <c r="K355" s="4"/>
       <c r="M355" s="4" t="str">
@@ -4448,8 +4796,9 @@
         <v/>
       </c>
       <c r="N355" s="7"/>
-    </row>
-    <row r="356" spans="7:14">
+      <c r="O355" s="10"/>
+    </row>
+    <row r="356" spans="7:15">
       <c r="G356" s="4"/>
       <c r="K356" s="4"/>
       <c r="M356" s="4" t="str">
@@ -4457,6 +4806,7 @@
         <v/>
       </c>
       <c r="N356" s="7"/>
+      <c r="O356" s="10"/>
     </row>
     <row r="357" spans="7:14">
       <c r="G357" s="4"/>
@@ -10939,7 +11289,7 @@
   <mergeCells count="3">
     <mergeCell ref="A6:G6"/>
     <mergeCell ref="A1:G5"/>
-    <mergeCell ref="I1:N6"/>
+    <mergeCell ref="I1:O6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="portrait"/>

--- a/ReporteChoferes.xlsx
+++ b/ReporteChoferes.xlsx
@@ -90,9 +90,25 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="28">
     <font>
       <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="24"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="14"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <charset val="134"/>
@@ -106,12 +122,6 @@
     <font>
       <sz val="18"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="14"/>
-      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <charset val="134"/>
     </font>
@@ -287,7 +297,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF000000"/>
+        <fgColor theme="0"/>
         <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
@@ -478,12 +488,27 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -587,26 +612,17 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -615,136 +631,144 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
@@ -1375,7 +1399,7 @@
         <v/>
       </c>
       <c r="N15" s="7"/>
-      <c r="O15" s="9"/>
+      <c r="O15" s="8"/>
     </row>
     <row r="16" customHeight="1" spans="7:18">
       <c r="G16" s="4"/>
@@ -1476,7 +1500,7 @@
         <v/>
       </c>
       <c r="N23" s="7"/>
-      <c r="O23" s="9"/>
+      <c r="O23" s="8"/>
     </row>
     <row r="24" spans="7:15">
       <c r="G24" s="4"/>
@@ -1486,7 +1510,7 @@
         <v/>
       </c>
       <c r="N24" s="7"/>
-      <c r="O24" s="9"/>
+      <c r="O24" s="8"/>
     </row>
     <row r="25" spans="7:15">
       <c r="G25" s="4"/>
@@ -1496,7 +1520,7 @@
         <v/>
       </c>
       <c r="N25" s="7"/>
-      <c r="O25" s="9"/>
+      <c r="O25" s="8"/>
     </row>
     <row r="26" spans="7:15">
       <c r="G26" s="4"/>
@@ -1506,7 +1530,7 @@
         <v/>
       </c>
       <c r="N26" s="7"/>
-      <c r="O26" s="9"/>
+      <c r="O26" s="8"/>
     </row>
     <row r="27" spans="7:15">
       <c r="G27" s="4"/>
@@ -1516,7 +1540,7 @@
         <v/>
       </c>
       <c r="N27" s="7"/>
-      <c r="O27" s="9"/>
+      <c r="O27" s="8"/>
     </row>
     <row r="28" spans="7:15">
       <c r="G28" s="4"/>
@@ -1526,7 +1550,7 @@
         <v/>
       </c>
       <c r="N28" s="7"/>
-      <c r="O28" s="9"/>
+      <c r="O28" s="8"/>
     </row>
     <row r="29" spans="7:15">
       <c r="G29" s="4"/>
@@ -1536,7 +1560,7 @@
         <v/>
       </c>
       <c r="N29" s="7"/>
-      <c r="O29" s="9"/>
+      <c r="O29" s="8"/>
     </row>
     <row r="30" spans="7:15">
       <c r="G30" s="4"/>
@@ -1546,7 +1570,7 @@
         <v/>
       </c>
       <c r="N30" s="7"/>
-      <c r="O30" s="9"/>
+      <c r="O30" s="8"/>
     </row>
     <row r="31" spans="7:15">
       <c r="G31" s="4"/>
@@ -1556,7 +1580,7 @@
         <v/>
       </c>
       <c r="N31" s="7"/>
-      <c r="O31" s="9"/>
+      <c r="O31" s="8"/>
     </row>
     <row r="32" spans="7:15">
       <c r="G32" s="4"/>
@@ -1566,7 +1590,7 @@
         <v/>
       </c>
       <c r="N32" s="7"/>
-      <c r="O32" s="9"/>
+      <c r="O32" s="8"/>
     </row>
     <row r="33" spans="7:15">
       <c r="G33" s="4"/>
@@ -1576,7 +1600,7 @@
         <v/>
       </c>
       <c r="N33" s="7"/>
-      <c r="O33" s="9"/>
+      <c r="O33" s="8"/>
     </row>
     <row r="34" spans="7:15">
       <c r="G34" s="4"/>
@@ -1586,7 +1610,7 @@
         <v/>
       </c>
       <c r="N34" s="7"/>
-      <c r="O34" s="9"/>
+      <c r="O34" s="8"/>
     </row>
     <row r="35" spans="7:15">
       <c r="G35" s="4"/>
@@ -1596,7 +1620,7 @@
         <v/>
       </c>
       <c r="N35" s="7"/>
-      <c r="O35" s="9"/>
+      <c r="O35" s="8"/>
     </row>
     <row r="36" spans="7:15">
       <c r="G36" s="4"/>
@@ -1606,7 +1630,7 @@
         <v/>
       </c>
       <c r="N36" s="7"/>
-      <c r="O36" s="9"/>
+      <c r="O36" s="8"/>
     </row>
     <row r="37" spans="7:15">
       <c r="G37" s="4"/>
@@ -1616,7 +1640,7 @@
         <v/>
       </c>
       <c r="N37" s="7"/>
-      <c r="O37" s="9"/>
+      <c r="O37" s="8"/>
     </row>
     <row r="38" spans="7:15">
       <c r="G38" s="4"/>
@@ -1626,7 +1650,7 @@
         <v/>
       </c>
       <c r="N38" s="7"/>
-      <c r="O38" s="9"/>
+      <c r="O38" s="8"/>
     </row>
     <row r="39" spans="7:15">
       <c r="G39" s="4"/>
@@ -1636,7 +1660,7 @@
         <v/>
       </c>
       <c r="N39" s="7"/>
-      <c r="O39" s="9"/>
+      <c r="O39" s="8"/>
     </row>
     <row r="40" spans="7:15">
       <c r="G40" s="4"/>
@@ -1646,7 +1670,7 @@
         <v/>
       </c>
       <c r="N40" s="7"/>
-      <c r="O40" s="9"/>
+      <c r="O40" s="8"/>
     </row>
     <row r="41" spans="7:15">
       <c r="G41" s="4"/>
@@ -1656,7 +1680,7 @@
         <v/>
       </c>
       <c r="N41" s="7"/>
-      <c r="O41" s="9"/>
+      <c r="O41" s="8"/>
     </row>
     <row r="42" spans="7:15">
       <c r="G42" s="4"/>
@@ -1666,7 +1690,7 @@
         <v/>
       </c>
       <c r="N42" s="7"/>
-      <c r="O42" s="9"/>
+      <c r="O42" s="8"/>
     </row>
     <row r="43" spans="7:15">
       <c r="G43" s="4"/>
@@ -1676,7 +1700,7 @@
         <v/>
       </c>
       <c r="N43" s="7"/>
-      <c r="O43" s="9"/>
+      <c r="O43" s="8"/>
     </row>
     <row r="44" spans="7:15">
       <c r="G44" s="4"/>
@@ -1686,7 +1710,7 @@
         <v/>
       </c>
       <c r="N44" s="7"/>
-      <c r="O44" s="9"/>
+      <c r="O44" s="8"/>
     </row>
     <row r="45" spans="7:15">
       <c r="G45" s="4"/>
@@ -1696,7 +1720,7 @@
         <v/>
       </c>
       <c r="N45" s="7"/>
-      <c r="O45" s="9"/>
+      <c r="O45" s="8"/>
     </row>
     <row r="46" spans="7:15">
       <c r="G46" s="4"/>
@@ -1706,7 +1730,7 @@
         <v/>
       </c>
       <c r="N46" s="7"/>
-      <c r="O46" s="9"/>
+      <c r="O46" s="8"/>
     </row>
     <row r="47" spans="7:15">
       <c r="G47" s="4"/>
@@ -1716,7 +1740,7 @@
         <v/>
       </c>
       <c r="N47" s="7"/>
-      <c r="O47" s="9"/>
+      <c r="O47" s="8"/>
     </row>
     <row r="48" spans="7:15">
       <c r="G48" s="4"/>
@@ -1726,7 +1750,7 @@
         <v/>
       </c>
       <c r="N48" s="7"/>
-      <c r="O48" s="9"/>
+      <c r="O48" s="8"/>
     </row>
     <row r="49" spans="7:15">
       <c r="G49" s="4"/>
@@ -1736,7 +1760,7 @@
         <v/>
       </c>
       <c r="N49" s="7"/>
-      <c r="O49" s="9"/>
+      <c r="O49" s="8"/>
     </row>
     <row r="50" spans="7:15">
       <c r="G50" s="4"/>
@@ -1746,7 +1770,7 @@
         <v/>
       </c>
       <c r="N50" s="7"/>
-      <c r="O50" s="9"/>
+      <c r="O50" s="8"/>
     </row>
     <row r="51" spans="7:15">
       <c r="G51" s="4"/>
@@ -1756,7 +1780,7 @@
         <v/>
       </c>
       <c r="N51" s="7"/>
-      <c r="O51" s="9"/>
+      <c r="O51" s="8"/>
     </row>
     <row r="52" spans="7:15">
       <c r="G52" s="4"/>
@@ -1766,7 +1790,7 @@
         <v/>
       </c>
       <c r="N52" s="7"/>
-      <c r="O52" s="9"/>
+      <c r="O52" s="8"/>
     </row>
     <row r="53" spans="7:15">
       <c r="G53" s="4"/>
@@ -1776,7 +1800,7 @@
         <v/>
       </c>
       <c r="N53" s="7"/>
-      <c r="O53" s="9"/>
+      <c r="O53" s="8"/>
     </row>
     <row r="54" spans="7:15">
       <c r="G54" s="4"/>
@@ -1786,7 +1810,7 @@
         <v/>
       </c>
       <c r="N54" s="7"/>
-      <c r="O54" s="9"/>
+      <c r="O54" s="8"/>
     </row>
     <row r="55" spans="7:15">
       <c r="G55" s="4"/>
@@ -1796,7 +1820,7 @@
         <v/>
       </c>
       <c r="N55" s="7"/>
-      <c r="O55" s="9"/>
+      <c r="O55" s="8"/>
     </row>
     <row r="56" spans="7:15">
       <c r="G56" s="4"/>
@@ -1806,7 +1830,7 @@
         <v/>
       </c>
       <c r="N56" s="7"/>
-      <c r="O56" s="9"/>
+      <c r="O56" s="8"/>
     </row>
     <row r="57" spans="7:15">
       <c r="G57" s="4"/>
@@ -1816,7 +1840,7 @@
         <v/>
       </c>
       <c r="N57" s="7"/>
-      <c r="O57" s="9"/>
+      <c r="O57" s="8"/>
     </row>
     <row r="58" spans="7:15">
       <c r="G58" s="4"/>
@@ -1826,7 +1850,7 @@
         <v/>
       </c>
       <c r="N58" s="7"/>
-      <c r="O58" s="9"/>
+      <c r="O58" s="8"/>
     </row>
     <row r="59" spans="7:15">
       <c r="G59" s="4"/>
@@ -1836,7 +1860,7 @@
         <v/>
       </c>
       <c r="N59" s="7"/>
-      <c r="O59" s="9"/>
+      <c r="O59" s="8"/>
     </row>
     <row r="60" spans="7:15">
       <c r="G60" s="4"/>
@@ -1846,7 +1870,7 @@
         <v/>
       </c>
       <c r="N60" s="7"/>
-      <c r="O60" s="9"/>
+      <c r="O60" s="8"/>
     </row>
     <row r="61" spans="7:15">
       <c r="G61" s="4"/>
@@ -1856,7 +1880,7 @@
         <v/>
       </c>
       <c r="N61" s="7"/>
-      <c r="O61" s="9"/>
+      <c r="O61" s="8"/>
     </row>
     <row r="62" spans="7:15">
       <c r="G62" s="4"/>
@@ -1866,7 +1890,7 @@
         <v/>
       </c>
       <c r="N62" s="7"/>
-      <c r="O62" s="9"/>
+      <c r="O62" s="8"/>
     </row>
     <row r="63" spans="7:15">
       <c r="G63" s="4"/>
@@ -1876,7 +1900,7 @@
         <v/>
       </c>
       <c r="N63" s="7"/>
-      <c r="O63" s="9"/>
+      <c r="O63" s="8"/>
     </row>
     <row r="64" spans="7:15">
       <c r="G64" s="4"/>
@@ -1886,7 +1910,7 @@
         <v/>
       </c>
       <c r="N64" s="7"/>
-      <c r="O64" s="9"/>
+      <c r="O64" s="8"/>
     </row>
     <row r="65" spans="7:15">
       <c r="G65" s="4"/>
@@ -1896,7 +1920,7 @@
         <v/>
       </c>
       <c r="N65" s="7"/>
-      <c r="O65" s="9"/>
+      <c r="O65" s="8"/>
     </row>
     <row r="66" spans="7:15">
       <c r="G66" s="4"/>
@@ -1906,7 +1930,7 @@
         <v/>
       </c>
       <c r="N66" s="7"/>
-      <c r="O66" s="9"/>
+      <c r="O66" s="8"/>
     </row>
     <row r="67" spans="7:15">
       <c r="G67" s="4"/>
@@ -1916,7 +1940,7 @@
         <v/>
       </c>
       <c r="N67" s="7"/>
-      <c r="O67" s="9"/>
+      <c r="O67" s="8"/>
     </row>
     <row r="68" spans="7:15">
       <c r="G68" s="4"/>
@@ -1926,7 +1950,7 @@
         <v/>
       </c>
       <c r="N68" s="7"/>
-      <c r="O68" s="9"/>
+      <c r="O68" s="8"/>
     </row>
     <row r="69" spans="7:15">
       <c r="G69" s="4"/>
@@ -1936,7 +1960,7 @@
         <v/>
       </c>
       <c r="N69" s="7"/>
-      <c r="O69" s="9"/>
+      <c r="O69" s="8"/>
     </row>
     <row r="70" spans="7:15">
       <c r="G70" s="4"/>
@@ -1946,7 +1970,7 @@
         <v/>
       </c>
       <c r="N70" s="7"/>
-      <c r="O70" s="9"/>
+      <c r="O70" s="8"/>
     </row>
     <row r="71" spans="7:15">
       <c r="G71" s="4"/>
@@ -1956,7 +1980,7 @@
         <v/>
       </c>
       <c r="N71" s="7"/>
-      <c r="O71" s="9"/>
+      <c r="O71" s="8"/>
     </row>
     <row r="72" spans="7:15">
       <c r="G72" s="4"/>
@@ -1966,7 +1990,7 @@
         <v/>
       </c>
       <c r="N72" s="7"/>
-      <c r="O72" s="9"/>
+      <c r="O72" s="8"/>
     </row>
     <row r="73" spans="7:15">
       <c r="G73" s="4"/>
@@ -1976,7 +2000,7 @@
         <v/>
       </c>
       <c r="N73" s="7"/>
-      <c r="O73" s="9"/>
+      <c r="O73" s="8"/>
     </row>
     <row r="74" spans="7:15">
       <c r="G74" s="4"/>
@@ -1986,7 +2010,7 @@
         <v/>
       </c>
       <c r="N74" s="7"/>
-      <c r="O74" s="9"/>
+      <c r="O74" s="8"/>
     </row>
     <row r="75" spans="7:15">
       <c r="G75" s="4"/>
@@ -1996,7 +2020,7 @@
         <v/>
       </c>
       <c r="N75" s="7"/>
-      <c r="O75" s="9"/>
+      <c r="O75" s="8"/>
     </row>
     <row r="76" spans="7:15">
       <c r="G76" s="4"/>
@@ -2006,7 +2030,7 @@
         <v/>
       </c>
       <c r="N76" s="7"/>
-      <c r="O76" s="9"/>
+      <c r="O76" s="8"/>
     </row>
     <row r="77" spans="7:15">
       <c r="G77" s="4"/>
@@ -2016,7 +2040,7 @@
         <v/>
       </c>
       <c r="N77" s="7"/>
-      <c r="O77" s="9"/>
+      <c r="O77" s="8"/>
     </row>
     <row r="78" spans="7:15">
       <c r="G78" s="4"/>
@@ -2026,7 +2050,7 @@
         <v/>
       </c>
       <c r="N78" s="7"/>
-      <c r="O78" s="9"/>
+      <c r="O78" s="8"/>
     </row>
     <row r="79" spans="7:15">
       <c r="G79" s="4"/>
@@ -2036,7 +2060,7 @@
         <v/>
       </c>
       <c r="N79" s="7"/>
-      <c r="O79" s="9"/>
+      <c r="O79" s="8"/>
     </row>
     <row r="80" spans="7:15">
       <c r="G80" s="4"/>
@@ -2046,7 +2070,7 @@
         <v/>
       </c>
       <c r="N80" s="7"/>
-      <c r="O80" s="9"/>
+      <c r="O80" s="8"/>
     </row>
     <row r="81" spans="7:15">
       <c r="G81" s="4"/>
@@ -2056,7 +2080,7 @@
         <v/>
       </c>
       <c r="N81" s="7"/>
-      <c r="O81" s="9"/>
+      <c r="O81" s="8"/>
     </row>
     <row r="82" spans="7:15">
       <c r="G82" s="4"/>
@@ -2066,7 +2090,7 @@
         <v/>
       </c>
       <c r="N82" s="7"/>
-      <c r="O82" s="9"/>
+      <c r="O82" s="8"/>
     </row>
     <row r="83" spans="7:15">
       <c r="G83" s="4"/>
@@ -2076,7 +2100,7 @@
         <v/>
       </c>
       <c r="N83" s="7"/>
-      <c r="O83" s="9"/>
+      <c r="O83" s="8"/>
     </row>
     <row r="84" spans="7:15">
       <c r="G84" s="4"/>
@@ -2086,7 +2110,7 @@
         <v/>
       </c>
       <c r="N84" s="7"/>
-      <c r="O84" s="9"/>
+      <c r="O84" s="8"/>
     </row>
     <row r="85" spans="7:15">
       <c r="G85" s="4"/>
@@ -2096,7 +2120,7 @@
         <v/>
       </c>
       <c r="N85" s="7"/>
-      <c r="O85" s="9"/>
+      <c r="O85" s="8"/>
     </row>
     <row r="86" spans="7:15">
       <c r="G86" s="4"/>
@@ -2106,7 +2130,7 @@
         <v/>
       </c>
       <c r="N86" s="7"/>
-      <c r="O86" s="9"/>
+      <c r="O86" s="8"/>
     </row>
     <row r="87" spans="7:15">
       <c r="G87" s="4"/>
@@ -2116,7 +2140,7 @@
         <v/>
       </c>
       <c r="N87" s="7"/>
-      <c r="O87" s="9"/>
+      <c r="O87" s="8"/>
     </row>
     <row r="88" spans="7:15">
       <c r="G88" s="4"/>
@@ -2126,7 +2150,7 @@
         <v/>
       </c>
       <c r="N88" s="7"/>
-      <c r="O88" s="9"/>
+      <c r="O88" s="8"/>
     </row>
     <row r="89" spans="7:15">
       <c r="G89" s="4"/>
@@ -2136,7 +2160,7 @@
         <v/>
       </c>
       <c r="N89" s="7"/>
-      <c r="O89" s="9"/>
+      <c r="O89" s="8"/>
     </row>
     <row r="90" spans="7:15">
       <c r="G90" s="4"/>
@@ -2146,7 +2170,7 @@
         <v/>
       </c>
       <c r="N90" s="7"/>
-      <c r="O90" s="9"/>
+      <c r="O90" s="8"/>
     </row>
     <row r="91" spans="7:15">
       <c r="G91" s="4"/>
@@ -2156,7 +2180,7 @@
         <v/>
       </c>
       <c r="N91" s="7"/>
-      <c r="O91" s="9"/>
+      <c r="O91" s="8"/>
     </row>
     <row r="92" spans="7:15">
       <c r="G92" s="4"/>
@@ -2166,7 +2190,7 @@
         <v/>
       </c>
       <c r="N92" s="7"/>
-      <c r="O92" s="9"/>
+      <c r="O92" s="8"/>
     </row>
     <row r="93" spans="7:15">
       <c r="G93" s="4"/>
@@ -2176,7 +2200,7 @@
         <v/>
       </c>
       <c r="N93" s="7"/>
-      <c r="O93" s="9"/>
+      <c r="O93" s="8"/>
     </row>
     <row r="94" spans="7:15">
       <c r="G94" s="4"/>
@@ -2186,7 +2210,7 @@
         <v/>
       </c>
       <c r="N94" s="7"/>
-      <c r="O94" s="9"/>
+      <c r="O94" s="8"/>
     </row>
     <row r="95" spans="7:15">
       <c r="G95" s="4"/>
@@ -2196,7 +2220,7 @@
         <v/>
       </c>
       <c r="N95" s="7"/>
-      <c r="O95" s="9"/>
+      <c r="O95" s="8"/>
     </row>
     <row r="96" spans="7:15">
       <c r="G96" s="4"/>
@@ -2206,7 +2230,7 @@
         <v/>
       </c>
       <c r="N96" s="7"/>
-      <c r="O96" s="9"/>
+      <c r="O96" s="8"/>
     </row>
     <row r="97" spans="7:15">
       <c r="G97" s="4"/>
@@ -2216,7 +2240,7 @@
         <v/>
       </c>
       <c r="N97" s="7"/>
-      <c r="O97" s="9"/>
+      <c r="O97" s="8"/>
     </row>
     <row r="98" spans="7:15">
       <c r="G98" s="4"/>
@@ -2226,7 +2250,7 @@
         <v/>
       </c>
       <c r="N98" s="7"/>
-      <c r="O98" s="9"/>
+      <c r="O98" s="8"/>
     </row>
     <row r="99" spans="7:15">
       <c r="G99" s="4"/>
@@ -2236,7 +2260,7 @@
         <v/>
       </c>
       <c r="N99" s="7"/>
-      <c r="O99" s="9"/>
+      <c r="O99" s="8"/>
     </row>
     <row r="100" spans="7:15">
       <c r="G100" s="4"/>
@@ -2246,7 +2270,7 @@
         <v/>
       </c>
       <c r="N100" s="7"/>
-      <c r="O100" s="9"/>
+      <c r="O100" s="8"/>
     </row>
     <row r="101" spans="7:15">
       <c r="G101" s="4"/>
@@ -2256,7 +2280,7 @@
         <v/>
       </c>
       <c r="N101" s="7"/>
-      <c r="O101" s="9"/>
+      <c r="O101" s="8"/>
     </row>
     <row r="102" spans="7:15">
       <c r="G102" s="4"/>
@@ -2266,7 +2290,7 @@
         <v/>
       </c>
       <c r="N102" s="7"/>
-      <c r="O102" s="9"/>
+      <c r="O102" s="8"/>
     </row>
     <row r="103" spans="7:15">
       <c r="G103" s="4"/>
@@ -2276,7 +2300,7 @@
         <v/>
       </c>
       <c r="N103" s="7"/>
-      <c r="O103" s="9"/>
+      <c r="O103" s="8"/>
     </row>
     <row r="104" spans="7:15">
       <c r="G104" s="4"/>
@@ -2286,7 +2310,7 @@
         <v/>
       </c>
       <c r="N104" s="7"/>
-      <c r="O104" s="9"/>
+      <c r="O104" s="8"/>
     </row>
     <row r="105" spans="7:15">
       <c r="G105" s="4"/>
@@ -2296,7 +2320,7 @@
         <v/>
       </c>
       <c r="N105" s="7"/>
-      <c r="O105" s="9"/>
+      <c r="O105" s="8"/>
     </row>
     <row r="106" spans="7:15">
       <c r="G106" s="4"/>
@@ -2306,7 +2330,7 @@
         <v/>
       </c>
       <c r="N106" s="7"/>
-      <c r="O106" s="9"/>
+      <c r="O106" s="8"/>
     </row>
     <row r="107" spans="7:15">
       <c r="G107" s="4"/>
@@ -2316,7 +2340,7 @@
         <v/>
       </c>
       <c r="N107" s="7"/>
-      <c r="O107" s="9"/>
+      <c r="O107" s="8"/>
     </row>
     <row r="108" spans="7:15">
       <c r="G108" s="4"/>
@@ -2326,7 +2350,7 @@
         <v/>
       </c>
       <c r="N108" s="7"/>
-      <c r="O108" s="9"/>
+      <c r="O108" s="8"/>
     </row>
     <row r="109" spans="7:15">
       <c r="G109" s="4"/>
@@ -2336,7 +2360,7 @@
         <v/>
       </c>
       <c r="N109" s="7"/>
-      <c r="O109" s="9"/>
+      <c r="O109" s="8"/>
     </row>
     <row r="110" spans="7:15">
       <c r="G110" s="4"/>
@@ -2346,7 +2370,7 @@
         <v/>
       </c>
       <c r="N110" s="7"/>
-      <c r="O110" s="9"/>
+      <c r="O110" s="8"/>
     </row>
     <row r="111" spans="7:15">
       <c r="G111" s="4"/>
@@ -2356,7 +2380,7 @@
         <v/>
       </c>
       <c r="N111" s="7"/>
-      <c r="O111" s="9"/>
+      <c r="O111" s="8"/>
     </row>
     <row r="112" spans="7:15">
       <c r="G112" s="4"/>
@@ -2366,7 +2390,7 @@
         <v/>
       </c>
       <c r="N112" s="7"/>
-      <c r="O112" s="9"/>
+      <c r="O112" s="8"/>
     </row>
     <row r="113" spans="7:15">
       <c r="G113" s="4"/>
@@ -2376,7 +2400,7 @@
         <v/>
       </c>
       <c r="N113" s="7"/>
-      <c r="O113" s="9"/>
+      <c r="O113" s="8"/>
     </row>
     <row r="114" spans="7:15">
       <c r="G114" s="4"/>
@@ -2386,7 +2410,7 @@
         <v/>
       </c>
       <c r="N114" s="7"/>
-      <c r="O114" s="9"/>
+      <c r="O114" s="8"/>
     </row>
     <row r="115" spans="7:15">
       <c r="G115" s="4"/>
@@ -2396,7 +2420,7 @@
         <v/>
       </c>
       <c r="N115" s="7"/>
-      <c r="O115" s="9"/>
+      <c r="O115" s="8"/>
     </row>
     <row r="116" spans="7:15">
       <c r="G116" s="4"/>
@@ -2406,7 +2430,7 @@
         <v/>
       </c>
       <c r="N116" s="7"/>
-      <c r="O116" s="9"/>
+      <c r="O116" s="8"/>
     </row>
     <row r="117" spans="7:15">
       <c r="G117" s="4"/>
@@ -2416,7 +2440,7 @@
         <v/>
       </c>
       <c r="N117" s="7"/>
-      <c r="O117" s="9"/>
+      <c r="O117" s="8"/>
     </row>
     <row r="118" spans="7:15">
       <c r="G118" s="4"/>
@@ -2426,7 +2450,7 @@
         <v/>
       </c>
       <c r="N118" s="7"/>
-      <c r="O118" s="9"/>
+      <c r="O118" s="8"/>
     </row>
     <row r="119" spans="7:15">
       <c r="G119" s="4"/>
@@ -2436,7 +2460,7 @@
         <v/>
       </c>
       <c r="N119" s="7"/>
-      <c r="O119" s="9"/>
+      <c r="O119" s="8"/>
     </row>
     <row r="120" spans="7:15">
       <c r="G120" s="4"/>
@@ -2446,7 +2470,7 @@
         <v/>
       </c>
       <c r="N120" s="7"/>
-      <c r="O120" s="9"/>
+      <c r="O120" s="8"/>
     </row>
     <row r="121" spans="7:15">
       <c r="G121" s="4"/>
@@ -2456,7 +2480,7 @@
         <v/>
       </c>
       <c r="N121" s="7"/>
-      <c r="O121" s="9"/>
+      <c r="O121" s="8"/>
     </row>
     <row r="122" spans="7:15">
       <c r="G122" s="4"/>
@@ -2466,7 +2490,7 @@
         <v/>
       </c>
       <c r="N122" s="7"/>
-      <c r="O122" s="9"/>
+      <c r="O122" s="8"/>
     </row>
     <row r="123" spans="7:15">
       <c r="G123" s="4"/>
@@ -2476,7 +2500,7 @@
         <v/>
       </c>
       <c r="N123" s="7"/>
-      <c r="O123" s="9"/>
+      <c r="O123" s="8"/>
     </row>
     <row r="124" spans="7:15">
       <c r="G124" s="4"/>
@@ -2486,7 +2510,7 @@
         <v/>
       </c>
       <c r="N124" s="7"/>
-      <c r="O124" s="9"/>
+      <c r="O124" s="8"/>
     </row>
     <row r="125" spans="7:15">
       <c r="G125" s="4"/>
@@ -2496,7 +2520,7 @@
         <v/>
       </c>
       <c r="N125" s="7"/>
-      <c r="O125" s="9"/>
+      <c r="O125" s="8"/>
     </row>
     <row r="126" spans="7:15">
       <c r="G126" s="4"/>
@@ -2506,7 +2530,7 @@
         <v/>
       </c>
       <c r="N126" s="7"/>
-      <c r="O126" s="9"/>
+      <c r="O126" s="8"/>
     </row>
     <row r="127" spans="7:15">
       <c r="G127" s="4"/>
@@ -2516,7 +2540,7 @@
         <v/>
       </c>
       <c r="N127" s="7"/>
-      <c r="O127" s="9"/>
+      <c r="O127" s="8"/>
     </row>
     <row r="128" spans="7:15">
       <c r="G128" s="4"/>
@@ -2526,7 +2550,7 @@
         <v/>
       </c>
       <c r="N128" s="7"/>
-      <c r="O128" s="9"/>
+      <c r="O128" s="8"/>
     </row>
     <row r="129" spans="7:15">
       <c r="G129" s="4"/>
@@ -2536,7 +2560,7 @@
         <v/>
       </c>
       <c r="N129" s="7"/>
-      <c r="O129" s="9"/>
+      <c r="O129" s="8"/>
     </row>
     <row r="130" spans="7:15">
       <c r="G130" s="4"/>
@@ -2546,7 +2570,7 @@
         <v/>
       </c>
       <c r="N130" s="7"/>
-      <c r="O130" s="9"/>
+      <c r="O130" s="8"/>
     </row>
     <row r="131" spans="7:15">
       <c r="G131" s="4"/>
@@ -2556,7 +2580,7 @@
         <v/>
       </c>
       <c r="N131" s="7"/>
-      <c r="O131" s="9"/>
+      <c r="O131" s="8"/>
     </row>
     <row r="132" spans="7:15">
       <c r="G132" s="4"/>
@@ -2566,7 +2590,7 @@
         <v/>
       </c>
       <c r="N132" s="7"/>
-      <c r="O132" s="9"/>
+      <c r="O132" s="8"/>
     </row>
     <row r="133" spans="7:15">
       <c r="G133" s="4"/>
@@ -2576,7 +2600,7 @@
         <v/>
       </c>
       <c r="N133" s="7"/>
-      <c r="O133" s="9"/>
+      <c r="O133" s="8"/>
     </row>
     <row r="134" spans="7:15">
       <c r="G134" s="4"/>
@@ -2586,7 +2610,7 @@
         <v/>
       </c>
       <c r="N134" s="7"/>
-      <c r="O134" s="9"/>
+      <c r="O134" s="8"/>
     </row>
     <row r="135" spans="7:15">
       <c r="G135" s="4"/>
@@ -2596,7 +2620,7 @@
         <v/>
       </c>
       <c r="N135" s="7"/>
-      <c r="O135" s="9"/>
+      <c r="O135" s="8"/>
     </row>
     <row r="136" spans="7:15">
       <c r="G136" s="4"/>
@@ -2606,7 +2630,7 @@
         <v/>
       </c>
       <c r="N136" s="7"/>
-      <c r="O136" s="9"/>
+      <c r="O136" s="8"/>
     </row>
     <row r="137" spans="7:15">
       <c r="G137" s="4"/>
@@ -2616,7 +2640,7 @@
         <v/>
       </c>
       <c r="N137" s="7"/>
-      <c r="O137" s="9"/>
+      <c r="O137" s="8"/>
     </row>
     <row r="138" spans="7:15">
       <c r="G138" s="4"/>
@@ -2626,7 +2650,7 @@
         <v/>
       </c>
       <c r="N138" s="7"/>
-      <c r="O138" s="9"/>
+      <c r="O138" s="8"/>
     </row>
     <row r="139" spans="7:15">
       <c r="G139" s="4"/>
@@ -2636,7 +2660,7 @@
         <v/>
       </c>
       <c r="N139" s="7"/>
-      <c r="O139" s="9"/>
+      <c r="O139" s="8"/>
     </row>
     <row r="140" spans="7:15">
       <c r="G140" s="4"/>
@@ -2646,7 +2670,7 @@
         <v/>
       </c>
       <c r="N140" s="7"/>
-      <c r="O140" s="9"/>
+      <c r="O140" s="8"/>
     </row>
     <row r="141" spans="7:15">
       <c r="G141" s="4"/>
@@ -2656,7 +2680,7 @@
         <v/>
       </c>
       <c r="N141" s="7"/>
-      <c r="O141" s="9"/>
+      <c r="O141" s="8"/>
     </row>
     <row r="142" spans="7:15">
       <c r="G142" s="4"/>
@@ -2666,7 +2690,7 @@
         <v/>
       </c>
       <c r="N142" s="7"/>
-      <c r="O142" s="9"/>
+      <c r="O142" s="8"/>
     </row>
     <row r="143" spans="7:15">
       <c r="G143" s="4"/>
@@ -2676,7 +2700,7 @@
         <v/>
       </c>
       <c r="N143" s="7"/>
-      <c r="O143" s="9"/>
+      <c r="O143" s="8"/>
     </row>
     <row r="144" spans="7:15">
       <c r="G144" s="4"/>
@@ -2686,7 +2710,7 @@
         <v/>
       </c>
       <c r="N144" s="7"/>
-      <c r="O144" s="9"/>
+      <c r="O144" s="8"/>
     </row>
     <row r="145" spans="7:15">
       <c r="G145" s="4"/>
@@ -2696,7 +2720,7 @@
         <v/>
       </c>
       <c r="N145" s="7"/>
-      <c r="O145" s="9"/>
+      <c r="O145" s="8"/>
     </row>
     <row r="146" spans="7:15">
       <c r="G146" s="4"/>
@@ -2706,7 +2730,7 @@
         <v/>
       </c>
       <c r="N146" s="7"/>
-      <c r="O146" s="9"/>
+      <c r="O146" s="8"/>
     </row>
     <row r="147" spans="7:15">
       <c r="G147" s="4"/>
@@ -2716,7 +2740,7 @@
         <v/>
       </c>
       <c r="N147" s="7"/>
-      <c r="O147" s="9"/>
+      <c r="O147" s="8"/>
     </row>
     <row r="148" spans="7:15">
       <c r="G148" s="4"/>
@@ -2726,7 +2750,7 @@
         <v/>
       </c>
       <c r="N148" s="7"/>
-      <c r="O148" s="9"/>
+      <c r="O148" s="8"/>
     </row>
     <row r="149" spans="7:15">
       <c r="G149" s="4"/>
@@ -2736,7 +2760,7 @@
         <v/>
       </c>
       <c r="N149" s="7"/>
-      <c r="O149" s="9"/>
+      <c r="O149" s="8"/>
     </row>
     <row r="150" spans="7:15">
       <c r="G150" s="4"/>
@@ -2746,7 +2770,7 @@
         <v/>
       </c>
       <c r="N150" s="7"/>
-      <c r="O150" s="9"/>
+      <c r="O150" s="8"/>
     </row>
     <row r="151" spans="7:15">
       <c r="G151" s="4"/>
@@ -2756,7 +2780,7 @@
         <v/>
       </c>
       <c r="N151" s="7"/>
-      <c r="O151" s="9"/>
+      <c r="O151" s="8"/>
     </row>
     <row r="152" spans="7:15">
       <c r="G152" s="4"/>
@@ -2766,7 +2790,7 @@
         <v/>
       </c>
       <c r="N152" s="7"/>
-      <c r="O152" s="9"/>
+      <c r="O152" s="8"/>
     </row>
     <row r="153" spans="7:15">
       <c r="G153" s="4"/>
@@ -2776,7 +2800,7 @@
         <v/>
       </c>
       <c r="N153" s="7"/>
-      <c r="O153" s="9"/>
+      <c r="O153" s="8"/>
     </row>
     <row r="154" spans="7:15">
       <c r="G154" s="4"/>
@@ -2786,7 +2810,7 @@
         <v/>
       </c>
       <c r="N154" s="7"/>
-      <c r="O154" s="9"/>
+      <c r="O154" s="8"/>
     </row>
     <row r="155" spans="7:15">
       <c r="G155" s="4"/>
@@ -2796,7 +2820,7 @@
         <v/>
       </c>
       <c r="N155" s="7"/>
-      <c r="O155" s="9"/>
+      <c r="O155" s="8"/>
     </row>
     <row r="156" spans="7:15">
       <c r="G156" s="4"/>
@@ -2806,7 +2830,7 @@
         <v/>
       </c>
       <c r="N156" s="7"/>
-      <c r="O156" s="9"/>
+      <c r="O156" s="8"/>
     </row>
     <row r="157" spans="7:15">
       <c r="G157" s="4"/>
@@ -2816,7 +2840,7 @@
         <v/>
       </c>
       <c r="N157" s="7"/>
-      <c r="O157" s="9"/>
+      <c r="O157" s="8"/>
     </row>
     <row r="158" spans="7:15">
       <c r="G158" s="4"/>
@@ -2826,7 +2850,7 @@
         <v/>
       </c>
       <c r="N158" s="7"/>
-      <c r="O158" s="9"/>
+      <c r="O158" s="8"/>
     </row>
     <row r="159" spans="7:15">
       <c r="G159" s="4"/>
@@ -2836,7 +2860,7 @@
         <v/>
       </c>
       <c r="N159" s="7"/>
-      <c r="O159" s="9"/>
+      <c r="O159" s="8"/>
     </row>
     <row r="160" spans="7:15">
       <c r="G160" s="4"/>
@@ -2846,7 +2870,7 @@
         <v/>
       </c>
       <c r="N160" s="7"/>
-      <c r="O160" s="9"/>
+      <c r="O160" s="8"/>
     </row>
     <row r="161" spans="7:15">
       <c r="G161" s="4"/>
@@ -2856,7 +2880,7 @@
         <v/>
       </c>
       <c r="N161" s="7"/>
-      <c r="O161" s="9"/>
+      <c r="O161" s="8"/>
     </row>
     <row r="162" spans="7:15">
       <c r="G162" s="4"/>
@@ -2866,7 +2890,7 @@
         <v/>
       </c>
       <c r="N162" s="7"/>
-      <c r="O162" s="9"/>
+      <c r="O162" s="8"/>
     </row>
     <row r="163" spans="7:15">
       <c r="G163" s="4"/>
@@ -2876,7 +2900,7 @@
         <v/>
       </c>
       <c r="N163" s="7"/>
-      <c r="O163" s="9"/>
+      <c r="O163" s="8"/>
     </row>
     <row r="164" spans="7:15">
       <c r="G164" s="4"/>
@@ -2886,7 +2910,7 @@
         <v/>
       </c>
       <c r="N164" s="7"/>
-      <c r="O164" s="9"/>
+      <c r="O164" s="8"/>
     </row>
     <row r="165" spans="7:15">
       <c r="G165" s="4"/>
@@ -2896,7 +2920,7 @@
         <v/>
       </c>
       <c r="N165" s="7"/>
-      <c r="O165" s="9"/>
+      <c r="O165" s="8"/>
     </row>
     <row r="166" spans="7:15">
       <c r="G166" s="4"/>
@@ -2906,7 +2930,7 @@
         <v/>
       </c>
       <c r="N166" s="7"/>
-      <c r="O166" s="9"/>
+      <c r="O166" s="8"/>
     </row>
     <row r="167" spans="7:15">
       <c r="G167" s="4"/>
@@ -2916,7 +2940,7 @@
         <v/>
       </c>
       <c r="N167" s="7"/>
-      <c r="O167" s="9"/>
+      <c r="O167" s="8"/>
     </row>
     <row r="168" spans="7:15">
       <c r="G168" s="4"/>
@@ -2926,7 +2950,7 @@
         <v/>
       </c>
       <c r="N168" s="7"/>
-      <c r="O168" s="9"/>
+      <c r="O168" s="8"/>
     </row>
     <row r="169" spans="7:15">
       <c r="G169" s="4"/>
@@ -2936,7 +2960,7 @@
         <v/>
       </c>
       <c r="N169" s="7"/>
-      <c r="O169" s="9"/>
+      <c r="O169" s="8"/>
     </row>
     <row r="170" spans="7:15">
       <c r="G170" s="4"/>
@@ -2946,7 +2970,7 @@
         <v/>
       </c>
       <c r="N170" s="7"/>
-      <c r="O170" s="9"/>
+      <c r="O170" s="8"/>
     </row>
     <row r="171" spans="7:15">
       <c r="G171" s="4"/>
@@ -2956,7 +2980,7 @@
         <v/>
       </c>
       <c r="N171" s="7"/>
-      <c r="O171" s="9"/>
+      <c r="O171" s="8"/>
     </row>
     <row r="172" spans="7:15">
       <c r="G172" s="4"/>
@@ -2966,7 +2990,7 @@
         <v/>
       </c>
       <c r="N172" s="7"/>
-      <c r="O172" s="9"/>
+      <c r="O172" s="8"/>
     </row>
     <row r="173" spans="7:15">
       <c r="G173" s="4"/>
@@ -2976,7 +3000,7 @@
         <v/>
       </c>
       <c r="N173" s="7"/>
-      <c r="O173" s="9"/>
+      <c r="O173" s="8"/>
     </row>
     <row r="174" spans="7:15">
       <c r="G174" s="4"/>
@@ -2986,7 +3010,7 @@
         <v/>
       </c>
       <c r="N174" s="7"/>
-      <c r="O174" s="9"/>
+      <c r="O174" s="8"/>
     </row>
     <row r="175" spans="7:15">
       <c r="G175" s="4"/>
@@ -2996,7 +3020,7 @@
         <v/>
       </c>
       <c r="N175" s="7"/>
-      <c r="O175" s="9"/>
+      <c r="O175" s="8"/>
     </row>
     <row r="176" spans="7:15">
       <c r="G176" s="4"/>
@@ -3006,7 +3030,7 @@
         <v/>
       </c>
       <c r="N176" s="7"/>
-      <c r="O176" s="9"/>
+      <c r="O176" s="8"/>
     </row>
     <row r="177" spans="7:15">
       <c r="G177" s="4"/>
@@ -3016,7 +3040,7 @@
         <v/>
       </c>
       <c r="N177" s="7"/>
-      <c r="O177" s="9"/>
+      <c r="O177" s="8"/>
     </row>
     <row r="178" spans="7:15">
       <c r="G178" s="4"/>
@@ -3026,7 +3050,7 @@
         <v/>
       </c>
       <c r="N178" s="7"/>
-      <c r="O178" s="9"/>
+      <c r="O178" s="8"/>
     </row>
     <row r="179" spans="7:15">
       <c r="G179" s="4"/>
@@ -3036,7 +3060,7 @@
         <v/>
       </c>
       <c r="N179" s="7"/>
-      <c r="O179" s="9"/>
+      <c r="O179" s="8"/>
     </row>
     <row r="180" spans="7:15">
       <c r="G180" s="4"/>
@@ -3046,7 +3070,7 @@
         <v/>
       </c>
       <c r="N180" s="7"/>
-      <c r="O180" s="9"/>
+      <c r="O180" s="8"/>
     </row>
     <row r="181" spans="7:15">
       <c r="G181" s="4"/>
@@ -3056,7 +3080,7 @@
         <v/>
       </c>
       <c r="N181" s="7"/>
-      <c r="O181" s="9"/>
+      <c r="O181" s="8"/>
     </row>
     <row r="182" spans="7:15">
       <c r="G182" s="4"/>
@@ -3066,7 +3090,7 @@
         <v/>
       </c>
       <c r="N182" s="7"/>
-      <c r="O182" s="9"/>
+      <c r="O182" s="8"/>
     </row>
     <row r="183" spans="7:15">
       <c r="G183" s="4"/>
@@ -3076,7 +3100,7 @@
         <v/>
       </c>
       <c r="N183" s="7"/>
-      <c r="O183" s="9"/>
+      <c r="O183" s="8"/>
     </row>
     <row r="184" spans="7:15">
       <c r="G184" s="4"/>
@@ -3086,7 +3110,7 @@
         <v/>
       </c>
       <c r="N184" s="7"/>
-      <c r="O184" s="9"/>
+      <c r="O184" s="8"/>
     </row>
     <row r="185" spans="7:15">
       <c r="G185" s="4"/>
@@ -3096,7 +3120,7 @@
         <v/>
       </c>
       <c r="N185" s="7"/>
-      <c r="O185" s="9"/>
+      <c r="O185" s="8"/>
     </row>
     <row r="186" spans="7:15">
       <c r="G186" s="4"/>
@@ -3106,7 +3130,7 @@
         <v/>
       </c>
       <c r="N186" s="7"/>
-      <c r="O186" s="9"/>
+      <c r="O186" s="8"/>
     </row>
     <row r="187" spans="7:15">
       <c r="G187" s="4"/>
@@ -3116,7 +3140,7 @@
         <v/>
       </c>
       <c r="N187" s="7"/>
-      <c r="O187" s="9"/>
+      <c r="O187" s="8"/>
     </row>
     <row r="188" spans="7:15">
       <c r="G188" s="4"/>
@@ -3126,7 +3150,7 @@
         <v/>
       </c>
       <c r="N188" s="7"/>
-      <c r="O188" s="9"/>
+      <c r="O188" s="8"/>
     </row>
     <row r="189" spans="7:15">
       <c r="G189" s="4"/>
@@ -3136,7 +3160,7 @@
         <v/>
       </c>
       <c r="N189" s="7"/>
-      <c r="O189" s="9"/>
+      <c r="O189" s="8"/>
     </row>
     <row r="190" spans="7:15">
       <c r="G190" s="4"/>
@@ -3146,7 +3170,7 @@
         <v/>
       </c>
       <c r="N190" s="7"/>
-      <c r="O190" s="9"/>
+      <c r="O190" s="8"/>
     </row>
     <row r="191" spans="7:15">
       <c r="G191" s="4"/>
@@ -3156,7 +3180,7 @@
         <v/>
       </c>
       <c r="N191" s="7"/>
-      <c r="O191" s="9"/>
+      <c r="O191" s="8"/>
     </row>
     <row r="192" spans="7:15">
       <c r="G192" s="4"/>
@@ -3166,7 +3190,7 @@
         <v/>
       </c>
       <c r="N192" s="7"/>
-      <c r="O192" s="9"/>
+      <c r="O192" s="8"/>
     </row>
     <row r="193" spans="7:15">
       <c r="G193" s="4"/>
@@ -3176,7 +3200,7 @@
         <v/>
       </c>
       <c r="N193" s="7"/>
-      <c r="O193" s="9"/>
+      <c r="O193" s="8"/>
     </row>
     <row r="194" spans="7:15">
       <c r="G194" s="4"/>
@@ -3186,7 +3210,7 @@
         <v/>
       </c>
       <c r="N194" s="7"/>
-      <c r="O194" s="9"/>
+      <c r="O194" s="8"/>
     </row>
     <row r="195" spans="7:15">
       <c r="G195" s="4"/>
@@ -3196,7 +3220,7 @@
         <v/>
       </c>
       <c r="N195" s="7"/>
-      <c r="O195" s="9"/>
+      <c r="O195" s="8"/>
     </row>
     <row r="196" spans="7:15">
       <c r="G196" s="4"/>
@@ -3206,7 +3230,7 @@
         <v/>
       </c>
       <c r="N196" s="7"/>
-      <c r="O196" s="9"/>
+      <c r="O196" s="8"/>
     </row>
     <row r="197" spans="7:15">
       <c r="G197" s="4"/>
@@ -3216,7 +3240,7 @@
         <v/>
       </c>
       <c r="N197" s="7"/>
-      <c r="O197" s="9"/>
+      <c r="O197" s="8"/>
     </row>
     <row r="198" spans="7:15">
       <c r="G198" s="4"/>
@@ -3226,7 +3250,7 @@
         <v/>
       </c>
       <c r="N198" s="7"/>
-      <c r="O198" s="9"/>
+      <c r="O198" s="8"/>
     </row>
     <row r="199" spans="7:15">
       <c r="G199" s="4"/>
@@ -3236,7 +3260,7 @@
         <v/>
       </c>
       <c r="N199" s="7"/>
-      <c r="O199" s="9"/>
+      <c r="O199" s="8"/>
     </row>
     <row r="200" spans="7:15">
       <c r="G200" s="4"/>
@@ -3246,7 +3270,7 @@
         <v/>
       </c>
       <c r="N200" s="7"/>
-      <c r="O200" s="9"/>
+      <c r="O200" s="8"/>
     </row>
     <row r="201" spans="7:15">
       <c r="G201" s="4"/>
@@ -3256,7 +3280,7 @@
         <v/>
       </c>
       <c r="N201" s="7"/>
-      <c r="O201" s="9"/>
+      <c r="O201" s="8"/>
     </row>
     <row r="202" spans="7:15">
       <c r="G202" s="4"/>
@@ -3266,7 +3290,7 @@
         <v/>
       </c>
       <c r="N202" s="7"/>
-      <c r="O202" s="9"/>
+      <c r="O202" s="8"/>
     </row>
     <row r="203" spans="7:15">
       <c r="G203" s="4"/>
@@ -3276,7 +3300,7 @@
         <v/>
       </c>
       <c r="N203" s="7"/>
-      <c r="O203" s="9"/>
+      <c r="O203" s="8"/>
     </row>
     <row r="204" spans="7:15">
       <c r="G204" s="4"/>
@@ -3286,7 +3310,7 @@
         <v/>
       </c>
       <c r="N204" s="7"/>
-      <c r="O204" s="9"/>
+      <c r="O204" s="8"/>
     </row>
     <row r="205" spans="7:15">
       <c r="G205" s="4"/>
@@ -3296,7 +3320,7 @@
         <v/>
       </c>
       <c r="N205" s="7"/>
-      <c r="O205" s="9"/>
+      <c r="O205" s="8"/>
     </row>
     <row r="206" spans="7:15">
       <c r="G206" s="4"/>
@@ -3306,7 +3330,7 @@
         <v/>
       </c>
       <c r="N206" s="7"/>
-      <c r="O206" s="9"/>
+      <c r="O206" s="8"/>
     </row>
     <row r="207" spans="7:15">
       <c r="G207" s="4"/>
@@ -3316,7 +3340,7 @@
         <v/>
       </c>
       <c r="N207" s="7"/>
-      <c r="O207" s="9"/>
+      <c r="O207" s="8"/>
     </row>
     <row r="208" spans="7:15">
       <c r="G208" s="4"/>
@@ -3326,7 +3350,7 @@
         <v/>
       </c>
       <c r="N208" s="7"/>
-      <c r="O208" s="9"/>
+      <c r="O208" s="8"/>
     </row>
     <row r="209" spans="7:15">
       <c r="G209" s="4"/>
@@ -3336,7 +3360,7 @@
         <v/>
       </c>
       <c r="N209" s="7"/>
-      <c r="O209" s="9"/>
+      <c r="O209" s="8"/>
     </row>
     <row r="210" spans="7:15">
       <c r="G210" s="4"/>
@@ -3346,7 +3370,7 @@
         <v/>
       </c>
       <c r="N210" s="7"/>
-      <c r="O210" s="9"/>
+      <c r="O210" s="8"/>
     </row>
     <row r="211" spans="7:15">
       <c r="G211" s="4"/>
@@ -3356,7 +3380,7 @@
         <v/>
       </c>
       <c r="N211" s="7"/>
-      <c r="O211" s="9"/>
+      <c r="O211" s="8"/>
     </row>
     <row r="212" spans="7:15">
       <c r="G212" s="4"/>
@@ -3366,7 +3390,7 @@
         <v/>
       </c>
       <c r="N212" s="7"/>
-      <c r="O212" s="9"/>
+      <c r="O212" s="8"/>
     </row>
     <row r="213" spans="7:15">
       <c r="G213" s="4"/>
@@ -3376,7 +3400,7 @@
         <v/>
       </c>
       <c r="N213" s="7"/>
-      <c r="O213" s="9"/>
+      <c r="O213" s="8"/>
     </row>
     <row r="214" spans="7:15">
       <c r="G214" s="4"/>
@@ -3386,7 +3410,7 @@
         <v/>
       </c>
       <c r="N214" s="7"/>
-      <c r="O214" s="9"/>
+      <c r="O214" s="8"/>
     </row>
     <row r="215" spans="7:15">
       <c r="G215" s="4"/>
@@ -3396,7 +3420,7 @@
         <v/>
       </c>
       <c r="N215" s="7"/>
-      <c r="O215" s="9"/>
+      <c r="O215" s="8"/>
     </row>
     <row r="216" spans="7:15">
       <c r="G216" s="4"/>
@@ -3406,7 +3430,7 @@
         <v/>
       </c>
       <c r="N216" s="7"/>
-      <c r="O216" s="9"/>
+      <c r="O216" s="8"/>
     </row>
     <row r="217" spans="7:15">
       <c r="G217" s="4"/>
@@ -3416,7 +3440,7 @@
         <v/>
       </c>
       <c r="N217" s="7"/>
-      <c r="O217" s="9"/>
+      <c r="O217" s="8"/>
     </row>
     <row r="218" spans="7:15">
       <c r="G218" s="4"/>
@@ -3426,7 +3450,7 @@
         <v/>
       </c>
       <c r="N218" s="7"/>
-      <c r="O218" s="9"/>
+      <c r="O218" s="8"/>
     </row>
     <row r="219" spans="7:15">
       <c r="G219" s="4"/>
@@ -3436,7 +3460,7 @@
         <v/>
       </c>
       <c r="N219" s="7"/>
-      <c r="O219" s="9"/>
+      <c r="O219" s="8"/>
     </row>
     <row r="220" spans="7:15">
       <c r="G220" s="4"/>
@@ -3446,7 +3470,7 @@
         <v/>
       </c>
       <c r="N220" s="7"/>
-      <c r="O220" s="9"/>
+      <c r="O220" s="8"/>
     </row>
     <row r="221" spans="7:15">
       <c r="G221" s="4"/>
@@ -3456,7 +3480,7 @@
         <v/>
       </c>
       <c r="N221" s="7"/>
-      <c r="O221" s="9"/>
+      <c r="O221" s="8"/>
     </row>
     <row r="222" spans="7:15">
       <c r="G222" s="4"/>
@@ -3466,7 +3490,7 @@
         <v/>
       </c>
       <c r="N222" s="7"/>
-      <c r="O222" s="9"/>
+      <c r="O222" s="8"/>
     </row>
     <row r="223" spans="7:15">
       <c r="G223" s="4"/>
@@ -3476,7 +3500,7 @@
         <v/>
       </c>
       <c r="N223" s="7"/>
-      <c r="O223" s="9"/>
+      <c r="O223" s="8"/>
     </row>
     <row r="224" spans="7:15">
       <c r="G224" s="4"/>
@@ -3486,7 +3510,7 @@
         <v/>
       </c>
       <c r="N224" s="7"/>
-      <c r="O224" s="9"/>
+      <c r="O224" s="8"/>
     </row>
     <row r="225" spans="7:15">
       <c r="G225" s="4"/>
@@ -3496,7 +3520,7 @@
         <v/>
       </c>
       <c r="N225" s="7"/>
-      <c r="O225" s="9"/>
+      <c r="O225" s="8"/>
     </row>
     <row r="226" spans="7:15">
       <c r="G226" s="4"/>
@@ -3506,7 +3530,7 @@
         <v/>
       </c>
       <c r="N226" s="7"/>
-      <c r="O226" s="9"/>
+      <c r="O226" s="8"/>
     </row>
     <row r="227" spans="7:15">
       <c r="G227" s="4"/>
@@ -3516,7 +3540,7 @@
         <v/>
       </c>
       <c r="N227" s="7"/>
-      <c r="O227" s="9"/>
+      <c r="O227" s="8"/>
     </row>
     <row r="228" spans="7:15">
       <c r="G228" s="4"/>
@@ -3526,7 +3550,7 @@
         <v/>
       </c>
       <c r="N228" s="7"/>
-      <c r="O228" s="9"/>
+      <c r="O228" s="8"/>
     </row>
     <row r="229" spans="7:15">
       <c r="G229" s="4"/>
@@ -3536,7 +3560,7 @@
         <v/>
       </c>
       <c r="N229" s="7"/>
-      <c r="O229" s="9"/>
+      <c r="O229" s="8"/>
     </row>
     <row r="230" spans="7:15">
       <c r="G230" s="4"/>
@@ -3546,7 +3570,7 @@
         <v/>
       </c>
       <c r="N230" s="7"/>
-      <c r="O230" s="9"/>
+      <c r="O230" s="8"/>
     </row>
     <row r="231" spans="7:15">
       <c r="G231" s="4"/>
@@ -3556,7 +3580,7 @@
         <v/>
       </c>
       <c r="N231" s="7"/>
-      <c r="O231" s="9"/>
+      <c r="O231" s="8"/>
     </row>
     <row r="232" spans="7:15">
       <c r="G232" s="4"/>
@@ -3566,7 +3590,7 @@
         <v/>
       </c>
       <c r="N232" s="7"/>
-      <c r="O232" s="9"/>
+      <c r="O232" s="8"/>
     </row>
     <row r="233" spans="7:15">
       <c r="G233" s="4"/>
@@ -3576,7 +3600,7 @@
         <v/>
       </c>
       <c r="N233" s="7"/>
-      <c r="O233" s="9"/>
+      <c r="O233" s="8"/>
     </row>
     <row r="234" spans="7:15">
       <c r="G234" s="4"/>
@@ -3586,7 +3610,7 @@
         <v/>
       </c>
       <c r="N234" s="7"/>
-      <c r="O234" s="9"/>
+      <c r="O234" s="8"/>
     </row>
     <row r="235" spans="7:15">
       <c r="G235" s="4"/>
@@ -3596,7 +3620,7 @@
         <v/>
       </c>
       <c r="N235" s="7"/>
-      <c r="O235" s="9"/>
+      <c r="O235" s="8"/>
     </row>
     <row r="236" spans="7:15">
       <c r="G236" s="4"/>
@@ -3606,7 +3630,7 @@
         <v/>
       </c>
       <c r="N236" s="7"/>
-      <c r="O236" s="9"/>
+      <c r="O236" s="8"/>
     </row>
     <row r="237" spans="7:15">
       <c r="G237" s="4"/>
@@ -3616,7 +3640,7 @@
         <v/>
       </c>
       <c r="N237" s="7"/>
-      <c r="O237" s="9"/>
+      <c r="O237" s="8"/>
     </row>
     <row r="238" spans="7:15">
       <c r="G238" s="4"/>
@@ -3626,7 +3650,7 @@
         <v/>
       </c>
       <c r="N238" s="7"/>
-      <c r="O238" s="9"/>
+      <c r="O238" s="8"/>
     </row>
     <row r="239" spans="7:15">
       <c r="G239" s="4"/>
@@ -3636,7 +3660,7 @@
         <v/>
       </c>
       <c r="N239" s="7"/>
-      <c r="O239" s="9"/>
+      <c r="O239" s="8"/>
     </row>
     <row r="240" spans="7:15">
       <c r="G240" s="4"/>
@@ -3646,7 +3670,7 @@
         <v/>
       </c>
       <c r="N240" s="7"/>
-      <c r="O240" s="9"/>
+      <c r="O240" s="8"/>
     </row>
     <row r="241" spans="7:15">
       <c r="G241" s="4"/>
@@ -3656,7 +3680,7 @@
         <v/>
       </c>
       <c r="N241" s="7"/>
-      <c r="O241" s="9"/>
+      <c r="O241" s="8"/>
     </row>
     <row r="242" spans="7:15">
       <c r="G242" s="4"/>
@@ -3666,7 +3690,7 @@
         <v/>
       </c>
       <c r="N242" s="7"/>
-      <c r="O242" s="9"/>
+      <c r="O242" s="8"/>
     </row>
     <row r="243" spans="7:15">
       <c r="G243" s="4"/>
@@ -3676,7 +3700,7 @@
         <v/>
       </c>
       <c r="N243" s="7"/>
-      <c r="O243" s="9"/>
+      <c r="O243" s="8"/>
     </row>
     <row r="244" spans="7:15">
       <c r="G244" s="4"/>
@@ -3686,7 +3710,7 @@
         <v/>
       </c>
       <c r="N244" s="7"/>
-      <c r="O244" s="9"/>
+      <c r="O244" s="8"/>
     </row>
     <row r="245" spans="7:15">
       <c r="G245" s="4"/>
@@ -3696,7 +3720,7 @@
         <v/>
       </c>
       <c r="N245" s="7"/>
-      <c r="O245" s="9"/>
+      <c r="O245" s="8"/>
     </row>
     <row r="246" spans="7:15">
       <c r="G246" s="4"/>
@@ -3706,7 +3730,7 @@
         <v/>
       </c>
       <c r="N246" s="7"/>
-      <c r="O246" s="9"/>
+      <c r="O246" s="8"/>
     </row>
     <row r="247" spans="7:15">
       <c r="G247" s="4"/>
@@ -3716,7 +3740,7 @@
         <v/>
       </c>
       <c r="N247" s="7"/>
-      <c r="O247" s="9"/>
+      <c r="O247" s="8"/>
     </row>
     <row r="248" spans="7:15">
       <c r="G248" s="4"/>
@@ -3726,7 +3750,7 @@
         <v/>
       </c>
       <c r="N248" s="7"/>
-      <c r="O248" s="9"/>
+      <c r="O248" s="8"/>
     </row>
     <row r="249" spans="7:15">
       <c r="G249" s="4"/>
@@ -3736,7 +3760,7 @@
         <v/>
       </c>
       <c r="N249" s="7"/>
-      <c r="O249" s="9"/>
+      <c r="O249" s="8"/>
     </row>
     <row r="250" spans="7:15">
       <c r="G250" s="4"/>
@@ -3746,7 +3770,7 @@
         <v/>
       </c>
       <c r="N250" s="7"/>
-      <c r="O250" s="9"/>
+      <c r="O250" s="8"/>
     </row>
     <row r="251" spans="7:15">
       <c r="G251" s="4"/>
@@ -3756,7 +3780,7 @@
         <v/>
       </c>
       <c r="N251" s="7"/>
-      <c r="O251" s="9"/>
+      <c r="O251" s="8"/>
     </row>
     <row r="252" spans="7:15">
       <c r="G252" s="4"/>
@@ -3766,7 +3790,7 @@
         <v/>
       </c>
       <c r="N252" s="7"/>
-      <c r="O252" s="9"/>
+      <c r="O252" s="8"/>
     </row>
     <row r="253" spans="7:15">
       <c r="G253" s="4"/>
@@ -3776,7 +3800,7 @@
         <v/>
       </c>
       <c r="N253" s="7"/>
-      <c r="O253" s="9"/>
+      <c r="O253" s="8"/>
     </row>
     <row r="254" spans="7:15">
       <c r="G254" s="4"/>
@@ -3786,7 +3810,7 @@
         <v/>
       </c>
       <c r="N254" s="7"/>
-      <c r="O254" s="9"/>
+      <c r="O254" s="8"/>
     </row>
     <row r="255" spans="7:15">
       <c r="G255" s="4"/>
@@ -3796,7 +3820,7 @@
         <v/>
       </c>
       <c r="N255" s="7"/>
-      <c r="O255" s="9"/>
+      <c r="O255" s="8"/>
     </row>
     <row r="256" spans="7:15">
       <c r="G256" s="4"/>
@@ -3806,7 +3830,7 @@
         <v/>
       </c>
       <c r="N256" s="7"/>
-      <c r="O256" s="9"/>
+      <c r="O256" s="8"/>
     </row>
     <row r="257" spans="7:15">
       <c r="G257" s="4"/>
@@ -3816,7 +3840,7 @@
         <v/>
       </c>
       <c r="N257" s="7"/>
-      <c r="O257" s="9"/>
+      <c r="O257" s="8"/>
     </row>
     <row r="258" spans="7:15">
       <c r="G258" s="4"/>
@@ -3826,7 +3850,7 @@
         <v/>
       </c>
       <c r="N258" s="7"/>
-      <c r="O258" s="9"/>
+      <c r="O258" s="8"/>
     </row>
     <row r="259" spans="7:15">
       <c r="G259" s="4"/>
@@ -3836,7 +3860,7 @@
         <v/>
       </c>
       <c r="N259" s="7"/>
-      <c r="O259" s="9"/>
+      <c r="O259" s="8"/>
     </row>
     <row r="260" spans="7:15">
       <c r="G260" s="4"/>
@@ -3846,7 +3870,7 @@
         <v/>
       </c>
       <c r="N260" s="7"/>
-      <c r="O260" s="9"/>
+      <c r="O260" s="8"/>
     </row>
     <row r="261" spans="7:15">
       <c r="G261" s="4"/>
@@ -3856,7 +3880,7 @@
         <v/>
       </c>
       <c r="N261" s="7"/>
-      <c r="O261" s="9"/>
+      <c r="O261" s="8"/>
     </row>
     <row r="262" spans="7:15">
       <c r="G262" s="4"/>
@@ -3866,7 +3890,7 @@
         <v/>
       </c>
       <c r="N262" s="7"/>
-      <c r="O262" s="9"/>
+      <c r="O262" s="8"/>
     </row>
     <row r="263" spans="7:15">
       <c r="G263" s="4"/>
@@ -3876,7 +3900,7 @@
         <v/>
       </c>
       <c r="N263" s="7"/>
-      <c r="O263" s="9"/>
+      <c r="O263" s="8"/>
     </row>
     <row r="264" spans="7:15">
       <c r="G264" s="4"/>
@@ -3886,7 +3910,7 @@
         <v/>
       </c>
       <c r="N264" s="7"/>
-      <c r="O264" s="9"/>
+      <c r="O264" s="8"/>
     </row>
     <row r="265" spans="7:15">
       <c r="G265" s="4"/>
@@ -3896,7 +3920,7 @@
         <v/>
       </c>
       <c r="N265" s="7"/>
-      <c r="O265" s="9"/>
+      <c r="O265" s="8"/>
     </row>
     <row r="266" spans="7:15">
       <c r="G266" s="4"/>
@@ -3906,7 +3930,7 @@
         <v/>
       </c>
       <c r="N266" s="7"/>
-      <c r="O266" s="9"/>
+      <c r="O266" s="8"/>
     </row>
     <row r="267" spans="7:15">
       <c r="G267" s="4"/>
@@ -3916,7 +3940,7 @@
         <v/>
       </c>
       <c r="N267" s="7"/>
-      <c r="O267" s="9"/>
+      <c r="O267" s="8"/>
     </row>
     <row r="268" spans="7:15">
       <c r="G268" s="4"/>
@@ -3926,7 +3950,7 @@
         <v/>
       </c>
       <c r="N268" s="7"/>
-      <c r="O268" s="9"/>
+      <c r="O268" s="8"/>
     </row>
     <row r="269" spans="7:15">
       <c r="G269" s="4"/>
@@ -3936,7 +3960,7 @@
         <v/>
       </c>
       <c r="N269" s="7"/>
-      <c r="O269" s="9"/>
+      <c r="O269" s="8"/>
     </row>
     <row r="270" spans="7:15">
       <c r="G270" s="4"/>
@@ -3946,7 +3970,7 @@
         <v/>
       </c>
       <c r="N270" s="7"/>
-      <c r="O270" s="9"/>
+      <c r="O270" s="8"/>
     </row>
     <row r="271" spans="7:15">
       <c r="G271" s="4"/>
@@ -3956,7 +3980,7 @@
         <v/>
       </c>
       <c r="N271" s="7"/>
-      <c r="O271" s="9"/>
+      <c r="O271" s="8"/>
     </row>
     <row r="272" spans="7:15">
       <c r="G272" s="4"/>
@@ -3966,7 +3990,7 @@
         <v/>
       </c>
       <c r="N272" s="7"/>
-      <c r="O272" s="9"/>
+      <c r="O272" s="8"/>
     </row>
     <row r="273" spans="7:15">
       <c r="G273" s="4"/>
@@ -3976,7 +4000,7 @@
         <v/>
       </c>
       <c r="N273" s="7"/>
-      <c r="O273" s="9"/>
+      <c r="O273" s="8"/>
     </row>
     <row r="274" spans="7:15">
       <c r="G274" s="4"/>
@@ -3986,7 +4010,7 @@
         <v/>
       </c>
       <c r="N274" s="7"/>
-      <c r="O274" s="9"/>
+      <c r="O274" s="8"/>
     </row>
     <row r="275" spans="7:15">
       <c r="G275" s="4"/>
@@ -3996,7 +4020,7 @@
         <v/>
       </c>
       <c r="N275" s="7"/>
-      <c r="O275" s="9"/>
+      <c r="O275" s="8"/>
     </row>
     <row r="276" spans="7:15">
       <c r="G276" s="4"/>
@@ -4006,7 +4030,7 @@
         <v/>
       </c>
       <c r="N276" s="7"/>
-      <c r="O276" s="9"/>
+      <c r="O276" s="8"/>
     </row>
     <row r="277" spans="7:15">
       <c r="G277" s="4"/>
@@ -4016,7 +4040,7 @@
         <v/>
       </c>
       <c r="N277" s="7"/>
-      <c r="O277" s="9"/>
+      <c r="O277" s="8"/>
     </row>
     <row r="278" spans="7:15">
       <c r="G278" s="4"/>
@@ -4026,7 +4050,7 @@
         <v/>
       </c>
       <c r="N278" s="7"/>
-      <c r="O278" s="9"/>
+      <c r="O278" s="8"/>
     </row>
     <row r="279" spans="7:15">
       <c r="G279" s="4"/>
@@ -4036,7 +4060,7 @@
         <v/>
       </c>
       <c r="N279" s="7"/>
-      <c r="O279" s="9"/>
+      <c r="O279" s="8"/>
     </row>
     <row r="280" spans="7:15">
       <c r="G280" s="4"/>
@@ -4046,7 +4070,7 @@
         <v/>
       </c>
       <c r="N280" s="7"/>
-      <c r="O280" s="9"/>
+      <c r="O280" s="8"/>
     </row>
     <row r="281" spans="7:15">
       <c r="G281" s="4"/>
@@ -4056,7 +4080,7 @@
         <v/>
       </c>
       <c r="N281" s="7"/>
-      <c r="O281" s="9"/>
+      <c r="O281" s="8"/>
     </row>
     <row r="282" spans="7:15">
       <c r="G282" s="4"/>
@@ -4066,7 +4090,7 @@
         <v/>
       </c>
       <c r="N282" s="7"/>
-      <c r="O282" s="9"/>
+      <c r="O282" s="8"/>
     </row>
     <row r="283" spans="7:15">
       <c r="G283" s="4"/>
@@ -4076,7 +4100,7 @@
         <v/>
       </c>
       <c r="N283" s="7"/>
-      <c r="O283" s="9"/>
+      <c r="O283" s="8"/>
     </row>
     <row r="284" spans="7:15">
       <c r="G284" s="4"/>
@@ -4086,7 +4110,7 @@
         <v/>
       </c>
       <c r="N284" s="7"/>
-      <c r="O284" s="9"/>
+      <c r="O284" s="8"/>
     </row>
     <row r="285" spans="7:15">
       <c r="G285" s="4"/>
@@ -4096,7 +4120,7 @@
         <v/>
       </c>
       <c r="N285" s="7"/>
-      <c r="O285" s="9"/>
+      <c r="O285" s="8"/>
     </row>
     <row r="286" spans="7:15">
       <c r="G286" s="4"/>
@@ -4106,7 +4130,7 @@
         <v/>
       </c>
       <c r="N286" s="7"/>
-      <c r="O286" s="9"/>
+      <c r="O286" s="8"/>
     </row>
     <row r="287" spans="7:15">
       <c r="G287" s="4"/>
@@ -4116,7 +4140,7 @@
         <v/>
       </c>
       <c r="N287" s="7"/>
-      <c r="O287" s="9"/>
+      <c r="O287" s="8"/>
     </row>
     <row r="288" spans="7:15">
       <c r="G288" s="4"/>
@@ -4126,7 +4150,7 @@
         <v/>
       </c>
       <c r="N288" s="7"/>
-      <c r="O288" s="9"/>
+      <c r="O288" s="8"/>
     </row>
     <row r="289" spans="7:15">
       <c r="G289" s="4"/>
@@ -4136,7 +4160,7 @@
         <v/>
       </c>
       <c r="N289" s="7"/>
-      <c r="O289" s="9"/>
+      <c r="O289" s="8"/>
     </row>
     <row r="290" spans="7:15">
       <c r="G290" s="4"/>
@@ -4146,7 +4170,7 @@
         <v/>
       </c>
       <c r="N290" s="7"/>
-      <c r="O290" s="9"/>
+      <c r="O290" s="8"/>
     </row>
     <row r="291" spans="7:15">
       <c r="G291" s="4"/>
@@ -4156,7 +4180,7 @@
         <v/>
       </c>
       <c r="N291" s="7"/>
-      <c r="O291" s="9"/>
+      <c r="O291" s="8"/>
     </row>
     <row r="292" spans="7:15">
       <c r="G292" s="4"/>
@@ -4166,7 +4190,7 @@
         <v/>
       </c>
       <c r="N292" s="7"/>
-      <c r="O292" s="9"/>
+      <c r="O292" s="8"/>
     </row>
     <row r="293" spans="7:15">
       <c r="G293" s="4"/>
@@ -4176,7 +4200,7 @@
         <v/>
       </c>
       <c r="N293" s="7"/>
-      <c r="O293" s="9"/>
+      <c r="O293" s="8"/>
     </row>
     <row r="294" spans="7:15">
       <c r="G294" s="4"/>
@@ -4186,7 +4210,7 @@
         <v/>
       </c>
       <c r="N294" s="7"/>
-      <c r="O294" s="9"/>
+      <c r="O294" s="8"/>
     </row>
     <row r="295" spans="7:15">
       <c r="G295" s="4"/>
@@ -4196,7 +4220,7 @@
         <v/>
       </c>
       <c r="N295" s="7"/>
-      <c r="O295" s="9"/>
+      <c r="O295" s="8"/>
     </row>
     <row r="296" spans="7:15">
       <c r="G296" s="4"/>
@@ -4206,7 +4230,7 @@
         <v/>
       </c>
       <c r="N296" s="7"/>
-      <c r="O296" s="9"/>
+      <c r="O296" s="8"/>
     </row>
     <row r="297" spans="7:15">
       <c r="G297" s="4"/>
@@ -4216,7 +4240,7 @@
         <v/>
       </c>
       <c r="N297" s="7"/>
-      <c r="O297" s="9"/>
+      <c r="O297" s="8"/>
     </row>
     <row r="298" spans="7:15">
       <c r="G298" s="4"/>
@@ -4226,7 +4250,7 @@
         <v/>
       </c>
       <c r="N298" s="7"/>
-      <c r="O298" s="9"/>
+      <c r="O298" s="8"/>
     </row>
     <row r="299" spans="7:15">
       <c r="G299" s="4"/>
@@ -4236,7 +4260,7 @@
         <v/>
       </c>
       <c r="N299" s="7"/>
-      <c r="O299" s="9"/>
+      <c r="O299" s="8"/>
     </row>
     <row r="300" spans="7:15">
       <c r="G300" s="4"/>
@@ -4246,7 +4270,7 @@
         <v/>
       </c>
       <c r="N300" s="7"/>
-      <c r="O300" s="9"/>
+      <c r="O300" s="8"/>
     </row>
     <row r="301" spans="7:15">
       <c r="G301" s="4"/>
@@ -4256,7 +4280,7 @@
         <v/>
       </c>
       <c r="N301" s="7"/>
-      <c r="O301" s="9"/>
+      <c r="O301" s="8"/>
     </row>
     <row r="302" spans="7:15">
       <c r="G302" s="4"/>
@@ -4266,7 +4290,7 @@
         <v/>
       </c>
       <c r="N302" s="7"/>
-      <c r="O302" s="9"/>
+      <c r="O302" s="8"/>
     </row>
     <row r="303" spans="7:15">
       <c r="G303" s="4"/>
@@ -4276,7 +4300,7 @@
         <v/>
       </c>
       <c r="N303" s="7"/>
-      <c r="O303" s="9"/>
+      <c r="O303" s="8"/>
     </row>
     <row r="304" spans="7:15">
       <c r="G304" s="4"/>
@@ -4286,7 +4310,7 @@
         <v/>
       </c>
       <c r="N304" s="7"/>
-      <c r="O304" s="9"/>
+      <c r="O304" s="8"/>
     </row>
     <row r="305" spans="7:15">
       <c r="G305" s="4"/>
@@ -4296,7 +4320,7 @@
         <v/>
       </c>
       <c r="N305" s="7"/>
-      <c r="O305" s="9"/>
+      <c r="O305" s="8"/>
     </row>
     <row r="306" spans="7:15">
       <c r="G306" s="4"/>
@@ -4306,7 +4330,7 @@
         <v/>
       </c>
       <c r="N306" s="7"/>
-      <c r="O306" s="9"/>
+      <c r="O306" s="8"/>
     </row>
     <row r="307" spans="7:15">
       <c r="G307" s="4"/>
@@ -4316,7 +4340,7 @@
         <v/>
       </c>
       <c r="N307" s="7"/>
-      <c r="O307" s="9"/>
+      <c r="O307" s="8"/>
     </row>
     <row r="308" spans="7:15">
       <c r="G308" s="4"/>
@@ -4326,7 +4350,7 @@
         <v/>
       </c>
       <c r="N308" s="7"/>
-      <c r="O308" s="9"/>
+      <c r="O308" s="8"/>
     </row>
     <row r="309" spans="7:15">
       <c r="G309" s="4"/>
@@ -4336,7 +4360,7 @@
         <v/>
       </c>
       <c r="N309" s="7"/>
-      <c r="O309" s="9"/>
+      <c r="O309" s="8"/>
     </row>
     <row r="310" spans="7:15">
       <c r="G310" s="4"/>
@@ -4346,7 +4370,7 @@
         <v/>
       </c>
       <c r="N310" s="7"/>
-      <c r="O310" s="9"/>
+      <c r="O310" s="8"/>
     </row>
     <row r="311" spans="7:15">
       <c r="G311" s="4"/>
@@ -4356,7 +4380,7 @@
         <v/>
       </c>
       <c r="N311" s="7"/>
-      <c r="O311" s="9"/>
+      <c r="O311" s="8"/>
     </row>
     <row r="312" spans="7:15">
       <c r="G312" s="4"/>
@@ -4366,7 +4390,7 @@
         <v/>
       </c>
       <c r="N312" s="7"/>
-      <c r="O312" s="9"/>
+      <c r="O312" s="8"/>
     </row>
     <row r="313" spans="7:15">
       <c r="G313" s="4"/>
@@ -4376,7 +4400,7 @@
         <v/>
       </c>
       <c r="N313" s="7"/>
-      <c r="O313" s="9"/>
+      <c r="O313" s="8"/>
     </row>
     <row r="314" spans="7:15">
       <c r="G314" s="4"/>
@@ -4386,7 +4410,7 @@
         <v/>
       </c>
       <c r="N314" s="7"/>
-      <c r="O314" s="9"/>
+      <c r="O314" s="8"/>
     </row>
     <row r="315" spans="7:15">
       <c r="G315" s="4"/>
@@ -4396,7 +4420,7 @@
         <v/>
       </c>
       <c r="N315" s="7"/>
-      <c r="O315" s="9"/>
+      <c r="O315" s="8"/>
     </row>
     <row r="316" spans="7:15">
       <c r="G316" s="4"/>
@@ -4406,7 +4430,7 @@
         <v/>
       </c>
       <c r="N316" s="7"/>
-      <c r="O316" s="9"/>
+      <c r="O316" s="8"/>
     </row>
     <row r="317" spans="7:15">
       <c r="G317" s="4"/>
@@ -4416,7 +4440,7 @@
         <v/>
       </c>
       <c r="N317" s="7"/>
-      <c r="O317" s="9"/>
+      <c r="O317" s="8"/>
     </row>
     <row r="318" spans="7:15">
       <c r="G318" s="4"/>
@@ -4426,7 +4450,7 @@
         <v/>
       </c>
       <c r="N318" s="7"/>
-      <c r="O318" s="9"/>
+      <c r="O318" s="8"/>
     </row>
     <row r="319" spans="7:15">
       <c r="G319" s="4"/>
@@ -4436,7 +4460,7 @@
         <v/>
       </c>
       <c r="N319" s="7"/>
-      <c r="O319" s="9"/>
+      <c r="O319" s="8"/>
     </row>
     <row r="320" spans="7:15">
       <c r="G320" s="4"/>
@@ -4446,7 +4470,7 @@
         <v/>
       </c>
       <c r="N320" s="7"/>
-      <c r="O320" s="9"/>
+      <c r="O320" s="8"/>
     </row>
     <row r="321" spans="7:15">
       <c r="G321" s="4"/>
@@ -4456,7 +4480,7 @@
         <v/>
       </c>
       <c r="N321" s="7"/>
-      <c r="O321" s="9"/>
+      <c r="O321" s="8"/>
     </row>
     <row r="322" spans="7:15">
       <c r="G322" s="4"/>
@@ -4466,7 +4490,7 @@
         <v/>
       </c>
       <c r="N322" s="7"/>
-      <c r="O322" s="9"/>
+      <c r="O322" s="8"/>
     </row>
     <row r="323" spans="7:15">
       <c r="G323" s="4"/>
@@ -4476,7 +4500,7 @@
         <v/>
       </c>
       <c r="N323" s="7"/>
-      <c r="O323" s="9"/>
+      <c r="O323" s="8"/>
     </row>
     <row r="324" spans="7:15">
       <c r="G324" s="4"/>
@@ -4486,7 +4510,7 @@
         <v/>
       </c>
       <c r="N324" s="7"/>
-      <c r="O324" s="9"/>
+      <c r="O324" s="8"/>
     </row>
     <row r="325" spans="7:15">
       <c r="G325" s="4"/>
@@ -4496,7 +4520,7 @@
         <v/>
       </c>
       <c r="N325" s="7"/>
-      <c r="O325" s="9"/>
+      <c r="O325" s="8"/>
     </row>
     <row r="326" spans="7:15">
       <c r="G326" s="4"/>
@@ -4506,7 +4530,7 @@
         <v/>
       </c>
       <c r="N326" s="7"/>
-      <c r="O326" s="9"/>
+      <c r="O326" s="8"/>
     </row>
     <row r="327" spans="7:15">
       <c r="G327" s="4"/>
@@ -4516,7 +4540,7 @@
         <v/>
       </c>
       <c r="N327" s="7"/>
-      <c r="O327" s="9"/>
+      <c r="O327" s="8"/>
     </row>
     <row r="328" spans="7:15">
       <c r="G328" s="4"/>
@@ -4526,7 +4550,7 @@
         <v/>
       </c>
       <c r="N328" s="7"/>
-      <c r="O328" s="9"/>
+      <c r="O328" s="8"/>
     </row>
     <row r="329" spans="7:15">
       <c r="G329" s="4"/>
@@ -4536,7 +4560,7 @@
         <v/>
       </c>
       <c r="N329" s="7"/>
-      <c r="O329" s="9"/>
+      <c r="O329" s="8"/>
     </row>
     <row r="330" spans="7:15">
       <c r="G330" s="4"/>
@@ -4546,7 +4570,7 @@
         <v/>
       </c>
       <c r="N330" s="7"/>
-      <c r="O330" s="9"/>
+      <c r="O330" s="8"/>
     </row>
     <row r="331" spans="7:15">
       <c r="G331" s="4"/>
@@ -4556,7 +4580,7 @@
         <v/>
       </c>
       <c r="N331" s="7"/>
-      <c r="O331" s="9"/>
+      <c r="O331" s="8"/>
     </row>
     <row r="332" spans="7:15">
       <c r="G332" s="4"/>
@@ -4566,7 +4590,7 @@
         <v/>
       </c>
       <c r="N332" s="7"/>
-      <c r="O332" s="9"/>
+      <c r="O332" s="8"/>
     </row>
     <row r="333" spans="7:15">
       <c r="G333" s="4"/>
@@ -4576,7 +4600,7 @@
         <v/>
       </c>
       <c r="N333" s="7"/>
-      <c r="O333" s="9"/>
+      <c r="O333" s="8"/>
     </row>
     <row r="334" spans="7:15">
       <c r="G334" s="4"/>
@@ -4586,7 +4610,7 @@
         <v/>
       </c>
       <c r="N334" s="7"/>
-      <c r="O334" s="9"/>
+      <c r="O334" s="8"/>
     </row>
     <row r="335" spans="7:15">
       <c r="G335" s="4"/>
@@ -4596,7 +4620,7 @@
         <v/>
       </c>
       <c r="N335" s="7"/>
-      <c r="O335" s="9"/>
+      <c r="O335" s="8"/>
     </row>
     <row r="336" spans="7:15">
       <c r="G336" s="4"/>
@@ -4606,7 +4630,7 @@
         <v/>
       </c>
       <c r="N336" s="7"/>
-      <c r="O336" s="9"/>
+      <c r="O336" s="8"/>
     </row>
     <row r="337" spans="7:15">
       <c r="G337" s="4"/>
@@ -4616,7 +4640,7 @@
         <v/>
       </c>
       <c r="N337" s="7"/>
-      <c r="O337" s="9"/>
+      <c r="O337" s="8"/>
     </row>
     <row r="338" spans="7:15">
       <c r="G338" s="4"/>
@@ -4626,7 +4650,7 @@
         <v/>
       </c>
       <c r="N338" s="7"/>
-      <c r="O338" s="9"/>
+      <c r="O338" s="8"/>
     </row>
     <row r="339" spans="7:15">
       <c r="G339" s="4"/>
@@ -4636,7 +4660,7 @@
         <v/>
       </c>
       <c r="N339" s="7"/>
-      <c r="O339" s="9"/>
+      <c r="O339" s="8"/>
     </row>
     <row r="340" spans="7:15">
       <c r="G340" s="4"/>
@@ -4646,7 +4670,7 @@
         <v/>
       </c>
       <c r="N340" s="7"/>
-      <c r="O340" s="9"/>
+      <c r="O340" s="8"/>
     </row>
     <row r="341" spans="7:15">
       <c r="G341" s="4"/>
@@ -4656,7 +4680,7 @@
         <v/>
       </c>
       <c r="N341" s="7"/>
-      <c r="O341" s="9"/>
+      <c r="O341" s="8"/>
     </row>
     <row r="342" spans="7:15">
       <c r="G342" s="4"/>
@@ -4666,7 +4690,7 @@
         <v/>
       </c>
       <c r="N342" s="7"/>
-      <c r="O342" s="9"/>
+      <c r="O342" s="8"/>
     </row>
     <row r="343" spans="7:15">
       <c r="G343" s="4"/>
@@ -4676,7 +4700,7 @@
         <v/>
       </c>
       <c r="N343" s="7"/>
-      <c r="O343" s="9"/>
+      <c r="O343" s="8"/>
     </row>
     <row r="344" spans="7:15">
       <c r="G344" s="4"/>
@@ -4686,7 +4710,7 @@
         <v/>
       </c>
       <c r="N344" s="7"/>
-      <c r="O344" s="9"/>
+      <c r="O344" s="8"/>
     </row>
     <row r="345" spans="7:15">
       <c r="G345" s="4"/>
@@ -4696,7 +4720,7 @@
         <v/>
       </c>
       <c r="N345" s="7"/>
-      <c r="O345" s="9"/>
+      <c r="O345" s="8"/>
     </row>
     <row r="346" spans="7:15">
       <c r="G346" s="4"/>
@@ -4706,7 +4730,7 @@
         <v/>
       </c>
       <c r="N346" s="7"/>
-      <c r="O346" s="9"/>
+      <c r="O346" s="8"/>
     </row>
     <row r="347" spans="7:15">
       <c r="G347" s="4"/>
@@ -4716,7 +4740,7 @@
         <v/>
       </c>
       <c r="N347" s="7"/>
-      <c r="O347" s="9"/>
+      <c r="O347" s="8"/>
     </row>
     <row r="348" spans="7:15">
       <c r="G348" s="4"/>
@@ -4726,7 +4750,7 @@
         <v/>
       </c>
       <c r="N348" s="7"/>
-      <c r="O348" s="9"/>
+      <c r="O348" s="8"/>
     </row>
     <row r="349" spans="7:15">
       <c r="G349" s="4"/>
@@ -4736,7 +4760,7 @@
         <v/>
       </c>
       <c r="N349" s="7"/>
-      <c r="O349" s="9"/>
+      <c r="O349" s="8"/>
     </row>
     <row r="350" spans="7:15">
       <c r="G350" s="4"/>
@@ -4746,7 +4770,7 @@
         <v/>
       </c>
       <c r="N350" s="7"/>
-      <c r="O350" s="10"/>
+      <c r="O350" s="9"/>
     </row>
     <row r="351" spans="7:15">
       <c r="G351" s="4"/>
@@ -4756,7 +4780,7 @@
         <v/>
       </c>
       <c r="N351" s="7"/>
-      <c r="O351" s="10"/>
+      <c r="O351" s="9"/>
     </row>
     <row r="352" spans="7:15">
       <c r="G352" s="4"/>
@@ -4766,7 +4790,7 @@
         <v/>
       </c>
       <c r="N352" s="7"/>
-      <c r="O352" s="10"/>
+      <c r="O352" s="9"/>
     </row>
     <row r="353" spans="7:15">
       <c r="G353" s="4"/>
@@ -4776,7 +4800,7 @@
         <v/>
       </c>
       <c r="N353" s="7"/>
-      <c r="O353" s="10"/>
+      <c r="O353" s="9"/>
     </row>
     <row r="354" spans="7:15">
       <c r="G354" s="4"/>
@@ -4786,7 +4810,7 @@
         <v/>
       </c>
       <c r="N354" s="7"/>
-      <c r="O354" s="10"/>
+      <c r="O354" s="9"/>
     </row>
     <row r="355" spans="7:15">
       <c r="G355" s="4"/>
@@ -4796,7 +4820,7 @@
         <v/>
       </c>
       <c r="N355" s="7"/>
-      <c r="O355" s="10"/>
+      <c r="O355" s="9"/>
     </row>
     <row r="356" spans="7:15">
       <c r="G356" s="4"/>
@@ -4806,7 +4830,7 @@
         <v/>
       </c>
       <c r="N356" s="7"/>
-      <c r="O356" s="10"/>
+      <c r="O356" s="9"/>
     </row>
     <row r="357" spans="7:14">
       <c r="G357" s="4"/>
